--- a/research/traditional_assets/database/data/switzerland/switzerland_shoe.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_shoe.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nyse_onon" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="F2">
-        <v>0.454</v>
+        <v>0.386</v>
       </c>
       <c r="G2">
-        <v>-0.1339335959482273</v>
+        <v>0.05962175446094668</v>
       </c>
       <c r="H2">
-        <v>-0.1339335959482273</v>
+        <v>0.05962175446094668</v>
       </c>
       <c r="I2">
-        <v>-0.1023260176327143</v>
+        <v>0.08996687680307726</v>
       </c>
       <c r="J2">
-        <v>-0.1023260176327143</v>
+        <v>0.08023576563866278</v>
       </c>
       <c r="K2">
-        <v>-104.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.09829300318889514</v>
+        <v>0.04669302275884176</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>362.7</v>
+        <v>472.4</v>
       </c>
       <c r="V2">
-        <v>0.06656755863891642</v>
+        <v>0.0550845975349526</v>
       </c>
       <c r="W2">
-        <v>-0.109064418774066</v>
+        <v>0.0892656521295067</v>
       </c>
       <c r="X2">
-        <v>0.09988168669671926</v>
+        <v>0.07983556465201325</v>
       </c>
       <c r="Y2">
-        <v>-0.2089461054707852</v>
+        <v>0.009430087477493451</v>
       </c>
       <c r="Z2">
-        <v>2.582223298619521</v>
+        <v>1.93188151512024</v>
       </c>
       <c r="AA2">
-        <v>-0.2642286267861468</v>
+        <v>0.1550059924888523</v>
       </c>
       <c r="AB2">
-        <v>0.09655291378113541</v>
+        <v>0.07889597454569418</v>
       </c>
       <c r="AC2">
-        <v>-0.3607815405672822</v>
+        <v>0.07611001794315815</v>
       </c>
       <c r="AD2">
-        <v>352.5</v>
+        <v>227.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>352.5</v>
+        <v>227.2</v>
       </c>
       <c r="AG2">
-        <v>-10.19999999999999</v>
+        <v>-245.2</v>
       </c>
       <c r="AH2">
-        <v>0.06076433779800382</v>
+        <v>0.02580908997966625</v>
       </c>
       <c r="AI2">
-        <v>0.2647191348753379</v>
+        <v>0.1596739054044557</v>
       </c>
       <c r="AJ2">
-        <v>-0.001875551632833184</v>
+        <v>-0.0294333009230917</v>
       </c>
       <c r="AK2">
-        <v>-0.01052740220869025</v>
+        <v>-0.2579694897422409</v>
       </c>
       <c r="AL2">
-        <v>5.82</v>
+        <v>6.01</v>
       </c>
       <c r="AM2">
-        <v>2.5</v>
+        <v>-4.59</v>
       </c>
       <c r="AN2">
-        <v>-4.226618705035971</v>
+        <v>1.135432283858071</v>
       </c>
       <c r="AO2">
-        <v>-18.74570446735395</v>
+        <v>28.01996672212979</v>
       </c>
       <c r="AP2">
-        <v>0.1223021582733811</v>
+        <v>-1.225387306346827</v>
       </c>
       <c r="AQ2">
-        <v>-43.63999999999999</v>
+        <v>-36.68845315904139</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="F3">
-        <v>0.454</v>
+        <v>0.386</v>
       </c>
       <c r="G3">
-        <v>-0.1339335959482273</v>
+        <v>0.05962175446094668</v>
       </c>
       <c r="H3">
-        <v>-0.1339335959482273</v>
+        <v>0.05962175446094668</v>
       </c>
       <c r="I3">
-        <v>-0.1023260176327143</v>
+        <v>0.08996687680307726</v>
       </c>
       <c r="J3">
-        <v>-0.1023260176327143</v>
+        <v>0.08023576563866278</v>
       </c>
       <c r="K3">
-        <v>-104.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L3">
-        <v>-0.09829300318889514</v>
+        <v>0.04669302275884176</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>362.7</v>
+        <v>472.4</v>
       </c>
       <c r="V3">
-        <v>0.06656755863891642</v>
+        <v>0.0550845975349526</v>
       </c>
       <c r="W3">
-        <v>-0.109064418774066</v>
+        <v>0.0892656521295067</v>
       </c>
       <c r="X3">
-        <v>0.09988168669671926</v>
+        <v>0.07983556465201325</v>
       </c>
       <c r="Y3">
-        <v>-0.2089461054707852</v>
+        <v>0.009430087477493451</v>
       </c>
       <c r="Z3">
-        <v>2.582223298619521</v>
+        <v>1.93188151512024</v>
       </c>
       <c r="AA3">
-        <v>-0.2642286267861468</v>
+        <v>0.1550059924888523</v>
       </c>
       <c r="AB3">
-        <v>0.09655291378113541</v>
+        <v>0.07889597454569418</v>
       </c>
       <c r="AC3">
-        <v>-0.3607815405672822</v>
+        <v>0.07611001794315815</v>
       </c>
       <c r="AD3">
-        <v>352.5</v>
+        <v>227.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>352.5</v>
+        <v>227.2</v>
       </c>
       <c r="AG3">
-        <v>-10.19999999999999</v>
+        <v>-245.2</v>
       </c>
       <c r="AH3">
-        <v>0.06076433779800382</v>
+        <v>0.02580908997966625</v>
       </c>
       <c r="AI3">
-        <v>0.2647191348753379</v>
+        <v>0.1596739054044557</v>
       </c>
       <c r="AJ3">
-        <v>-0.001875551632833184</v>
+        <v>-0.0294333009230917</v>
       </c>
       <c r="AK3">
-        <v>-0.01052740220869025</v>
+        <v>-0.2579694897422409</v>
       </c>
       <c r="AL3">
-        <v>5.82</v>
+        <v>6.01</v>
       </c>
       <c r="AM3">
-        <v>2.5</v>
+        <v>-4.59</v>
       </c>
       <c r="AN3">
-        <v>-4.226618705035971</v>
+        <v>1.135432283858071</v>
       </c>
       <c r="AO3">
-        <v>-18.74570446735395</v>
+        <v>28.01996672212979</v>
       </c>
       <c r="AP3">
-        <v>0.1223021582733811</v>
+        <v>-1.225387306346827</v>
       </c>
       <c r="AQ3">
-        <v>-43.63999999999999</v>
+        <v>-36.68845315904139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>On Holding AG (NYSE:ONON)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NYSE:ONON</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shoe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>28.0199667221298</v>
+      </c>
+      <c r="F2">
+        <v>6.96128995315383</v>
+      </c>
+      <c r="G2">
+        <v>1.13543228385807</v>
+      </c>
+      <c r="H2">
+        <v>2.63961019490255</v>
+      </c>
+      <c r="I2">
+        <v>0.0258090899796663</v>
+      </c>
+      <c r="J2">
+        <v>0.06</v>
+      </c>
+      <c r="K2">
+        <v>8575.9</v>
+      </c>
+      <c r="L2">
+        <v>8337.92986866233</v>
+      </c>
+      <c r="M2">
+        <v>8330.700000000001</v>
+      </c>
+      <c r="N2">
+        <v>8393.71586866233</v>
+      </c>
+      <c r="O2">
+        <v>227.2</v>
+      </c>
+      <c r="P2">
+        <v>528.186</v>
+      </c>
+      <c r="Q2">
+        <v>0.07889597454569421</v>
+      </c>
+      <c r="R2">
+        <v>0.0785949537933367</v>
+      </c>
+      <c r="S2">
+        <v>0.04343017</v>
+      </c>
+      <c r="T2">
+        <v>0.0391132</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.07983556465201321</v>
+      </c>
+      <c r="X2">
+        <v>0.08111506573759231</v>
+      </c>
+      <c r="Y2">
+        <v>0.89207749243507</v>
+      </c>
+      <c r="Z2">
+        <v>0.919892733425919</v>
+      </c>
+      <c r="AA2">
+        <v>227.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>28.01996672212979</v>
+      </c>
+      <c r="AD2">
+        <v>227.2</v>
+      </c>
+      <c r="AE2">
+        <v>6.01</v>
+      </c>
+      <c r="AF2">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="AG2">
+        <v>200.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>8575.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.146</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>78.80000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>6.01</v>
+      </c>
+      <c r="AS2">
+        <v>227.2</v>
+      </c>
+      <c r="AT2">
+        <v>472.4</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>0</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.07892768027252403</v>
+      </c>
+      <c r="C2">
+        <v>8796.517738162096</v>
+      </c>
+      <c r="D2">
+        <v>8324.117738162096</v>
+      </c>
+      <c r="E2">
+        <v>-227.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>472.4</v>
+      </c>
+      <c r="H2">
+        <v>8575.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>200.1</v>
+      </c>
+      <c r="K2">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L2">
+        <v>168.4</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>168.4</v>
+      </c>
+      <c r="O2">
+        <v>24.5864</v>
+      </c>
+      <c r="P2">
+        <v>143.8136</v>
+      </c>
+      <c r="Q2">
+        <v>175.5136</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.07892768027252403</v>
+      </c>
+      <c r="T2">
+        <v>0.8723408754896529</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.146</v>
+      </c>
+      <c r="W2">
+        <v>0.0381738</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07886283185932615</v>
+      </c>
+      <c r="C3">
+        <v>8721.960718945273</v>
+      </c>
+      <c r="D3">
+        <v>8337.591718945274</v>
+      </c>
+      <c r="E3">
+        <v>-139.169</v>
+      </c>
+      <c r="F3">
+        <v>88.03100000000001</v>
+      </c>
+      <c r="G3">
+        <v>472.4</v>
+      </c>
+      <c r="H3">
+        <v>8575.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>200.1</v>
+      </c>
+      <c r="K3">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L3">
+        <v>168.4</v>
+      </c>
+      <c r="M3">
+        <v>3.9349857</v>
+      </c>
+      <c r="N3">
+        <v>164.4650143</v>
+      </c>
+      <c r="O3">
+        <v>24.0118920878</v>
+      </c>
+      <c r="P3">
+        <v>140.4531222122</v>
+      </c>
+      <c r="Q3">
+        <v>172.1531222122</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07927383218113751</v>
+      </c>
+      <c r="T3">
+        <v>0.8798659169812504</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.146</v>
+      </c>
+      <c r="W3">
+        <v>0.0381738</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>42.79558118851613</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07879798344612826</v>
+      </c>
+      <c r="C4">
+        <v>8647.447390244717</v>
+      </c>
+      <c r="D4">
+        <v>8351.109390244717</v>
+      </c>
+      <c r="E4">
+        <v>-51.13799999999998</v>
+      </c>
+      <c r="F4">
+        <v>176.062</v>
+      </c>
+      <c r="G4">
+        <v>472.4</v>
+      </c>
+      <c r="H4">
+        <v>8575.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>200.1</v>
+      </c>
+      <c r="K4">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L4">
+        <v>168.4</v>
+      </c>
+      <c r="M4">
+        <v>7.869971400000001</v>
+      </c>
+      <c r="N4">
+        <v>160.5300286</v>
+      </c>
+      <c r="O4">
+        <v>23.4373841756</v>
+      </c>
+      <c r="P4">
+        <v>137.0926444244</v>
+      </c>
+      <c r="Q4">
+        <v>168.7926444244</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07962704841441659</v>
+      </c>
+      <c r="T4">
+        <v>0.8875445307481867</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.146</v>
+      </c>
+      <c r="W4">
+        <v>0.0381738</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>21.39779059425807</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07873313503293038</v>
+      </c>
+      <c r="C5">
+        <v>8572.977964910786</v>
+      </c>
+      <c r="D5">
+        <v>8364.670964910787</v>
+      </c>
+      <c r="E5">
+        <v>36.89300000000003</v>
+      </c>
+      <c r="F5">
+        <v>264.093</v>
+      </c>
+      <c r="G5">
+        <v>472.4</v>
+      </c>
+      <c r="H5">
+        <v>8575.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>200.1</v>
+      </c>
+      <c r="K5">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L5">
+        <v>168.4</v>
+      </c>
+      <c r="M5">
+        <v>11.8049571</v>
+      </c>
+      <c r="N5">
+        <v>156.5950429</v>
+      </c>
+      <c r="O5">
+        <v>22.8628762634</v>
+      </c>
+      <c r="P5">
+        <v>133.7321666366</v>
+      </c>
+      <c r="Q5">
+        <v>165.4321666366</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.07998754745662925</v>
+      </c>
+      <c r="T5">
+        <v>0.8953814664484619</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.146</v>
+      </c>
+      <c r="W5">
+        <v>0.0381738</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.26519372950538</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.07866828661973249</v>
+      </c>
+      <c r="C6">
+        <v>8498.552657178696</v>
+      </c>
+      <c r="D6">
+        <v>8378.276657178696</v>
+      </c>
+      <c r="E6">
+        <v>124.924</v>
+      </c>
+      <c r="F6">
+        <v>352.124</v>
+      </c>
+      <c r="G6">
+        <v>472.4</v>
+      </c>
+      <c r="H6">
+        <v>8575.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>200.1</v>
+      </c>
+      <c r="K6">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L6">
+        <v>168.4</v>
+      </c>
+      <c r="M6">
+        <v>15.7399428</v>
+      </c>
+      <c r="N6">
+        <v>152.6600572</v>
+      </c>
+      <c r="O6">
+        <v>22.2883683512</v>
+      </c>
+      <c r="P6">
+        <v>130.3716888488</v>
+      </c>
+      <c r="Q6">
+        <v>162.0716888488</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08035555689555468</v>
+      </c>
+      <c r="T6">
+        <v>0.9033816716424931</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.146</v>
+      </c>
+      <c r="W6">
+        <v>0.0381738</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.69889529712903</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07865040820653459</v>
+      </c>
+      <c r="C7">
+        <v>8414.280471672819</v>
+      </c>
+      <c r="D7">
+        <v>8382.03547167282</v>
+      </c>
+      <c r="E7">
+        <v>212.955</v>
+      </c>
+      <c r="F7">
+        <v>440.155</v>
+      </c>
+      <c r="G7">
+        <v>472.4</v>
+      </c>
+      <c r="H7">
+        <v>8575.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>200.1</v>
+      </c>
+      <c r="K7">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L7">
+        <v>168.4</v>
+      </c>
+      <c r="M7">
+        <v>20.159099</v>
+      </c>
+      <c r="N7">
+        <v>148.240901</v>
+      </c>
+      <c r="O7">
+        <v>21.643171546</v>
+      </c>
+      <c r="P7">
+        <v>126.597729454</v>
+      </c>
+      <c r="Q7">
+        <v>158.297729454</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08073131390161536</v>
+      </c>
+      <c r="T7">
+        <v>0.9115503022090299</v>
+      </c>
+      <c r="U7">
+        <v>0.0458</v>
+      </c>
+      <c r="V7">
+        <v>0.146</v>
+      </c>
+      <c r="W7">
+        <v>0.0391132</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>8.353547943784591</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07859495379333671</v>
+      </c>
+      <c r="C8">
+        <v>8337.92986866233</v>
+      </c>
+      <c r="D8">
+        <v>8393.71586866233</v>
+      </c>
+      <c r="E8">
+        <v>300.986</v>
+      </c>
+      <c r="F8">
+        <v>528.186</v>
+      </c>
+      <c r="G8">
+        <v>472.4</v>
+      </c>
+      <c r="H8">
+        <v>8575.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>200.1</v>
+      </c>
+      <c r="K8">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L8">
+        <v>168.4</v>
+      </c>
+      <c r="M8">
+        <v>24.1909188</v>
+      </c>
+      <c r="N8">
+        <v>144.2090812</v>
+      </c>
+      <c r="O8">
+        <v>21.0545258552</v>
+      </c>
+      <c r="P8">
+        <v>123.1545553448</v>
+      </c>
+      <c r="Q8">
+        <v>154.8545553448</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08111506573759225</v>
+      </c>
+      <c r="T8">
+        <v>0.9198927334259187</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.146</v>
+      </c>
+      <c r="W8">
+        <v>0.0391132</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.961289953153826</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07867101538013883</v>
+      </c>
+      <c r="C9">
+        <v>8233.886250421996</v>
+      </c>
+      <c r="D9">
+        <v>8377.703250421997</v>
+      </c>
+      <c r="E9">
+        <v>389.0170000000001</v>
+      </c>
+      <c r="F9">
+        <v>616.2170000000001</v>
+      </c>
+      <c r="G9">
+        <v>472.4</v>
+      </c>
+      <c r="H9">
+        <v>8575.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>200.1</v>
+      </c>
+      <c r="K9">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L9">
+        <v>168.4</v>
+      </c>
+      <c r="M9">
+        <v>29.578416</v>
+      </c>
+      <c r="N9">
+        <v>138.821584</v>
+      </c>
+      <c r="O9">
+        <v>20.267951264</v>
+      </c>
+      <c r="P9">
+        <v>118.553632736</v>
+      </c>
+      <c r="Q9">
+        <v>150.253632736</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08150707030122456</v>
+      </c>
+      <c r="T9">
+        <v>0.9284145717657513</v>
+      </c>
+      <c r="U9">
+        <v>0.048</v>
+      </c>
+      <c r="V9">
+        <v>0.146</v>
+      </c>
+      <c r="W9">
+        <v>0.040992</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.693340711686521</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07873682896694095</v>
+      </c>
+      <c r="C10">
+        <v>8132.049279483983</v>
+      </c>
+      <c r="D10">
+        <v>8363.897279483983</v>
+      </c>
+      <c r="E10">
+        <v>477.0480000000001</v>
+      </c>
+      <c r="F10">
+        <v>704.248</v>
+      </c>
+      <c r="G10">
+        <v>472.4</v>
+      </c>
+      <c r="H10">
+        <v>8575.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>200.1</v>
+      </c>
+      <c r="K10">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L10">
+        <v>168.4</v>
+      </c>
+      <c r="M10">
+        <v>34.86027600000001</v>
+      </c>
+      <c r="N10">
+        <v>133.539724</v>
+      </c>
+      <c r="O10">
+        <v>19.496799704</v>
+      </c>
+      <c r="P10">
+        <v>114.042924296</v>
+      </c>
+      <c r="Q10">
+        <v>145.742924296</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08190759670319669</v>
+      </c>
+      <c r="T10">
+        <v>0.9371216674607975</v>
+      </c>
+      <c r="U10">
+        <v>0.0495</v>
+      </c>
+      <c r="V10">
+        <v>0.146</v>
+      </c>
+      <c r="W10">
+        <v>0.042273</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.830713331127957</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07871297255374306</v>
+      </c>
+      <c r="C11">
+        <v>8049.017470891622</v>
+      </c>
+      <c r="D11">
+        <v>8368.896470891623</v>
+      </c>
+      <c r="E11">
+        <v>565.079</v>
+      </c>
+      <c r="F11">
+        <v>792.279</v>
+      </c>
+      <c r="G11">
+        <v>472.4</v>
+      </c>
+      <c r="H11">
+        <v>8575.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>200.1</v>
+      </c>
+      <c r="K11">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L11">
+        <v>168.4</v>
+      </c>
+      <c r="M11">
+        <v>39.2178105</v>
+      </c>
+      <c r="N11">
+        <v>129.1821895</v>
+      </c>
+      <c r="O11">
+        <v>18.860599667</v>
+      </c>
+      <c r="P11">
+        <v>110.321589833</v>
+      </c>
+      <c r="Q11">
+        <v>142.021589833</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08231692588323414</v>
+      </c>
+      <c r="T11">
+        <v>0.9460201278963942</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.146</v>
+      </c>
+      <c r="W11">
+        <v>0.042273</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.293967405447074</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07880867614054518</v>
+      </c>
+      <c r="C12">
+        <v>7940.967477835556</v>
+      </c>
+      <c r="D12">
+        <v>8348.877477835556</v>
+      </c>
+      <c r="E12">
+        <v>653.1100000000001</v>
+      </c>
+      <c r="F12">
+        <v>880.3100000000001</v>
+      </c>
+      <c r="G12">
+        <v>472.4</v>
+      </c>
+      <c r="H12">
+        <v>8575.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>200.1</v>
+      </c>
+      <c r="K12">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L12">
+        <v>168.4</v>
+      </c>
+      <c r="M12">
+        <v>44.807779</v>
+      </c>
+      <c r="N12">
+        <v>123.592221</v>
+      </c>
+      <c r="O12">
+        <v>18.044464266</v>
+      </c>
+      <c r="P12">
+        <v>105.547756734</v>
+      </c>
+      <c r="Q12">
+        <v>137.247756734</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08273535126727243</v>
+      </c>
+      <c r="T12">
+        <v>0.9551163318972266</v>
+      </c>
+      <c r="U12">
+        <v>0.0509</v>
+      </c>
+      <c r="V12">
+        <v>0.146</v>
+      </c>
+      <c r="W12">
+        <v>0.0434686</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>3.75827599042568</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07879677572734729</v>
+      </c>
+      <c r="C13">
+        <v>7855.420555362258</v>
+      </c>
+      <c r="D13">
+        <v>8351.361555362259</v>
+      </c>
+      <c r="E13">
+        <v>741.1410000000001</v>
+      </c>
+      <c r="F13">
+        <v>968.341</v>
+      </c>
+      <c r="G13">
+        <v>472.4</v>
+      </c>
+      <c r="H13">
+        <v>8575.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>200.1</v>
+      </c>
+      <c r="K13">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L13">
+        <v>168.4</v>
+      </c>
+      <c r="M13">
+        <v>49.2885569</v>
+      </c>
+      <c r="N13">
+        <v>119.1114431</v>
+      </c>
+      <c r="O13">
+        <v>17.3902706926</v>
+      </c>
+      <c r="P13">
+        <v>101.7211724074</v>
+      </c>
+      <c r="Q13">
+        <v>133.4211724074</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08316317946892954</v>
+      </c>
+      <c r="T13">
+        <v>0.9644169449767293</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.146</v>
+      </c>
+      <c r="W13">
+        <v>0.0434686</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>3.416614536750618</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07878487531414942</v>
+      </c>
+      <c r="C14">
+        <v>7769.875111525503</v>
+      </c>
+      <c r="D14">
+        <v>8353.847111525503</v>
+      </c>
+      <c r="E14">
+        <v>829.172</v>
+      </c>
+      <c r="F14">
+        <v>1056.372</v>
+      </c>
+      <c r="G14">
+        <v>472.4</v>
+      </c>
+      <c r="H14">
+        <v>8575.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>200.1</v>
+      </c>
+      <c r="K14">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L14">
+        <v>168.4</v>
+      </c>
+      <c r="M14">
+        <v>53.7693348</v>
+      </c>
+      <c r="N14">
+        <v>114.6306652</v>
+      </c>
+      <c r="O14">
+        <v>16.7360771192</v>
+      </c>
+      <c r="P14">
+        <v>97.89458808080001</v>
+      </c>
+      <c r="Q14">
+        <v>129.5945880808</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.08360073103880615</v>
+      </c>
+      <c r="T14">
+        <v>0.9739289356262206</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.146</v>
+      </c>
+      <c r="W14">
+        <v>0.0434686</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.131896658688067</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07906162690095153</v>
+      </c>
+      <c r="C15">
+        <v>7624.421184982952</v>
+      </c>
+      <c r="D15">
+        <v>8296.424184982952</v>
+      </c>
+      <c r="E15">
+        <v>917.203</v>
+      </c>
+      <c r="F15">
+        <v>1144.403</v>
+      </c>
+      <c r="G15">
+        <v>472.4</v>
+      </c>
+      <c r="H15">
+        <v>8575.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>200.1</v>
+      </c>
+      <c r="K15">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L15">
+        <v>168.4</v>
+      </c>
+      <c r="M15">
+        <v>61.2255605</v>
+      </c>
+      <c r="N15">
+        <v>107.1744395</v>
+      </c>
+      <c r="O15">
+        <v>15.647468167</v>
+      </c>
+      <c r="P15">
+        <v>91.52697133300001</v>
+      </c>
+      <c r="Q15">
+        <v>123.226971333</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08404834126546153</v>
+      </c>
+      <c r="T15">
+        <v>0.9836595927274244</v>
+      </c>
+      <c r="U15">
+        <v>0.0535</v>
+      </c>
+      <c r="V15">
+        <v>0.146</v>
+      </c>
+      <c r="W15">
+        <v>0.045689</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.750485232389175</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07907193048775364</v>
+      </c>
+      <c r="C16">
+        <v>7534.267542097404</v>
+      </c>
+      <c r="D16">
+        <v>8294.301542097404</v>
+      </c>
+      <c r="E16">
+        <v>1005.234</v>
+      </c>
+      <c r="F16">
+        <v>1232.434</v>
+      </c>
+      <c r="G16">
+        <v>472.4</v>
+      </c>
+      <c r="H16">
+        <v>8575.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>200.1</v>
+      </c>
+      <c r="K16">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L16">
+        <v>168.4</v>
+      </c>
+      <c r="M16">
+        <v>65.935219</v>
+      </c>
+      <c r="N16">
+        <v>102.464781</v>
+      </c>
+      <c r="O16">
+        <v>14.959858026</v>
+      </c>
+      <c r="P16">
+        <v>87.50492297400001</v>
+      </c>
+      <c r="Q16">
+        <v>119.204922974</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08450636103227167</v>
+      </c>
+      <c r="T16">
+        <v>0.993616544179819</v>
+      </c>
+      <c r="U16">
+        <v>0.0535</v>
+      </c>
+      <c r="V16">
+        <v>0.146</v>
+      </c>
+      <c r="W16">
+        <v>0.045689</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.554022001504234</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07942810407455575</v>
+      </c>
+      <c r="C17">
+        <v>7373.523054782174</v>
+      </c>
+      <c r="D17">
+        <v>8221.588054782174</v>
+      </c>
+      <c r="E17">
+        <v>1093.265</v>
+      </c>
+      <c r="F17">
+        <v>1320.465</v>
+      </c>
+      <c r="G17">
+        <v>472.4</v>
+      </c>
+      <c r="H17">
+        <v>8575.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>200.1</v>
+      </c>
+      <c r="K17">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L17">
+        <v>168.4</v>
+      </c>
+      <c r="M17">
+        <v>74.210133</v>
+      </c>
+      <c r="N17">
+        <v>94.18986700000001</v>
+      </c>
+      <c r="O17">
+        <v>13.751720582</v>
+      </c>
+      <c r="P17">
+        <v>80.438146418</v>
+      </c>
+      <c r="Q17">
+        <v>112.138146418</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08497515773477149</v>
+      </c>
+      <c r="T17">
+        <v>1.003807776842858</v>
+      </c>
+      <c r="U17">
+        <v>0.0562</v>
+      </c>
+      <c r="V17">
+        <v>0.146</v>
+      </c>
+      <c r="W17">
+        <v>0.0479948</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>2.269231885085019</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.08201663366135788</v>
+      </c>
+      <c r="C18">
+        <v>6793.046851921968</v>
+      </c>
+      <c r="D18">
+        <v>7729.142851921968</v>
+      </c>
+      <c r="E18">
+        <v>1181.296</v>
+      </c>
+      <c r="F18">
+        <v>1408.496</v>
+      </c>
+      <c r="G18">
+        <v>472.4</v>
+      </c>
+      <c r="H18">
+        <v>8575.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>200.1</v>
+      </c>
+      <c r="K18">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L18">
+        <v>168.4</v>
+      </c>
+      <c r="M18">
+        <v>105.4963504</v>
+      </c>
+      <c r="N18">
+        <v>62.90364960000001</v>
+      </c>
+      <c r="O18">
+        <v>9.183932841600001</v>
+      </c>
+      <c r="P18">
+        <v>53.71971675840001</v>
+      </c>
+      <c r="Q18">
+        <v>85.4197167584</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08545511626352129</v>
+      </c>
+      <c r="T18">
+        <v>1.014241657902637</v>
+      </c>
+      <c r="U18">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V18">
+        <v>0.146</v>
+      </c>
+      <c r="W18">
+        <v>0.0639646</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>1.596263750940146</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.08220969324815998</v>
+      </c>
+      <c r="C19">
+        <v>6670.641383602274</v>
+      </c>
+      <c r="D19">
+        <v>7694.768383602274</v>
+      </c>
+      <c r="E19">
+        <v>1269.327</v>
+      </c>
+      <c r="F19">
+        <v>1496.527</v>
+      </c>
+      <c r="G19">
+        <v>472.4</v>
+      </c>
+      <c r="H19">
+        <v>8575.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>200.1</v>
+      </c>
+      <c r="K19">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L19">
+        <v>168.4</v>
+      </c>
+      <c r="M19">
+        <v>112.0898723</v>
+      </c>
+      <c r="N19">
+        <v>56.3101277</v>
+      </c>
+      <c r="O19">
+        <v>8.221278644199998</v>
+      </c>
+      <c r="P19">
+        <v>48.0888490558</v>
+      </c>
+      <c r="Q19">
+        <v>79.78884905579999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.08594664005802408</v>
+      </c>
+      <c r="T19">
+        <v>1.024926957783132</v>
+      </c>
+      <c r="U19">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V19">
+        <v>0.146</v>
+      </c>
+      <c r="W19">
+        <v>0.0639646</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>1.502365883237785</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09054820614069753</v>
+      </c>
+      <c r="C20">
+        <v>5342.704111348003</v>
+      </c>
+      <c r="D20">
+        <v>6454.862111348003</v>
+      </c>
+      <c r="E20">
+        <v>1357.358</v>
+      </c>
+      <c r="F20">
+        <v>1584.558</v>
+      </c>
+      <c r="G20">
+        <v>472.4</v>
+      </c>
+      <c r="H20">
+        <v>8575.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>200.1</v>
+      </c>
+      <c r="K20">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L20">
+        <v>168.4</v>
+      </c>
+      <c r="M20">
+        <v>196.3267362</v>
+      </c>
+      <c r="N20">
+        <v>-27.92673619999999</v>
+      </c>
+      <c r="O20">
+        <v>-4.077303485199999</v>
+      </c>
+      <c r="P20">
+        <v>-23.8494327148</v>
+      </c>
+      <c r="Q20">
+        <v>7.850567285199993</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08663308702466153</v>
+      </c>
+      <c r="T20">
+        <v>1.039849717927425</v>
+      </c>
+      <c r="U20">
+        <v>0.1239</v>
+      </c>
+      <c r="V20">
+        <v>0.125232051812615</v>
+      </c>
+      <c r="W20">
+        <v>0.108383748780417</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.8577537795384591</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09139920614069753</v>
+      </c>
+      <c r="C21">
+        <v>5150.240210933806</v>
+      </c>
+      <c r="D21">
+        <v>6350.429210933807</v>
+      </c>
+      <c r="E21">
+        <v>1445.389</v>
+      </c>
+      <c r="F21">
+        <v>1672.589</v>
+      </c>
+      <c r="G21">
+        <v>472.4</v>
+      </c>
+      <c r="H21">
+        <v>8575.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>200.1</v>
+      </c>
+      <c r="K21">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L21">
+        <v>168.4</v>
+      </c>
+      <c r="M21">
+        <v>207.2337771</v>
+      </c>
+      <c r="N21">
+        <v>-38.83377710000002</v>
+      </c>
+      <c r="O21">
+        <v>-5.669731456600003</v>
+      </c>
+      <c r="P21">
+        <v>-33.16404564340002</v>
+      </c>
+      <c r="Q21">
+        <v>-1.464045643400027</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.0872236189632376</v>
+      </c>
+      <c r="T21">
+        <v>1.052687368766035</v>
+      </c>
+      <c r="U21">
+        <v>0.1239</v>
+      </c>
+      <c r="V21">
+        <v>0.1186408911908984</v>
+      </c>
+      <c r="W21">
+        <v>0.1092003935814477</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.8126088437732769</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1095980040461305</v>
+      </c>
+      <c r="C22">
+        <v>3429.816047035581</v>
+      </c>
+      <c r="D22">
+        <v>4718.036047035581</v>
+      </c>
+      <c r="E22">
+        <v>1533.42</v>
+      </c>
+      <c r="F22">
+        <v>1760.62</v>
+      </c>
+      <c r="G22">
+        <v>472.4</v>
+      </c>
+      <c r="H22">
+        <v>8575.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>200.1</v>
+      </c>
+      <c r="K22">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L22">
+        <v>168.4</v>
+      </c>
+      <c r="M22">
+        <v>367.6174560000001</v>
+      </c>
+      <c r="N22">
+        <v>-199.2174560000001</v>
+      </c>
+      <c r="O22">
+        <v>-29.08574857600001</v>
+      </c>
+      <c r="P22">
+        <v>-170.131707424</v>
+      </c>
+      <c r="Q22">
+        <v>-138.4317074240001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08828866158206927</v>
+      </c>
+      <c r="T22">
+        <v>1.075840469175419</v>
+      </c>
+      <c r="U22">
+        <v>0.2088</v>
+      </c>
+      <c r="V22">
+        <v>0.06688039318785774</v>
+      </c>
+      <c r="W22">
+        <v>0.1948353739023753</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4580848848483408</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1112980040461305</v>
+      </c>
+      <c r="C23">
+        <v>3231.152190510912</v>
+      </c>
+      <c r="D23">
+        <v>4607.403190510912</v>
+      </c>
+      <c r="E23">
+        <v>1621.451</v>
+      </c>
+      <c r="F23">
+        <v>1848.651</v>
+      </c>
+      <c r="G23">
+        <v>472.4</v>
+      </c>
+      <c r="H23">
+        <v>8575.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>200.1</v>
+      </c>
+      <c r="K23">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L23">
+        <v>168.4</v>
+      </c>
+      <c r="M23">
+        <v>385.9983288</v>
+      </c>
+      <c r="N23">
+        <v>-217.5983288</v>
+      </c>
+      <c r="O23">
+        <v>-31.7693560048</v>
+      </c>
+      <c r="P23">
+        <v>-185.8289727952</v>
+      </c>
+      <c r="Q23">
+        <v>-154.1289727952</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08891510033627267</v>
+      </c>
+      <c r="T23">
+        <v>1.08945870296245</v>
+      </c>
+      <c r="U23">
+        <v>0.2088</v>
+      </c>
+      <c r="V23">
+        <v>0.06369561255986453</v>
+      </c>
+      <c r="W23">
+        <v>0.1955003560975003</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.4362713189031817</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1129980040461305</v>
+      </c>
+      <c r="C24">
+        <v>3037.557900439133</v>
+      </c>
+      <c r="D24">
+        <v>4501.839900439133</v>
+      </c>
+      <c r="E24">
+        <v>1709.482</v>
+      </c>
+      <c r="F24">
+        <v>1936.682</v>
+      </c>
+      <c r="G24">
+        <v>472.4</v>
+      </c>
+      <c r="H24">
+        <v>8575.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>200.1</v>
+      </c>
+      <c r="K24">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L24">
+        <v>168.4</v>
+      </c>
+      <c r="M24">
+        <v>404.3792016</v>
+      </c>
+      <c r="N24">
+        <v>-235.9792016</v>
+      </c>
+      <c r="O24">
+        <v>-34.4529634336</v>
+      </c>
+      <c r="P24">
+        <v>-201.5262381664</v>
+      </c>
+      <c r="Q24">
+        <v>-169.8262381664001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.08955760162263515</v>
+      </c>
+      <c r="T24">
+        <v>1.103426122231199</v>
+      </c>
+      <c r="U24">
+        <v>0.2088</v>
+      </c>
+      <c r="V24">
+        <v>0.06080035744350704</v>
+      </c>
+      <c r="W24">
+        <v>0.1961048853657957</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.4164408044075826</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1146980040461305</v>
+      </c>
+      <c r="C25">
+        <v>2848.692525056943</v>
+      </c>
+      <c r="D25">
+        <v>4401.005525056944</v>
+      </c>
+      <c r="E25">
+        <v>1797.513</v>
+      </c>
+      <c r="F25">
+        <v>2024.713</v>
+      </c>
+      <c r="G25">
+        <v>472.4</v>
+      </c>
+      <c r="H25">
+        <v>8575.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>200.1</v>
+      </c>
+      <c r="K25">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L25">
+        <v>168.4</v>
+      </c>
+      <c r="M25">
+        <v>422.7600744000001</v>
+      </c>
+      <c r="N25">
+        <v>-254.3600744000001</v>
+      </c>
+      <c r="O25">
+        <v>-37.13657086240001</v>
+      </c>
+      <c r="P25">
+        <v>-217.2235035376</v>
+      </c>
+      <c r="Q25">
+        <v>-185.5235035376</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09021679125409796</v>
+      </c>
+      <c r="T25">
+        <v>1.117756331610825</v>
+      </c>
+      <c r="U25">
+        <v>0.2088</v>
+      </c>
+      <c r="V25">
+        <v>0.05815686364161544</v>
+      </c>
+      <c r="W25">
+        <v>0.1966568468716307</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.398334682476818</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1163980040461305</v>
+      </c>
+      <c r="C26">
+        <v>2664.245264296561</v>
+      </c>
+      <c r="D26">
+        <v>4304.589264296562</v>
+      </c>
+      <c r="E26">
+        <v>1885.544</v>
+      </c>
+      <c r="F26">
+        <v>2112.744</v>
+      </c>
+      <c r="G26">
+        <v>472.4</v>
+      </c>
+      <c r="H26">
+        <v>8575.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>200.1</v>
+      </c>
+      <c r="K26">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L26">
+        <v>168.4</v>
+      </c>
+      <c r="M26">
+        <v>441.1409472000001</v>
+      </c>
+      <c r="N26">
+        <v>-272.7409472000001</v>
+      </c>
+      <c r="O26">
+        <v>-39.82017829120001</v>
+      </c>
+      <c r="P26">
+        <v>-232.9207689088</v>
+      </c>
+      <c r="Q26">
+        <v>-201.2207689088</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09089332798112557</v>
+      </c>
+      <c r="T26">
+        <v>1.132463651763599</v>
+      </c>
+      <c r="U26">
+        <v>0.2088</v>
+      </c>
+      <c r="V26">
+        <v>0.05573366098988145</v>
+      </c>
+      <c r="W26">
+        <v>0.1971628115853128</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.381737404040284</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1180980040461305</v>
+      </c>
+      <c r="C27">
+        <v>2483.931969964825</v>
+      </c>
+      <c r="D27">
+        <v>4212.306969964826</v>
+      </c>
+      <c r="E27">
+        <v>1973.575</v>
+      </c>
+      <c r="F27">
+        <v>2200.775</v>
+      </c>
+      <c r="G27">
+        <v>472.4</v>
+      </c>
+      <c r="H27">
+        <v>8575.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>200.1</v>
+      </c>
+      <c r="K27">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L27">
+        <v>168.4</v>
+      </c>
+      <c r="M27">
+        <v>459.52182</v>
+      </c>
+      <c r="N27">
+        <v>-291.1218200000001</v>
+      </c>
+      <c r="O27">
+        <v>-42.50378572000001</v>
+      </c>
+      <c r="P27">
+        <v>-248.6180342800001</v>
+      </c>
+      <c r="Q27">
+        <v>-216.9180342800001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09158790568754058</v>
+      </c>
+      <c r="T27">
+        <v>1.147563167120447</v>
+      </c>
+      <c r="U27">
+        <v>0.2088</v>
+      </c>
+      <c r="V27">
+        <v>0.0535043145502862</v>
+      </c>
+      <c r="W27">
+        <v>0.1976282991219003</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3664679078786726</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1197980040461305</v>
+      </c>
+      <c r="C28">
+        <v>2307.49234887261</v>
+      </c>
+      <c r="D28">
+        <v>4123.898348872611</v>
+      </c>
+      <c r="E28">
+        <v>2061.606</v>
+      </c>
+      <c r="F28">
+        <v>2288.806</v>
+      </c>
+      <c r="G28">
+        <v>472.4</v>
+      </c>
+      <c r="H28">
+        <v>8575.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>200.1</v>
+      </c>
+      <c r="K28">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L28">
+        <v>168.4</v>
+      </c>
+      <c r="M28">
+        <v>477.9026928</v>
+      </c>
+      <c r="N28">
+        <v>-309.5026928</v>
+      </c>
+      <c r="O28">
+        <v>-45.18739314879999</v>
+      </c>
+      <c r="P28">
+        <v>-264.3152996512</v>
+      </c>
+      <c r="Q28">
+        <v>-232.6152996512</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.09230125576439921</v>
+      </c>
+      <c r="T28">
+        <v>1.16307077748694</v>
+      </c>
+      <c r="U28">
+        <v>0.2088</v>
+      </c>
+      <c r="V28">
+        <v>0.05144645629835212</v>
+      </c>
+      <c r="W28">
+        <v>0.1980579799249041</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3523729883448776</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1214980040461305</v>
+      </c>
+      <c r="C29">
+        <v>2134.687510931215</v>
+      </c>
+      <c r="D29">
+        <v>4039.124510931215</v>
+      </c>
+      <c r="E29">
+        <v>2149.637000000001</v>
+      </c>
+      <c r="F29">
+        <v>2376.837</v>
+      </c>
+      <c r="G29">
+        <v>472.4</v>
+      </c>
+      <c r="H29">
+        <v>8575.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>200.1</v>
+      </c>
+      <c r="K29">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L29">
+        <v>168.4</v>
+      </c>
+      <c r="M29">
+        <v>496.2835656000001</v>
+      </c>
+      <c r="N29">
+        <v>-327.8835656000001</v>
+      </c>
+      <c r="O29">
+        <v>-47.87100057760001</v>
+      </c>
+      <c r="P29">
+        <v>-280.0125650224001</v>
+      </c>
+      <c r="Q29">
+        <v>-248.3125650224001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.09303414967898004</v>
+      </c>
+      <c r="T29">
+        <v>1.17900325389087</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.04954103199100574</v>
+      </c>
+      <c r="W29">
+        <v>0.198455832520278</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3393221369246969</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1231980040461305</v>
+      </c>
+      <c r="C30">
+        <v>1965.297813575885</v>
+      </c>
+      <c r="D30">
+        <v>3957.765813575886</v>
+      </c>
+      <c r="E30">
+        <v>2237.668000000001</v>
+      </c>
+      <c r="F30">
+        <v>2464.868</v>
+      </c>
+      <c r="G30">
+        <v>472.4</v>
+      </c>
+      <c r="H30">
+        <v>8575.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>200.1</v>
+      </c>
+      <c r="K30">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L30">
+        <v>168.4</v>
+      </c>
+      <c r="M30">
+        <v>514.6644384000001</v>
+      </c>
+      <c r="N30">
+        <v>-346.2644384000001</v>
+      </c>
+      <c r="O30">
+        <v>-50.55460800640002</v>
+      </c>
+      <c r="P30">
+        <v>-295.7098303936001</v>
+      </c>
+      <c r="Q30">
+        <v>-264.0098303936001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.09378740175785476</v>
+      </c>
+      <c r="T30">
+        <v>1.195378299083799</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.04777170941989839</v>
+      </c>
+      <c r="W30">
+        <v>0.1988252670731252</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3272034891773862</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1248980040461305</v>
+      </c>
+      <c r="C31">
+        <v>1799.120961559687</v>
+      </c>
+      <c r="D31">
+        <v>3879.619961559687</v>
+      </c>
+      <c r="E31">
+        <v>2325.699</v>
+      </c>
+      <c r="F31">
+        <v>2552.899</v>
+      </c>
+      <c r="G31">
+        <v>472.4</v>
+      </c>
+      <c r="H31">
+        <v>8575.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>200.1</v>
+      </c>
+      <c r="K31">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L31">
+        <v>168.4</v>
+      </c>
+      <c r="M31">
+        <v>533.0453112</v>
+      </c>
+      <c r="N31">
+        <v>-364.6453112</v>
+      </c>
+      <c r="O31">
+        <v>-53.2382154352</v>
+      </c>
+      <c r="P31">
+        <v>-311.4070957648</v>
+      </c>
+      <c r="Q31">
+        <v>-279.7070957648</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.09456187220514849</v>
+      </c>
+      <c r="T31">
+        <v>1.212214613155402</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.04612440909507431</v>
+      </c>
+      <c r="W31">
+        <v>0.1991692233809485</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.315920610240235</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1265980040461305</v>
+      </c>
+      <c r="C32">
+        <v>1635.970327505294</v>
+      </c>
+      <c r="D32">
+        <v>3804.500327505294</v>
+      </c>
+      <c r="E32">
+        <v>2413.73</v>
+      </c>
+      <c r="F32">
+        <v>2640.93</v>
+      </c>
+      <c r="G32">
+        <v>472.4</v>
+      </c>
+      <c r="H32">
+        <v>8575.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>200.1</v>
+      </c>
+      <c r="K32">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L32">
+        <v>168.4</v>
+      </c>
+      <c r="M32">
+        <v>551.426184</v>
+      </c>
+      <c r="N32">
+        <v>-383.0261840000001</v>
+      </c>
+      <c r="O32">
+        <v>-55.92182286400001</v>
+      </c>
+      <c r="P32">
+        <v>-327.1043611360001</v>
+      </c>
+      <c r="Q32">
+        <v>-295.4043611360001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.09535847037950773</v>
+      </c>
+      <c r="T32">
+        <v>1.229531964771907</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.04458692879190516</v>
+      </c>
+      <c r="W32">
+        <v>0.1994902492682502</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3053899232322271</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1282980040461305</v>
+      </c>
+      <c r="C33">
+        <v>1475.67346386184</v>
+      </c>
+      <c r="D33">
+        <v>3732.23446386184</v>
+      </c>
+      <c r="E33">
+        <v>2501.761</v>
+      </c>
+      <c r="F33">
+        <v>2728.961</v>
+      </c>
+      <c r="G33">
+        <v>472.4</v>
+      </c>
+      <c r="H33">
+        <v>8575.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>200.1</v>
+      </c>
+      <c r="K33">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L33">
+        <v>168.4</v>
+      </c>
+      <c r="M33">
+        <v>569.8070568000001</v>
+      </c>
+      <c r="N33">
+        <v>-401.4070568000001</v>
+      </c>
+      <c r="O33">
+        <v>-58.60543029280001</v>
+      </c>
+      <c r="P33">
+        <v>-342.8016265072001</v>
+      </c>
+      <c r="Q33">
+        <v>-311.1016265072001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.09617815835602234</v>
+      </c>
+      <c r="T33">
+        <v>1.247351268609181</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.04314864076635984</v>
+      </c>
+      <c r="W33">
+        <v>0.1997905638079841</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2955386353860263</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1299980040461305</v>
+      </c>
+      <c r="C34">
+        <v>1318.070781291289</v>
+      </c>
+      <c r="D34">
+        <v>3662.662781291289</v>
+      </c>
+      <c r="E34">
+        <v>2589.792</v>
+      </c>
+      <c r="F34">
+        <v>2816.992</v>
+      </c>
+      <c r="G34">
+        <v>472.4</v>
+      </c>
+      <c r="H34">
+        <v>8575.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>200.1</v>
+      </c>
+      <c r="K34">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L34">
+        <v>168.4</v>
+      </c>
+      <c r="M34">
+        <v>588.1879296000001</v>
+      </c>
+      <c r="N34">
+        <v>-419.7879296000001</v>
+      </c>
+      <c r="O34">
+        <v>-61.28903772160001</v>
+      </c>
+      <c r="P34">
+        <v>-358.4988918784001</v>
+      </c>
+      <c r="Q34">
+        <v>-326.7988918784001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.09702195480243445</v>
+      </c>
+      <c r="T34">
+        <v>1.26569466961814</v>
+      </c>
+      <c r="U34">
+        <v>0.2088</v>
+      </c>
+      <c r="V34">
+        <v>0.04180024574241109</v>
+      </c>
+      <c r="W34">
+        <v>0.2000721086889846</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.286303053030213</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1316980040461305</v>
+      </c>
+      <c r="C35">
+        <v>1163.014372165134</v>
+      </c>
+      <c r="D35">
+        <v>3595.637372165134</v>
+      </c>
+      <c r="E35">
+        <v>2677.823</v>
+      </c>
+      <c r="F35">
+        <v>2905.023</v>
+      </c>
+      <c r="G35">
+        <v>472.4</v>
+      </c>
+      <c r="H35">
+        <v>8575.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>200.1</v>
+      </c>
+      <c r="K35">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L35">
+        <v>168.4</v>
+      </c>
+      <c r="M35">
+        <v>606.5688024000001</v>
+      </c>
+      <c r="N35">
+        <v>-438.1688024000001</v>
+      </c>
+      <c r="O35">
+        <v>-63.97264515040001</v>
+      </c>
+      <c r="P35">
+        <v>-374.1961572496001</v>
+      </c>
+      <c r="Q35">
+        <v>-342.4961572496001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09789093920247079</v>
+      </c>
+      <c r="T35">
+        <v>1.284585634836321</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.04053357162900469</v>
+      </c>
+      <c r="W35">
+        <v>0.2003365902438638</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2776272029383883</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1333980040461305</v>
+      </c>
+      <c r="C36">
+        <v>1010.366960917174</v>
+      </c>
+      <c r="D36">
+        <v>3531.020960917175</v>
+      </c>
+      <c r="E36">
+        <v>2765.854000000001</v>
+      </c>
+      <c r="F36">
+        <v>2993.054000000001</v>
+      </c>
+      <c r="G36">
+        <v>472.4</v>
+      </c>
+      <c r="H36">
+        <v>8575.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>200.1</v>
+      </c>
+      <c r="K36">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L36">
+        <v>168.4</v>
+      </c>
+      <c r="M36">
+        <v>624.9496752000001</v>
+      </c>
+      <c r="N36">
+        <v>-456.5496752000001</v>
+      </c>
+      <c r="O36">
+        <v>-66.65625257920001</v>
+      </c>
+      <c r="P36">
+        <v>-389.8934226208002</v>
+      </c>
+      <c r="Q36">
+        <v>-358.1934226208002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09878625646311429</v>
+      </c>
+      <c r="T36">
+        <v>1.304049053545963</v>
+      </c>
+      <c r="U36">
+        <v>0.2088</v>
+      </c>
+      <c r="V36">
+        <v>0.03934140775756337</v>
+      </c>
+      <c r="W36">
+        <v>0.2005855140602208</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2694616969696122</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1350980040461305</v>
+      </c>
+      <c r="C37">
+        <v>860.000965576216</v>
+      </c>
+      <c r="D37">
+        <v>3468.685965576216</v>
+      </c>
+      <c r="E37">
+        <v>2853.885000000001</v>
+      </c>
+      <c r="F37">
+        <v>3081.085</v>
+      </c>
+      <c r="G37">
+        <v>472.4</v>
+      </c>
+      <c r="H37">
+        <v>8575.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>200.1</v>
+      </c>
+      <c r="K37">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L37">
+        <v>168.4</v>
+      </c>
+      <c r="M37">
+        <v>643.3305480000001</v>
+      </c>
+      <c r="N37">
+        <v>-474.9305480000002</v>
+      </c>
+      <c r="O37">
+        <v>-69.33986000800002</v>
+      </c>
+      <c r="P37">
+        <v>-405.5906879920001</v>
+      </c>
+      <c r="Q37">
+        <v>-373.8906879920002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09970912194716219</v>
+      </c>
+      <c r="T37">
+        <v>1.324111346677439</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.03821736753591871</v>
+      </c>
+      <c r="W37">
+        <v>0.2008202136585002</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2617627913419089</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1367980040461305</v>
+      </c>
+      <c r="C38">
+        <v>711.797656977933</v>
+      </c>
+      <c r="D38">
+        <v>3408.513656977933</v>
+      </c>
+      <c r="E38">
+        <v>2941.916</v>
+      </c>
+      <c r="F38">
+        <v>3169.116</v>
+      </c>
+      <c r="G38">
+        <v>472.4</v>
+      </c>
+      <c r="H38">
+        <v>8575.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>200.1</v>
+      </c>
+      <c r="K38">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L38">
+        <v>168.4</v>
+      </c>
+      <c r="M38">
+        <v>661.7114208</v>
+      </c>
+      <c r="N38">
+        <v>-493.3114208000001</v>
+      </c>
+      <c r="O38">
+        <v>-72.0234674368</v>
+      </c>
+      <c r="P38">
+        <v>-421.2879533632001</v>
+      </c>
+      <c r="Q38">
+        <v>-389.5879533632001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1006608269775866</v>
+      </c>
+      <c r="T38">
+        <v>1.344800586469274</v>
+      </c>
+      <c r="U38">
+        <v>0.2088</v>
+      </c>
+      <c r="V38">
+        <v>0.03715577399325431</v>
+      </c>
+      <c r="W38">
+        <v>0.2010418743902085</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2544916026935227</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1384980040461305</v>
+      </c>
+      <c r="C39">
+        <v>565.6464039969269</v>
+      </c>
+      <c r="D39">
+        <v>3350.393403996927</v>
+      </c>
+      <c r="E39">
+        <v>3029.947</v>
+      </c>
+      <c r="F39">
+        <v>3257.147</v>
+      </c>
+      <c r="G39">
+        <v>472.4</v>
+      </c>
+      <c r="H39">
+        <v>8575.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>200.1</v>
+      </c>
+      <c r="K39">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L39">
+        <v>168.4</v>
+      </c>
+      <c r="M39">
+        <v>680.0922936000001</v>
+      </c>
+      <c r="N39">
+        <v>-511.6922936000001</v>
+      </c>
+      <c r="O39">
+        <v>-74.70707486560001</v>
+      </c>
+      <c r="P39">
+        <v>-436.9852187344001</v>
+      </c>
+      <c r="Q39">
+        <v>-405.2852187344001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1016427448661197</v>
+      </c>
+      <c r="T39">
+        <v>1.366146627524342</v>
+      </c>
+      <c r="U39">
+        <v>0.2088</v>
+      </c>
+      <c r="V39">
+        <v>0.03615156388532852</v>
+      </c>
+      <c r="W39">
+        <v>0.2012515534607434</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2476134512693734</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1401980040461305</v>
+      </c>
+      <c r="C40">
+        <v>421.4439947036676</v>
+      </c>
+      <c r="D40">
+        <v>3294.221994703668</v>
+      </c>
+      <c r="E40">
+        <v>3117.978000000001</v>
+      </c>
+      <c r="F40">
+        <v>3345.178</v>
+      </c>
+      <c r="G40">
+        <v>472.4</v>
+      </c>
+      <c r="H40">
+        <v>8575.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>200.1</v>
+      </c>
+      <c r="K40">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L40">
+        <v>168.4</v>
+      </c>
+      <c r="M40">
+        <v>698.4731664000001</v>
+      </c>
+      <c r="N40">
+        <v>-530.0731664000001</v>
+      </c>
+      <c r="O40">
+        <v>-77.39068229440001</v>
+      </c>
+      <c r="P40">
+        <v>-452.6824841056001</v>
+      </c>
+      <c r="Q40">
+        <v>-420.9824841056001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1026563375252507</v>
+      </c>
+      <c r="T40">
+        <v>1.388181250548928</v>
+      </c>
+      <c r="U40">
+        <v>0.2088</v>
+      </c>
+      <c r="V40">
+        <v>0.03520020694097777</v>
+      </c>
+      <c r="W40">
+        <v>0.2014501967907238</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2410973078149161</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1418980040461305</v>
+      </c>
+      <c r="C41">
+        <v>279.0940246827677</v>
+      </c>
+      <c r="D41">
+        <v>3239.903024682768</v>
+      </c>
+      <c r="E41">
+        <v>3206.009</v>
+      </c>
+      <c r="F41">
+        <v>3433.209</v>
+      </c>
+      <c r="G41">
+        <v>472.4</v>
+      </c>
+      <c r="H41">
+        <v>8575.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>200.1</v>
+      </c>
+      <c r="K41">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L41">
+        <v>168.4</v>
+      </c>
+      <c r="M41">
+        <v>716.8540392000001</v>
+      </c>
+      <c r="N41">
+        <v>-548.4540392000001</v>
+      </c>
+      <c r="O41">
+        <v>-80.07428972320001</v>
+      </c>
+      <c r="P41">
+        <v>-468.3797494768001</v>
+      </c>
+      <c r="Q41">
+        <v>-436.6797494768001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1037031627305827</v>
+      </c>
+      <c r="T41">
+        <v>1.410938320230058</v>
+      </c>
+      <c r="U41">
+        <v>0.2088</v>
+      </c>
+      <c r="V41">
+        <v>0.03429763753223474</v>
+      </c>
+      <c r="W41">
+        <v>0.2016386532832694</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2349153255632517</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1435980040461305</v>
+      </c>
+      <c r="C42">
+        <v>138.5063448863075</v>
+      </c>
+      <c r="D42">
+        <v>3187.346344886308</v>
+      </c>
+      <c r="E42">
+        <v>3294.04</v>
+      </c>
+      <c r="F42">
+        <v>3521.24</v>
+      </c>
+      <c r="G42">
+        <v>472.4</v>
+      </c>
+      <c r="H42">
+        <v>8575.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>200.1</v>
+      </c>
+      <c r="K42">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L42">
+        <v>168.4</v>
+      </c>
+      <c r="M42">
+        <v>735.2349120000001</v>
+      </c>
+      <c r="N42">
+        <v>-566.8349120000001</v>
+      </c>
+      <c r="O42">
+        <v>-82.75789715200001</v>
+      </c>
+      <c r="P42">
+        <v>-484.0770148480001</v>
+      </c>
+      <c r="Q42">
+        <v>-452.3770148480002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1047848821094257</v>
+      </c>
+      <c r="T42">
+        <v>1.434453958900559</v>
+      </c>
+      <c r="U42">
+        <v>0.2088</v>
+      </c>
+      <c r="V42">
+        <v>0.03344019659392887</v>
+      </c>
+      <c r="W42">
+        <v>0.2018176869511877</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2290424424241704</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1452980040461305</v>
+      </c>
+      <c r="C43">
+        <v>-0.4034376302147393</v>
+      </c>
+      <c r="D43">
+        <v>3136.467562369786</v>
+      </c>
+      <c r="E43">
+        <v>3382.071000000001</v>
+      </c>
+      <c r="F43">
+        <v>3609.271000000001</v>
+      </c>
+      <c r="G43">
+        <v>472.4</v>
+      </c>
+      <c r="H43">
+        <v>8575.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>200.1</v>
+      </c>
+      <c r="K43">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L43">
+        <v>168.4</v>
+      </c>
+      <c r="M43">
+        <v>753.6157848000001</v>
+      </c>
+      <c r="N43">
+        <v>-585.2157848000002</v>
+      </c>
+      <c r="O43">
+        <v>-85.44150458080001</v>
+      </c>
+      <c r="P43">
+        <v>-499.7742802192001</v>
+      </c>
+      <c r="Q43">
+        <v>-468.0742802192001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1059032699417888</v>
+      </c>
+      <c r="T43">
+        <v>1.458766737864975</v>
+      </c>
+      <c r="U43">
+        <v>0.2088</v>
+      </c>
+      <c r="V43">
+        <v>0.03262458204285744</v>
+      </c>
+      <c r="W43">
+        <v>0.2019879872694514</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2234560413894344</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1469980040461305</v>
+      </c>
+      <c r="C44">
+        <v>-137.7144119054819</v>
+      </c>
+      <c r="D44">
+        <v>3087.187588094518</v>
+      </c>
+      <c r="E44">
+        <v>3470.102</v>
+      </c>
+      <c r="F44">
+        <v>3697.302</v>
+      </c>
+      <c r="G44">
+        <v>472.4</v>
+      </c>
+      <c r="H44">
+        <v>8575.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>200.1</v>
+      </c>
+      <c r="K44">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L44">
+        <v>168.4</v>
+      </c>
+      <c r="M44">
+        <v>771.9966576</v>
+      </c>
+      <c r="N44">
+        <v>-603.5966576000001</v>
+      </c>
+      <c r="O44">
+        <v>-88.1251120096</v>
+      </c>
+      <c r="P44">
+        <v>-515.4715455904001</v>
+      </c>
+      <c r="Q44">
+        <v>-483.7715455904001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1070602228718197</v>
+      </c>
+      <c r="T44">
+        <v>1.483917888517819</v>
+      </c>
+      <c r="U44">
+        <v>0.2088</v>
+      </c>
+      <c r="V44">
+        <v>0.03184780627993226</v>
+      </c>
+      <c r="W44">
+        <v>0.2021501780487502</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2181356594515909</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1486980040461305</v>
+      </c>
+      <c r="C45">
+        <v>-273.500773300013</v>
+      </c>
+      <c r="D45">
+        <v>3039.432226699987</v>
+      </c>
+      <c r="E45">
+        <v>3558.133</v>
+      </c>
+      <c r="F45">
+        <v>3785.333</v>
+      </c>
+      <c r="G45">
+        <v>472.4</v>
+      </c>
+      <c r="H45">
+        <v>8575.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>200.1</v>
+      </c>
+      <c r="K45">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L45">
+        <v>168.4</v>
+      </c>
+      <c r="M45">
+        <v>790.3775304000001</v>
+      </c>
+      <c r="N45">
+        <v>-621.9775304000001</v>
+      </c>
+      <c r="O45">
+        <v>-90.8087194384</v>
+      </c>
+      <c r="P45">
+        <v>-531.1688109616001</v>
+      </c>
+      <c r="Q45">
+        <v>-499.4688109616001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1082577706415007</v>
+      </c>
+      <c r="T45">
+        <v>1.509951535684799</v>
+      </c>
+      <c r="U45">
+        <v>0.2088</v>
+      </c>
+      <c r="V45">
+        <v>0.03110715962225942</v>
+      </c>
+      <c r="W45">
+        <v>0.2023048250708722</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2130627371387631</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1503980040461305</v>
+      </c>
+      <c r="C46">
+        <v>-407.8321962292107</v>
+      </c>
+      <c r="D46">
+        <v>2993.131803770789</v>
+      </c>
+      <c r="E46">
+        <v>3646.164</v>
+      </c>
+      <c r="F46">
+        <v>3873.364</v>
+      </c>
+      <c r="G46">
+        <v>472.4</v>
+      </c>
+      <c r="H46">
+        <v>8575.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>200.1</v>
+      </c>
+      <c r="K46">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L46">
+        <v>168.4</v>
+      </c>
+      <c r="M46">
+        <v>808.7584032000001</v>
+      </c>
+      <c r="N46">
+        <v>-640.3584032000001</v>
+      </c>
+      <c r="O46">
+        <v>-93.49232686720001</v>
+      </c>
+      <c r="P46">
+        <v>-546.8660763328</v>
+      </c>
+      <c r="Q46">
+        <v>-515.1660763328</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1094980879743847</v>
+      </c>
+      <c r="T46">
+        <v>1.536914955964884</v>
+      </c>
+      <c r="U46">
+        <v>0.2088</v>
+      </c>
+      <c r="V46">
+        <v>0.03040017872175352</v>
+      </c>
+      <c r="W46">
+        <v>0.2024524426828979</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2082204022037912</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1520980040461305</v>
+      </c>
+      <c r="C47">
+        <v>-540.774173339968</v>
+      </c>
+      <c r="D47">
+        <v>2948.220826660032</v>
+      </c>
+      <c r="E47">
+        <v>3734.195000000001</v>
+      </c>
+      <c r="F47">
+        <v>3961.395</v>
+      </c>
+      <c r="G47">
+        <v>472.4</v>
+      </c>
+      <c r="H47">
+        <v>8575.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>200.1</v>
+      </c>
+      <c r="K47">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L47">
+        <v>168.4</v>
+      </c>
+      <c r="M47">
+        <v>827.1392760000001</v>
+      </c>
+      <c r="N47">
+        <v>-658.7392760000001</v>
+      </c>
+      <c r="O47">
+        <v>-96.17593429600001</v>
+      </c>
+      <c r="P47">
+        <v>-562.5633417040001</v>
+      </c>
+      <c r="Q47">
+        <v>-530.863341704</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1107835077557371</v>
+      </c>
+      <c r="T47">
+        <v>1.564858864255155</v>
+      </c>
+      <c r="U47">
+        <v>0.2088</v>
+      </c>
+      <c r="V47">
+        <v>0.02972461919460344</v>
+      </c>
+      <c r="W47">
+        <v>0.2025934995121668</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2035932821548181</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1676654350771441</v>
+      </c>
+      <c r="C48">
+        <v>-984.9613788868837</v>
+      </c>
+      <c r="D48">
+        <v>2592.064621113117</v>
+      </c>
+      <c r="E48">
+        <v>3822.226000000001</v>
+      </c>
+      <c r="F48">
+        <v>4049.426</v>
+      </c>
+      <c r="G48">
+        <v>472.4</v>
+      </c>
+      <c r="H48">
+        <v>8575.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>200.1</v>
+      </c>
+      <c r="K48">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L48">
+        <v>168.4</v>
+      </c>
+      <c r="M48">
+        <v>967.0029288000002</v>
+      </c>
+      <c r="N48">
+        <v>-798.6029288000002</v>
+      </c>
+      <c r="O48">
+        <v>-116.5960276048</v>
+      </c>
+      <c r="P48">
+        <v>-682.0069011952002</v>
+      </c>
+      <c r="Q48">
+        <v>-650.3069011952002</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1122414079567946</v>
+      </c>
+      <c r="T48">
+        <v>1.596552346886839</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.02542536249658564</v>
+      </c>
+      <c r="W48">
+        <v>0.2327284234358153</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1741463184697647</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1696654350771442</v>
+      </c>
+      <c r="C49">
+        <v>-1112.606576777795</v>
+      </c>
+      <c r="D49">
+        <v>2552.450423222205</v>
+      </c>
+      <c r="E49">
+        <v>3910.257000000001</v>
+      </c>
+      <c r="F49">
+        <v>4137.457</v>
+      </c>
+      <c r="G49">
+        <v>472.4</v>
+      </c>
+      <c r="H49">
+        <v>8575.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>200.1</v>
+      </c>
+      <c r="K49">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L49">
+        <v>168.4</v>
+      </c>
+      <c r="M49">
+        <v>988.0247316000001</v>
+      </c>
+      <c r="N49">
+        <v>-819.6247316000001</v>
+      </c>
+      <c r="O49">
+        <v>-119.6652108136</v>
+      </c>
+      <c r="P49">
+        <v>-699.9595207864002</v>
+      </c>
+      <c r="Q49">
+        <v>-668.2595207864001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1136270948993756</v>
+      </c>
+      <c r="T49">
+        <v>1.626675976073383</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.02488439733708382</v>
+      </c>
+      <c r="W49">
+        <v>0.2328576059159044</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.170441077651259</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1716654350771441</v>
+      </c>
+      <c r="C50">
+        <v>-1239.059163577104</v>
+      </c>
+      <c r="D50">
+        <v>2514.028836422896</v>
+      </c>
+      <c r="E50">
+        <v>3998.288</v>
+      </c>
+      <c r="F50">
+        <v>4225.488</v>
+      </c>
+      <c r="G50">
+        <v>472.4</v>
+      </c>
+      <c r="H50">
+        <v>8575.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>200.1</v>
+      </c>
+      <c r="K50">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L50">
+        <v>168.4</v>
+      </c>
+      <c r="M50">
+        <v>1009.0465344</v>
+      </c>
+      <c r="N50">
+        <v>-840.6465344000002</v>
+      </c>
+      <c r="O50">
+        <v>-122.7343940224</v>
+      </c>
+      <c r="P50">
+        <v>-717.9121403776002</v>
+      </c>
+      <c r="Q50">
+        <v>-686.2121403776002</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1150660774935944</v>
+      </c>
+      <c r="T50">
+        <v>1.657958206382486</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.02436597239256124</v>
+      </c>
+      <c r="W50">
+        <v>0.2329814057926564</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1668902218668578</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1736654350771441</v>
+      </c>
+      <c r="C51">
+        <v>-1364.372197109044</v>
+      </c>
+      <c r="D51">
+        <v>2476.746802890957</v>
+      </c>
+      <c r="E51">
+        <v>4086.319</v>
+      </c>
+      <c r="F51">
+        <v>4313.519</v>
+      </c>
+      <c r="G51">
+        <v>472.4</v>
+      </c>
+      <c r="H51">
+        <v>8575.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>200.1</v>
+      </c>
+      <c r="K51">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L51">
+        <v>168.4</v>
+      </c>
+      <c r="M51">
+        <v>1030.0683372</v>
+      </c>
+      <c r="N51">
+        <v>-861.6683372000001</v>
+      </c>
+      <c r="O51">
+        <v>-125.8035772312</v>
+      </c>
+      <c r="P51">
+        <v>-735.8647599688001</v>
+      </c>
+      <c r="Q51">
+        <v>-704.1647599688001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1165614907777825</v>
+      </c>
+      <c r="T51">
+        <v>1.690467190821358</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.02386870764985591</v>
+      </c>
+      <c r="W51">
+        <v>0.2331001526132144</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1634842989716158</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1756654350771441</v>
+      </c>
+      <c r="C52">
+        <v>-1488.595633884552</v>
+      </c>
+      <c r="D52">
+        <v>2440.554366115448</v>
+      </c>
+      <c r="E52">
+        <v>4174.35</v>
+      </c>
+      <c r="F52">
+        <v>4401.55</v>
+      </c>
+      <c r="G52">
+        <v>472.4</v>
+      </c>
+      <c r="H52">
+        <v>8575.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>200.1</v>
+      </c>
+      <c r="K52">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L52">
+        <v>168.4</v>
+      </c>
+      <c r="M52">
+        <v>1051.09014</v>
+      </c>
+      <c r="N52">
+        <v>-882.69014</v>
+      </c>
+      <c r="O52">
+        <v>-128.87276044</v>
+      </c>
+      <c r="P52">
+        <v>-753.8173795600001</v>
+      </c>
+      <c r="Q52">
+        <v>-722.11737956</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1181167205933381</v>
+      </c>
+      <c r="T52">
+        <v>1.724276534637786</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.02339133349685879</v>
+      </c>
+      <c r="W52">
+        <v>0.2332141495609501</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1602146129921835</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1776654350771442</v>
+      </c>
+      <c r="C53">
+        <v>-1611.776552433536</v>
+      </c>
+      <c r="D53">
+        <v>2405.404447566464</v>
+      </c>
+      <c r="E53">
+        <v>4262.381</v>
+      </c>
+      <c r="F53">
+        <v>4489.581</v>
+      </c>
+      <c r="G53">
+        <v>472.4</v>
+      </c>
+      <c r="H53">
+        <v>8575.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>200.1</v>
+      </c>
+      <c r="K53">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L53">
+        <v>168.4</v>
+      </c>
+      <c r="M53">
+        <v>1072.1119428</v>
+      </c>
+      <c r="N53">
+        <v>-903.7119428000002</v>
+      </c>
+      <c r="O53">
+        <v>-131.9419436488</v>
+      </c>
+      <c r="P53">
+        <v>-771.7699991512002</v>
+      </c>
+      <c r="Q53">
+        <v>-740.0699991512001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1197354291768757</v>
+      </c>
+      <c r="T53">
+        <v>1.75946585167121</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02293267989888116</v>
+      </c>
+      <c r="W53">
+        <v>0.2333236760401472</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1570731499923368</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1796654350771441</v>
+      </c>
+      <c r="C54">
+        <v>-1733.959357611991</v>
+      </c>
+      <c r="D54">
+        <v>2371.252642388009</v>
+      </c>
+      <c r="E54">
+        <v>4350.412</v>
+      </c>
+      <c r="F54">
+        <v>4577.612</v>
+      </c>
+      <c r="G54">
+        <v>472.4</v>
+      </c>
+      <c r="H54">
+        <v>8575.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>200.1</v>
+      </c>
+      <c r="K54">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L54">
+        <v>168.4</v>
+      </c>
+      <c r="M54">
+        <v>1093.1337456</v>
+      </c>
+      <c r="N54">
+        <v>-924.7337456000001</v>
+      </c>
+      <c r="O54">
+        <v>-135.0111268576</v>
+      </c>
+      <c r="P54">
+        <v>-789.7226187424001</v>
+      </c>
+      <c r="Q54">
+        <v>-758.0226187424</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1214215839513939</v>
+      </c>
+      <c r="T54">
+        <v>1.796121390247694</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02249166682390268</v>
+      </c>
+      <c r="W54">
+        <v>0.233428989962452</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1540525124924841</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1816654350771442</v>
+      </c>
+      <c r="C55">
+        <v>-1855.185967748307</v>
+      </c>
+      <c r="D55">
+        <v>2338.057032251693</v>
+      </c>
+      <c r="E55">
+        <v>4438.443</v>
+      </c>
+      <c r="F55">
+        <v>4665.643</v>
+      </c>
+      <c r="G55">
+        <v>472.4</v>
+      </c>
+      <c r="H55">
+        <v>8575.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>200.1</v>
+      </c>
+      <c r="K55">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L55">
+        <v>168.4</v>
+      </c>
+      <c r="M55">
+        <v>1114.1555484</v>
+      </c>
+      <c r="N55">
+        <v>-945.7555484000001</v>
+      </c>
+      <c r="O55">
+        <v>-138.0803100664</v>
+      </c>
+      <c r="P55">
+        <v>-807.6752383336001</v>
+      </c>
+      <c r="Q55">
+        <v>-775.9752383336001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1231794899929129</v>
+      </c>
+      <c r="T55">
+        <v>1.834336738976368</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02206729575175358</v>
+      </c>
+      <c r="W55">
+        <v>0.2335303297744813</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1511458613133807</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1836654350771441</v>
+      </c>
+      <c r="C56">
+        <v>-1975.495986287224</v>
+      </c>
+      <c r="D56">
+        <v>2305.778013712777</v>
+      </c>
+      <c r="E56">
+        <v>4526.474000000001</v>
+      </c>
+      <c r="F56">
+        <v>4753.674000000001</v>
+      </c>
+      <c r="G56">
+        <v>472.4</v>
+      </c>
+      <c r="H56">
+        <v>8575.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>200.1</v>
+      </c>
+      <c r="K56">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L56">
+        <v>168.4</v>
+      </c>
+      <c r="M56">
+        <v>1135.1773512</v>
+      </c>
+      <c r="N56">
+        <v>-966.7773512000002</v>
+      </c>
+      <c r="O56">
+        <v>-141.1494932752</v>
+      </c>
+      <c r="P56">
+        <v>-825.6278579248002</v>
+      </c>
+      <c r="Q56">
+        <v>-793.9278579248003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1250138267318893</v>
+      </c>
+      <c r="T56">
+        <v>1.874213624606289</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0216586421267211</v>
+      </c>
+      <c r="W56">
+        <v>0.233627916260139</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1483468638816514</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1856654350771442</v>
+      </c>
+      <c r="C57">
+        <v>-2094.926859409197</v>
+      </c>
+      <c r="D57">
+        <v>2274.378140590803</v>
+      </c>
+      <c r="E57">
+        <v>4614.505000000001</v>
+      </c>
+      <c r="F57">
+        <v>4841.705000000001</v>
+      </c>
+      <c r="G57">
+        <v>472.4</v>
+      </c>
+      <c r="H57">
+        <v>8575.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>200.1</v>
+      </c>
+      <c r="K57">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L57">
+        <v>168.4</v>
+      </c>
+      <c r="M57">
+        <v>1156.199154</v>
+      </c>
+      <c r="N57">
+        <v>-987.7991540000004</v>
+      </c>
+      <c r="O57">
+        <v>-144.218676484</v>
+      </c>
+      <c r="P57">
+        <v>-843.5804775160003</v>
+      </c>
+      <c r="Q57">
+        <v>-811.8804775160004</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1269296895481535</v>
+      </c>
+      <c r="T57">
+        <v>1.915862816264207</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02126484863350799</v>
+      </c>
+      <c r="W57">
+        <v>0.2337219541463183</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1456496481747123</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1876654350771441</v>
+      </c>
+      <c r="C58">
+        <v>-2213.514020944106</v>
+      </c>
+      <c r="D58">
+        <v>2243.821979055895</v>
+      </c>
+      <c r="E58">
+        <v>4702.536000000001</v>
+      </c>
+      <c r="F58">
+        <v>4929.736000000001</v>
+      </c>
+      <c r="G58">
+        <v>472.4</v>
+      </c>
+      <c r="H58">
+        <v>8575.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>200.1</v>
+      </c>
+      <c r="K58">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L58">
+        <v>168.4</v>
+      </c>
+      <c r="M58">
+        <v>1177.2209568</v>
+      </c>
+      <c r="N58">
+        <v>-1008.8209568</v>
+      </c>
+      <c r="O58">
+        <v>-147.2878596928</v>
+      </c>
+      <c r="P58">
+        <v>-861.5330971072003</v>
+      </c>
+      <c r="Q58">
+        <v>-829.8330971072003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1289326370378842</v>
+      </c>
+      <c r="T58">
+        <v>1.959405152997484</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02088511919362392</v>
+      </c>
+      <c r="W58">
+        <v>0.2338126335365626</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1430487616001638</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1896654350771441</v>
+      </c>
+      <c r="C59">
+        <v>-2331.291025758376</v>
+      </c>
+      <c r="D59">
+        <v>2214.075974241625</v>
+      </c>
+      <c r="E59">
+        <v>4790.567000000001</v>
+      </c>
+      <c r="F59">
+        <v>5017.767000000001</v>
+      </c>
+      <c r="G59">
+        <v>472.4</v>
+      </c>
+      <c r="H59">
+        <v>8575.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>200.1</v>
+      </c>
+      <c r="K59">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L59">
+        <v>168.4</v>
+      </c>
+      <c r="M59">
+        <v>1198.2427596</v>
+      </c>
+      <c r="N59">
+        <v>-1029.8427596</v>
+      </c>
+      <c r="O59">
+        <v>-150.3570429016</v>
+      </c>
+      <c r="P59">
+        <v>-879.4857166984001</v>
+      </c>
+      <c r="Q59">
+        <v>-847.7857166984002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1310287448759746</v>
+      </c>
+      <c r="T59">
+        <v>2.0049727146951</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02051871359373578</v>
+      </c>
+      <c r="W59">
+        <v>0.2339001311938159</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1405391342036698</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1916654350771441</v>
+      </c>
+      <c r="C60">
+        <v>-2448.289672671155</v>
+      </c>
+      <c r="D60">
+        <v>2185.108327328845</v>
+      </c>
+      <c r="E60">
+        <v>4878.598</v>
+      </c>
+      <c r="F60">
+        <v>5105.798</v>
+      </c>
+      <c r="G60">
+        <v>472.4</v>
+      </c>
+      <c r="H60">
+        <v>8575.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>200.1</v>
+      </c>
+      <c r="K60">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L60">
+        <v>168.4</v>
+      </c>
+      <c r="M60">
+        <v>1219.2645624</v>
+      </c>
+      <c r="N60">
+        <v>-1050.8645624</v>
+      </c>
+      <c r="O60">
+        <v>-153.4262261104</v>
+      </c>
+      <c r="P60">
+        <v>-897.4383362895999</v>
+      </c>
+      <c r="Q60">
+        <v>-865.7383362895998</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1332246673730216</v>
+      </c>
+      <c r="T60">
+        <v>2.052710160283078</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02016494266970586</v>
+      </c>
+      <c r="W60">
+        <v>0.2339846116904743</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1381160456829169</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1936654350771441</v>
+      </c>
+      <c r="C61">
+        <v>-2564.540117846126</v>
+      </c>
+      <c r="D61">
+        <v>2156.888882153874</v>
+      </c>
+      <c r="E61">
+        <v>4966.629</v>
+      </c>
+      <c r="F61">
+        <v>5193.829</v>
+      </c>
+      <c r="G61">
+        <v>472.4</v>
+      </c>
+      <c r="H61">
+        <v>8575.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>200.1</v>
+      </c>
+      <c r="K61">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L61">
+        <v>168.4</v>
+      </c>
+      <c r="M61">
+        <v>1240.2863652</v>
+      </c>
+      <c r="N61">
+        <v>-1071.8863652</v>
+      </c>
+      <c r="O61">
+        <v>-156.4954093192</v>
+      </c>
+      <c r="P61">
+        <v>-915.3909558808</v>
+      </c>
+      <c r="Q61">
+        <v>-883.6909558807999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1355277080406563</v>
+      </c>
+      <c r="T61">
+        <v>2.102776261753397</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.01982316398038881</v>
+      </c>
+      <c r="W61">
+        <v>0.2340662284414831</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1357750957560878</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1956654350771441</v>
+      </c>
+      <c r="C62">
+        <v>-2680.070979508999</v>
+      </c>
+      <c r="D62">
+        <v>2129.389020491001</v>
+      </c>
+      <c r="E62">
+        <v>5054.66</v>
+      </c>
+      <c r="F62">
+        <v>5281.86</v>
+      </c>
+      <c r="G62">
+        <v>472.4</v>
+      </c>
+      <c r="H62">
+        <v>8575.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>200.1</v>
+      </c>
+      <c r="K62">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L62">
+        <v>168.4</v>
+      </c>
+      <c r="M62">
+        <v>1261.308168</v>
+      </c>
+      <c r="N62">
+        <v>-1092.908168</v>
+      </c>
+      <c r="O62">
+        <v>-159.564592528</v>
+      </c>
+      <c r="P62">
+        <v>-933.3435754719999</v>
+      </c>
+      <c r="Q62">
+        <v>-901.6435754719998</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1379459007416727</v>
+      </c>
+      <c r="T62">
+        <v>2.155345668297231</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.01949277791404899</v>
+      </c>
+      <c r="W62">
+        <v>0.2341451246341251</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1335121774934863</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1976654350771441</v>
+      </c>
+      <c r="C63">
+        <v>-2794.909434755095</v>
+      </c>
+      <c r="D63">
+        <v>2102.581565244905</v>
+      </c>
+      <c r="E63">
+        <v>5142.691000000001</v>
+      </c>
+      <c r="F63">
+        <v>5369.891000000001</v>
+      </c>
+      <c r="G63">
+        <v>472.4</v>
+      </c>
+      <c r="H63">
+        <v>8575.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>200.1</v>
+      </c>
+      <c r="K63">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L63">
+        <v>168.4</v>
+      </c>
+      <c r="M63">
+        <v>1282.3299708</v>
+      </c>
+      <c r="N63">
+        <v>-1113.9299708</v>
+      </c>
+      <c r="O63">
+        <v>-162.6337757368</v>
+      </c>
+      <c r="P63">
+        <v>-951.2961950632001</v>
+      </c>
+      <c r="Q63">
+        <v>-919.5961950632002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1404881033247925</v>
+      </c>
+      <c r="T63">
+        <v>2.210610941843315</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.01917322417775311</v>
+      </c>
+      <c r="W63">
+        <v>0.2342214340663526</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1313234532722817</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1996654350771441</v>
+      </c>
+      <c r="C64">
+        <v>-2909.081309135432</v>
+      </c>
+      <c r="D64">
+        <v>2076.440690864569</v>
+      </c>
+      <c r="E64">
+        <v>5230.722000000001</v>
+      </c>
+      <c r="F64">
+        <v>5457.922</v>
+      </c>
+      <c r="G64">
+        <v>472.4</v>
+      </c>
+      <c r="H64">
+        <v>8575.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>200.1</v>
+      </c>
+      <c r="K64">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L64">
+        <v>168.4</v>
+      </c>
+      <c r="M64">
+        <v>1303.3517736</v>
+      </c>
+      <c r="N64">
+        <v>-1134.9517736</v>
+      </c>
+      <c r="O64">
+        <v>-165.7029589456</v>
+      </c>
+      <c r="P64">
+        <v>-969.2488146544</v>
+      </c>
+      <c r="Q64">
+        <v>-937.5488146544001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.143164106043866</v>
+      </c>
+      <c r="T64">
+        <v>2.268784913997086</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.01886397862649903</v>
+      </c>
+      <c r="W64">
+        <v>0.234295281903992</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1292053330582126</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2016654350771441</v>
+      </c>
+      <c r="C65">
+        <v>-3022.611159642061</v>
+      </c>
+      <c r="D65">
+        <v>2050.941840357939</v>
+      </c>
+      <c r="E65">
+        <v>5318.753000000001</v>
+      </c>
+      <c r="F65">
+        <v>5545.953</v>
+      </c>
+      <c r="G65">
+        <v>472.4</v>
+      </c>
+      <c r="H65">
+        <v>8575.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>200.1</v>
+      </c>
+      <c r="K65">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L65">
+        <v>168.4</v>
+      </c>
+      <c r="M65">
+        <v>1324.3735764</v>
+      </c>
+      <c r="N65">
+        <v>-1155.9735764</v>
+      </c>
+      <c r="O65">
+        <v>-168.7721421544</v>
+      </c>
+      <c r="P65">
+        <v>-987.2014342456001</v>
+      </c>
+      <c r="Q65">
+        <v>-955.5014342456002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.145984757558565</v>
+      </c>
+      <c r="T65">
+        <v>2.330103425186197</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.01856455039433237</v>
+      </c>
+      <c r="W65">
+        <v>0.2343667853658334</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1271544547557013</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2036654350771441</v>
+      </c>
+      <c r="C66">
+        <v>-3135.522351653179</v>
+      </c>
+      <c r="D66">
+        <v>2026.061648346821</v>
+      </c>
+      <c r="E66">
+        <v>5406.784000000001</v>
+      </c>
+      <c r="F66">
+        <v>5633.984</v>
+      </c>
+      <c r="G66">
+        <v>472.4</v>
+      </c>
+      <c r="H66">
+        <v>8575.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>200.1</v>
+      </c>
+      <c r="K66">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L66">
+        <v>168.4</v>
+      </c>
+      <c r="M66">
+        <v>1345.3953792</v>
+      </c>
+      <c r="N66">
+        <v>-1176.9953792</v>
+      </c>
+      <c r="O66">
+        <v>-171.8413253632</v>
+      </c>
+      <c r="P66">
+        <v>-1005.1540538368</v>
+      </c>
+      <c r="Q66">
+        <v>-973.4540538368001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1489621119351919</v>
+      </c>
+      <c r="T66">
+        <v>2.394828520330258</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.01827447929442093</v>
+      </c>
+      <c r="W66">
+        <v>0.2344360543444923</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1251676664001434</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2056654350771441</v>
+      </c>
+      <c r="C67">
+        <v>-3247.837130344795</v>
+      </c>
+      <c r="D67">
+        <v>2001.777869655205</v>
+      </c>
+      <c r="E67">
+        <v>5494.815000000001</v>
+      </c>
+      <c r="F67">
+        <v>5722.015</v>
+      </c>
+      <c r="G67">
+        <v>472.4</v>
+      </c>
+      <c r="H67">
+        <v>8575.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>200.1</v>
+      </c>
+      <c r="K67">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L67">
+        <v>168.4</v>
+      </c>
+      <c r="M67">
+        <v>1366.417182</v>
+      </c>
+      <c r="N67">
+        <v>-1198.017182</v>
+      </c>
+      <c r="O67">
+        <v>-174.910508572</v>
+      </c>
+      <c r="P67">
+        <v>-1023.106673428</v>
+      </c>
+      <c r="Q67">
+        <v>-991.406673428</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1521096008476259</v>
+      </c>
+      <c r="T67">
+        <v>2.463252192339694</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.01799333345912215</v>
+      </c>
+      <c r="W67">
+        <v>0.2345031919699616</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1232420099939874</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2076654350771441</v>
+      </c>
+      <c r="C68">
+        <v>-3359.576687027702</v>
+      </c>
+      <c r="D68">
+        <v>1978.069312972298</v>
+      </c>
+      <c r="E68">
+        <v>5582.846</v>
+      </c>
+      <c r="F68">
+        <v>5810.046</v>
+      </c>
+      <c r="G68">
+        <v>472.4</v>
+      </c>
+      <c r="H68">
+        <v>8575.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>200.1</v>
+      </c>
+      <c r="K68">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L68">
+        <v>168.4</v>
+      </c>
+      <c r="M68">
+        <v>1387.4389848</v>
+      </c>
+      <c r="N68">
+        <v>-1219.0389848</v>
+      </c>
+      <c r="O68">
+        <v>-177.9796917808</v>
+      </c>
+      <c r="P68">
+        <v>-1041.0592930192</v>
+      </c>
+      <c r="Q68">
+        <v>-1009.3592930192</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1554422361666737</v>
+      </c>
+      <c r="T68">
+        <v>2.535700786232038</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.01772070719459</v>
+      </c>
+      <c r="W68">
+        <v>0.2345682951219319</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1213747068122603</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2096654350771441</v>
+      </c>
+      <c r="C69">
+        <v>-3470.761220825562</v>
+      </c>
+      <c r="D69">
+        <v>1954.915779174438</v>
+      </c>
+      <c r="E69">
+        <v>5670.877</v>
+      </c>
+      <c r="F69">
+        <v>5898.077</v>
+      </c>
+      <c r="G69">
+        <v>472.4</v>
+      </c>
+      <c r="H69">
+        <v>8575.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>200.1</v>
+      </c>
+      <c r="K69">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L69">
+        <v>168.4</v>
+      </c>
+      <c r="M69">
+        <v>1408.4607876</v>
+      </c>
+      <c r="N69">
+        <v>-1240.0607876</v>
+      </c>
+      <c r="O69">
+        <v>-181.0488749896</v>
+      </c>
+      <c r="P69">
+        <v>-1059.0119126104</v>
+      </c>
+      <c r="Q69">
+        <v>-1027.3119126104</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1589768493838457</v>
+      </c>
+      <c r="T69">
+        <v>2.612540203996645</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.01745621902750656</v>
+      </c>
+      <c r="W69">
+        <v>0.2346314548962314</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1195631440240176</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2116654350771441</v>
+      </c>
+      <c r="C70">
+        <v>-3581.409996071401</v>
+      </c>
+      <c r="D70">
+        <v>1932.2980039286</v>
+      </c>
+      <c r="E70">
+        <v>5758.908000000001</v>
+      </c>
+      <c r="F70">
+        <v>5986.108000000001</v>
+      </c>
+      <c r="G70">
+        <v>472.4</v>
+      </c>
+      <c r="H70">
+        <v>8575.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>200.1</v>
+      </c>
+      <c r="K70">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L70">
+        <v>168.4</v>
+      </c>
+      <c r="M70">
+        <v>1429.4825904</v>
+      </c>
+      <c r="N70">
+        <v>-1261.0825904</v>
+      </c>
+      <c r="O70">
+        <v>-184.1180581984</v>
+      </c>
+      <c r="P70">
+        <v>-1076.9645322016</v>
+      </c>
+      <c r="Q70">
+        <v>-1045.2645322016</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1627323759270908</v>
+      </c>
+      <c r="T70">
+        <v>2.69418208537154</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.01719950992416087</v>
+      </c>
+      <c r="W70">
+        <v>0.2346927570301104</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1178048624942526</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2136654350771442</v>
+      </c>
+      <c r="C71">
+        <v>-3691.541395765329</v>
+      </c>
+      <c r="D71">
+        <v>1910.197604234672</v>
+      </c>
+      <c r="E71">
+        <v>5846.939000000001</v>
+      </c>
+      <c r="F71">
+        <v>6074.139000000001</v>
+      </c>
+      <c r="G71">
+        <v>472.4</v>
+      </c>
+      <c r="H71">
+        <v>8575.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>200.1</v>
+      </c>
+      <c r="K71">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L71">
+        <v>168.4</v>
+      </c>
+      <c r="M71">
+        <v>1450.5043932</v>
+      </c>
+      <c r="N71">
+        <v>-1282.1043932</v>
+      </c>
+      <c r="O71">
+        <v>-187.1872414072</v>
+      </c>
+      <c r="P71">
+        <v>-1094.9171517928</v>
+      </c>
+      <c r="Q71">
+        <v>-1063.2171517928</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1667301945053841</v>
+      </c>
+      <c r="T71">
+        <v>2.781091184899655</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.01695024166439043</v>
+      </c>
+      <c r="W71">
+        <v>0.2347522822905436</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1160975456465099</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2156654350771441</v>
+      </c>
+      <c r="C72">
+        <v>-3801.172971405236</v>
+      </c>
+      <c r="D72">
+        <v>1888.597028594765</v>
+      </c>
+      <c r="E72">
+        <v>5934.970000000001</v>
+      </c>
+      <c r="F72">
+        <v>6162.170000000001</v>
+      </c>
+      <c r="G72">
+        <v>472.4</v>
+      </c>
+      <c r="H72">
+        <v>8575.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>200.1</v>
+      </c>
+      <c r="K72">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L72">
+        <v>168.4</v>
+      </c>
+      <c r="M72">
+        <v>1471.526196</v>
+      </c>
+      <c r="N72">
+        <v>-1303.126196</v>
+      </c>
+      <c r="O72">
+        <v>-190.256424616</v>
+      </c>
+      <c r="P72">
+        <v>-1112.869771384</v>
+      </c>
+      <c r="Q72">
+        <v>-1081.169771384</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1709945343222302</v>
+      </c>
+      <c r="T72">
+        <v>2.87379422439631</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.01670809535489914</v>
+      </c>
+      <c r="W72">
+        <v>0.2348101068292501</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1144390092801312</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2176654350771441</v>
+      </c>
+      <c r="C73">
+        <v>-3910.321489474395</v>
+      </c>
+      <c r="D73">
+        <v>1867.479510525605</v>
+      </c>
+      <c r="E73">
+        <v>6023.001</v>
+      </c>
+      <c r="F73">
+        <v>6250.201</v>
+      </c>
+      <c r="G73">
+        <v>472.4</v>
+      </c>
+      <c r="H73">
+        <v>8575.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>200.1</v>
+      </c>
+      <c r="K73">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L73">
+        <v>168.4</v>
+      </c>
+      <c r="M73">
+        <v>1492.5479988</v>
+      </c>
+      <c r="N73">
+        <v>-1324.1479988</v>
+      </c>
+      <c r="O73">
+        <v>-193.3256078248</v>
+      </c>
+      <c r="P73">
+        <v>-1130.8223909752</v>
+      </c>
+      <c r="Q73">
+        <v>-1099.1223909752</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1755529665402381</v>
+      </c>
+      <c r="T73">
+        <v>2.972890576961699</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.01647277006821042</v>
+      </c>
+      <c r="W73">
+        <v>0.2348663025077113</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1128271922480166</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2196654350771441</v>
+      </c>
+      <c r="C74">
+        <v>-4019.002974844683</v>
+      </c>
+      <c r="D74">
+        <v>1846.829025155317</v>
+      </c>
+      <c r="E74">
+        <v>6111.032</v>
+      </c>
+      <c r="F74">
+        <v>6338.232</v>
+      </c>
+      <c r="G74">
+        <v>472.4</v>
+      </c>
+      <c r="H74">
+        <v>8575.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>200.1</v>
+      </c>
+      <c r="K74">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L74">
+        <v>168.4</v>
+      </c>
+      <c r="M74">
+        <v>1513.5698016</v>
+      </c>
+      <c r="N74">
+        <v>-1345.1698016</v>
+      </c>
+      <c r="O74">
+        <v>-196.3947910336</v>
+      </c>
+      <c r="P74">
+        <v>-1148.7750105664</v>
+      </c>
+      <c r="Q74">
+        <v>-1117.0750105664</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1804370010595324</v>
+      </c>
+      <c r="T74">
+        <v>3.079065240424617</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.01624398159504083</v>
+      </c>
+      <c r="W74">
+        <v>0.2349209371951043</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1112601479112386</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2216654350771441</v>
+      </c>
+      <c r="C75">
+        <v>-4127.232751331625</v>
+      </c>
+      <c r="D75">
+        <v>1826.630248668375</v>
+      </c>
+      <c r="E75">
+        <v>6199.063</v>
+      </c>
+      <c r="F75">
+        <v>6426.263</v>
+      </c>
+      <c r="G75">
+        <v>472.4</v>
+      </c>
+      <c r="H75">
+        <v>8575.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>200.1</v>
+      </c>
+      <c r="K75">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L75">
+        <v>168.4</v>
+      </c>
+      <c r="M75">
+        <v>1534.5916044</v>
+      </c>
+      <c r="N75">
+        <v>-1366.1916044</v>
+      </c>
+      <c r="O75">
+        <v>-199.4639742424</v>
+      </c>
+      <c r="P75">
+        <v>-1166.7276301576</v>
+      </c>
+      <c r="Q75">
+        <v>-1135.0276301576</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1856828159135891</v>
+      </c>
+      <c r="T75">
+        <v>3.193104693773677</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.01602146129921835</v>
+      </c>
+      <c r="W75">
+        <v>0.2349740750417467</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1097360362960161</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2236654350771441</v>
+      </c>
+      <c r="C76">
+        <v>-4235.025479616916</v>
+      </c>
+      <c r="D76">
+        <v>1806.868520383084</v>
+      </c>
+      <c r="E76">
+        <v>6287.094</v>
+      </c>
+      <c r="F76">
+        <v>6514.294</v>
+      </c>
+      <c r="G76">
+        <v>472.4</v>
+      </c>
+      <c r="H76">
+        <v>8575.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>200.1</v>
+      </c>
+      <c r="K76">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L76">
+        <v>168.4</v>
+      </c>
+      <c r="M76">
+        <v>1555.6134072</v>
+      </c>
+      <c r="N76">
+        <v>-1387.2134072</v>
+      </c>
+      <c r="O76">
+        <v>-202.5331574512</v>
+      </c>
+      <c r="P76">
+        <v>-1184.6802497488</v>
+      </c>
+      <c r="Q76">
+        <v>-1152.9802497488</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1913321549871887</v>
+      </c>
+      <c r="T76">
+        <v>3.315916412764972</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.01580495506544513</v>
+      </c>
+      <c r="W76">
+        <v>0.2350257767303717</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1082531168866105</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2256654350771441</v>
+      </c>
+      <c r="C77">
+        <v>-4342.39519273566</v>
+      </c>
+      <c r="D77">
+        <v>1787.52980726434</v>
+      </c>
+      <c r="E77">
+        <v>6375.125000000001</v>
+      </c>
+      <c r="F77">
+        <v>6602.325000000001</v>
+      </c>
+      <c r="G77">
+        <v>472.4</v>
+      </c>
+      <c r="H77">
+        <v>8575.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>200.1</v>
+      </c>
+      <c r="K77">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L77">
+        <v>168.4</v>
+      </c>
+      <c r="M77">
+        <v>1576.63521</v>
+      </c>
+      <c r="N77">
+        <v>-1408.23521</v>
+      </c>
+      <c r="O77">
+        <v>-205.60234066</v>
+      </c>
+      <c r="P77">
+        <v>-1202.63286934</v>
+      </c>
+      <c r="Q77">
+        <v>-1170.93286934</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1974334411866763</v>
+      </c>
+      <c r="T77">
+        <v>3.448553069275571</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.0155942223312392</v>
+      </c>
+      <c r="W77">
+        <v>0.2350760997073001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1068097419947891</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2276654350771441</v>
+      </c>
+      <c r="C78">
+        <v>-4449.355329308843</v>
+      </c>
+      <c r="D78">
+        <v>1768.600670691158</v>
+      </c>
+      <c r="E78">
+        <v>6463.156000000001</v>
+      </c>
+      <c r="F78">
+        <v>6690.356000000001</v>
+      </c>
+      <c r="G78">
+        <v>472.4</v>
+      </c>
+      <c r="H78">
+        <v>8575.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>200.1</v>
+      </c>
+      <c r="K78">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L78">
+        <v>168.4</v>
+      </c>
+      <c r="M78">
+        <v>1597.6570128</v>
+      </c>
+      <c r="N78">
+        <v>-1429.2570128</v>
+      </c>
+      <c r="O78">
+        <v>-208.6715238688</v>
+      </c>
+      <c r="P78">
+        <v>-1220.5854889312</v>
+      </c>
+      <c r="Q78">
+        <v>-1188.8854889312</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2040431679027878</v>
+      </c>
+      <c r="T78">
+        <v>3.592242780495387</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01538903519530184</v>
+      </c>
+      <c r="W78">
+        <v>0.2351250983953619</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1054043506527523</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2296654350771441</v>
+      </c>
+      <c r="C79">
+        <v>-4555.91876468643</v>
+      </c>
+      <c r="D79">
+        <v>1750.06823531357</v>
+      </c>
+      <c r="E79">
+        <v>6551.187000000001</v>
+      </c>
+      <c r="F79">
+        <v>6778.387000000001</v>
+      </c>
+      <c r="G79">
+        <v>472.4</v>
+      </c>
+      <c r="H79">
+        <v>8575.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>200.1</v>
+      </c>
+      <c r="K79">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L79">
+        <v>168.4</v>
+      </c>
+      <c r="M79">
+        <v>1618.6788156</v>
+      </c>
+      <c r="N79">
+        <v>-1450.2788156</v>
+      </c>
+      <c r="O79">
+        <v>-211.7407070776</v>
+      </c>
+      <c r="P79">
+        <v>-1238.5381085224</v>
+      </c>
+      <c r="Q79">
+        <v>-1206.8381085224</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2112276534637786</v>
+      </c>
+      <c r="T79">
+        <v>3.748427249212577</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.01518917759536285</v>
+      </c>
+      <c r="W79">
+        <v>0.2351728243902274</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1040354629819374</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2316654350771441</v>
+      </c>
+      <c r="C80">
+        <v>-4662.097840152763</v>
+      </c>
+      <c r="D80">
+        <v>1731.920159847238</v>
+      </c>
+      <c r="E80">
+        <v>6639.218000000001</v>
+      </c>
+      <c r="F80">
+        <v>6866.418000000001</v>
+      </c>
+      <c r="G80">
+        <v>472.4</v>
+      </c>
+      <c r="H80">
+        <v>8575.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>200.1</v>
+      </c>
+      <c r="K80">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L80">
+        <v>168.4</v>
+      </c>
+      <c r="M80">
+        <v>1639.7006184</v>
+      </c>
+      <c r="N80">
+        <v>-1471.3006184</v>
+      </c>
+      <c r="O80">
+        <v>-214.8098902864</v>
+      </c>
+      <c r="P80">
+        <v>-1256.4907281136</v>
+      </c>
+      <c r="Q80">
+        <v>-1224.7907281136</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2190652740757685</v>
+      </c>
+      <c r="T80">
+        <v>3.918810305994967</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01499444454926846</v>
+      </c>
+      <c r="W80">
+        <v>0.2352193266416347</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1027016749949895</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2336654350771442</v>
+      </c>
+      <c r="C81">
+        <v>-4767.904390333446</v>
+      </c>
+      <c r="D81">
+        <v>1714.144609666555</v>
+      </c>
+      <c r="E81">
+        <v>6727.249000000001</v>
+      </c>
+      <c r="F81">
+        <v>6954.449000000001</v>
+      </c>
+      <c r="G81">
+        <v>472.4</v>
+      </c>
+      <c r="H81">
+        <v>8575.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>200.1</v>
+      </c>
+      <c r="K81">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L81">
+        <v>168.4</v>
+      </c>
+      <c r="M81">
+        <v>1660.7224212</v>
+      </c>
+      <c r="N81">
+        <v>-1492.3224212</v>
+      </c>
+      <c r="O81">
+        <v>-217.8790734952</v>
+      </c>
+      <c r="P81">
+        <v>-1274.4433477048</v>
+      </c>
+      <c r="Q81">
+        <v>-1242.7433477048</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2276493347460432</v>
+      </c>
+      <c r="T81">
+        <v>4.105420320566157</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0148046414537081</v>
+      </c>
+      <c r="W81">
+        <v>0.2352646516208545</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1014016537925213</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2356654350771442</v>
+      </c>
+      <c r="C82">
+        <v>-4873.349768931647</v>
+      </c>
+      <c r="D82">
+        <v>1696.730231068353</v>
+      </c>
+      <c r="E82">
+        <v>6815.280000000001</v>
+      </c>
+      <c r="F82">
+        <v>7042.48</v>
+      </c>
+      <c r="G82">
+        <v>472.4</v>
+      </c>
+      <c r="H82">
+        <v>8575.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>200.1</v>
+      </c>
+      <c r="K82">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L82">
+        <v>168.4</v>
+      </c>
+      <c r="M82">
+        <v>1681.744224</v>
+      </c>
+      <c r="N82">
+        <v>-1513.344224</v>
+      </c>
+      <c r="O82">
+        <v>-220.948256704</v>
+      </c>
+      <c r="P82">
+        <v>-1292.395967296</v>
+      </c>
+      <c r="Q82">
+        <v>-1260.695967296</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2370918014833454</v>
+      </c>
+      <c r="T82">
+        <v>4.310691336594465</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.01461958343553674</v>
+      </c>
+      <c r="W82">
+        <v>0.2353088434755939</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1001341331201148</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2376654350771442</v>
+      </c>
+      <c r="C83">
+        <v>-4978.444872911408</v>
+      </c>
+      <c r="D83">
+        <v>1679.666127088593</v>
+      </c>
+      <c r="E83">
+        <v>6903.311000000001</v>
+      </c>
+      <c r="F83">
+        <v>7130.511</v>
+      </c>
+      <c r="G83">
+        <v>472.4</v>
+      </c>
+      <c r="H83">
+        <v>8575.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>200.1</v>
+      </c>
+      <c r="K83">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L83">
+        <v>168.4</v>
+      </c>
+      <c r="M83">
+        <v>1702.7660268</v>
+      </c>
+      <c r="N83">
+        <v>-1534.3660268</v>
+      </c>
+      <c r="O83">
+        <v>-224.0174399128</v>
+      </c>
+      <c r="P83">
+        <v>-1310.3485868872</v>
+      </c>
+      <c r="Q83">
+        <v>-1278.6485868872</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.247528212087732</v>
+      </c>
+      <c r="T83">
+        <v>4.537569827994173</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0144390947511474</v>
+      </c>
+      <c r="W83">
+        <v>0.235351944173426</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.09889790925443431</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2396654350771441</v>
+      </c>
+      <c r="C84">
+        <v>-5083.200165236205</v>
+      </c>
+      <c r="D84">
+        <v>1662.941834763797</v>
+      </c>
+      <c r="E84">
+        <v>6991.342000000001</v>
+      </c>
+      <c r="F84">
+        <v>7218.542000000001</v>
+      </c>
+      <c r="G84">
+        <v>472.4</v>
+      </c>
+      <c r="H84">
+        <v>8575.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>200.1</v>
+      </c>
+      <c r="K84">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L84">
+        <v>168.4</v>
+      </c>
+      <c r="M84">
+        <v>1723.7878296</v>
+      </c>
+      <c r="N84">
+        <v>-1555.3878296</v>
+      </c>
+      <c r="O84">
+        <v>-227.0866231216</v>
+      </c>
+      <c r="P84">
+        <v>-1328.3012064784</v>
+      </c>
+      <c r="Q84">
+        <v>-1296.6012064784</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2591242238703838</v>
+      </c>
+      <c r="T84">
+        <v>4.789657040660517</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.01426300822979194</v>
+      </c>
+      <c r="W84">
+        <v>0.2353939936347257</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.09769183719035579</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2416654350771441</v>
+      </c>
+      <c r="C85">
+        <v>-5187.625696262461</v>
+      </c>
+      <c r="D85">
+        <v>1646.54730373754</v>
+      </c>
+      <c r="E85">
+        <v>7079.373000000001</v>
+      </c>
+      <c r="F85">
+        <v>7306.573000000001</v>
+      </c>
+      <c r="G85">
+        <v>472.4</v>
+      </c>
+      <c r="H85">
+        <v>8575.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>200.1</v>
+      </c>
+      <c r="K85">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L85">
+        <v>168.4</v>
+      </c>
+      <c r="M85">
+        <v>1744.8096324</v>
+      </c>
+      <c r="N85">
+        <v>-1576.4096324</v>
+      </c>
+      <c r="O85">
+        <v>-230.1558063304</v>
+      </c>
+      <c r="P85">
+        <v>-1346.2538260696</v>
+      </c>
+      <c r="Q85">
+        <v>-1314.5538260696</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2720844723333475</v>
+      </c>
+      <c r="T85">
+        <v>5.071401572464077</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01409116475714385</v>
+      </c>
+      <c r="W85">
+        <v>0.235435029855994</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.09651482710372505</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2436654350771441</v>
+      </c>
+      <c r="C86">
+        <v>-5291.731123879961</v>
+      </c>
+      <c r="D86">
+        <v>1630.472876120039</v>
+      </c>
+      <c r="E86">
+        <v>7167.404</v>
+      </c>
+      <c r="F86">
+        <v>7394.604</v>
+      </c>
+      <c r="G86">
+        <v>472.4</v>
+      </c>
+      <c r="H86">
+        <v>8575.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>200.1</v>
+      </c>
+      <c r="K86">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L86">
+        <v>168.4</v>
+      </c>
+      <c r="M86">
+        <v>1765.8314352</v>
+      </c>
+      <c r="N86">
+        <v>-1597.4314352</v>
+      </c>
+      <c r="O86">
+        <v>-233.2249895392</v>
+      </c>
+      <c r="P86">
+        <v>-1364.2064456608</v>
+      </c>
+      <c r="Q86">
+        <v>-1332.5064456608</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2866647518541816</v>
+      </c>
+      <c r="T86">
+        <v>5.388364170743079</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01392341279574928</v>
+      </c>
+      <c r="W86">
+        <v>0.2354750890243751</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.09536584106677592</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2456654350771441</v>
+      </c>
+      <c r="C87">
+        <v>-5395.525732483902</v>
+      </c>
+      <c r="D87">
+        <v>1614.709267516098</v>
+      </c>
+      <c r="E87">
+        <v>7255.435</v>
+      </c>
+      <c r="F87">
+        <v>7482.635</v>
+      </c>
+      <c r="G87">
+        <v>472.4</v>
+      </c>
+      <c r="H87">
+        <v>8575.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>200.1</v>
+      </c>
+      <c r="K87">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L87">
+        <v>168.4</v>
+      </c>
+      <c r="M87">
+        <v>1786.853238</v>
+      </c>
+      <c r="N87">
+        <v>-1618.453238</v>
+      </c>
+      <c r="O87">
+        <v>-236.294172748</v>
+      </c>
+      <c r="P87">
+        <v>-1382.159065252</v>
+      </c>
+      <c r="Q87">
+        <v>-1350.459065252</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3031890686444604</v>
+      </c>
+      <c r="T87">
+        <v>5.747588448792618</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0137596079393287</v>
+      </c>
+      <c r="W87">
+        <v>0.2355142056240883</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09424388999540212</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2476654350771441</v>
+      </c>
+      <c r="C88">
+        <v>-5499.018450856976</v>
+      </c>
+      <c r="D88">
+        <v>1599.247549143025</v>
+      </c>
+      <c r="E88">
+        <v>7343.466</v>
+      </c>
+      <c r="F88">
+        <v>7570.666</v>
+      </c>
+      <c r="G88">
+        <v>472.4</v>
+      </c>
+      <c r="H88">
+        <v>8575.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>200.1</v>
+      </c>
+      <c r="K88">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L88">
+        <v>168.4</v>
+      </c>
+      <c r="M88">
+        <v>1807.8750408</v>
+      </c>
+      <c r="N88">
+        <v>-1639.4750408</v>
+      </c>
+      <c r="O88">
+        <v>-239.3633559568</v>
+      </c>
+      <c r="P88">
+        <v>-1400.1116848432</v>
+      </c>
+      <c r="Q88">
+        <v>-1368.4116848432</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3220740021190648</v>
+      </c>
+      <c r="T88">
+        <v>6.158130480849234</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01359961249817372</v>
+      </c>
+      <c r="W88">
+        <v>0.2355524125354361</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09314803080940903</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2496654350771441</v>
+      </c>
+      <c r="C89">
+        <v>-5602.217869033788</v>
+      </c>
+      <c r="D89">
+        <v>1584.079130966212</v>
+      </c>
+      <c r="E89">
+        <v>7431.497</v>
+      </c>
+      <c r="F89">
+        <v>7658.697</v>
+      </c>
+      <c r="G89">
+        <v>472.4</v>
+      </c>
+      <c r="H89">
+        <v>8575.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>200.1</v>
+      </c>
+      <c r="K89">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L89">
+        <v>168.4</v>
+      </c>
+      <c r="M89">
+        <v>1828.8968436</v>
+      </c>
+      <c r="N89">
+        <v>-1660.4968436</v>
+      </c>
+      <c r="O89">
+        <v>-242.4325391656</v>
+      </c>
+      <c r="P89">
+        <v>-1418.0643044344</v>
+      </c>
+      <c r="Q89">
+        <v>-1386.3643044344</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3438643099743774</v>
+      </c>
+      <c r="T89">
+        <v>6.631832825529943</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01344329511313724</v>
+      </c>
+      <c r="W89">
+        <v>0.2355897411269828</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09207736378861131</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2516654350771441</v>
+      </c>
+      <c r="C90">
+        <v>-5705.132254214592</v>
+      </c>
+      <c r="D90">
+        <v>1569.195745785409</v>
+      </c>
+      <c r="E90">
+        <v>7519.528</v>
+      </c>
+      <c r="F90">
+        <v>7746.728</v>
+      </c>
+      <c r="G90">
+        <v>472.4</v>
+      </c>
+      <c r="H90">
+        <v>8575.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>200.1</v>
+      </c>
+      <c r="K90">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L90">
+        <v>168.4</v>
+      </c>
+      <c r="M90">
+        <v>1849.9186464</v>
+      </c>
+      <c r="N90">
+        <v>-1681.5186464</v>
+      </c>
+      <c r="O90">
+        <v>-245.5017223744</v>
+      </c>
+      <c r="P90">
+        <v>-1436.0169240256</v>
+      </c>
+      <c r="Q90">
+        <v>-1404.3169240256</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3692863358055756</v>
+      </c>
+      <c r="T90">
+        <v>7.184485560990774</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.0132905303959425</v>
+      </c>
+      <c r="W90">
+        <v>0.2356262213414489</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09103103010919522</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2536654350771442</v>
+      </c>
+      <c r="C91">
+        <v>-5807.769565790226</v>
+      </c>
+      <c r="D91">
+        <v>1554.589434209774</v>
+      </c>
+      <c r="E91">
+        <v>7607.559</v>
+      </c>
+      <c r="F91">
+        <v>7834.759</v>
+      </c>
+      <c r="G91">
+        <v>472.4</v>
+      </c>
+      <c r="H91">
+        <v>8575.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>200.1</v>
+      </c>
+      <c r="K91">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L91">
+        <v>168.4</v>
+      </c>
+      <c r="M91">
+        <v>1870.9404492</v>
+      </c>
+      <c r="N91">
+        <v>-1702.5404492</v>
+      </c>
+      <c r="O91">
+        <v>-248.5709055832</v>
+      </c>
+      <c r="P91">
+        <v>-1453.9695436168</v>
+      </c>
+      <c r="Q91">
+        <v>-1422.2695436168</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.399330548151537</v>
+      </c>
+      <c r="T91">
+        <v>7.837620611989935</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01314119859374089</v>
+      </c>
+      <c r="W91">
+        <v>0.2356618817758147</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09000820954617061</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2556654350771442</v>
+      </c>
+      <c r="C92">
+        <v>-5910.137469535692</v>
+      </c>
+      <c r="D92">
+        <v>1540.252530464309</v>
+      </c>
+      <c r="E92">
+        <v>7695.590000000001</v>
+      </c>
+      <c r="F92">
+        <v>7922.790000000001</v>
+      </c>
+      <c r="G92">
+        <v>472.4</v>
+      </c>
+      <c r="H92">
+        <v>8575.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>200.1</v>
+      </c>
+      <c r="K92">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L92">
+        <v>168.4</v>
+      </c>
+      <c r="M92">
+        <v>1891.962252</v>
+      </c>
+      <c r="N92">
+        <v>-1723.562252</v>
+      </c>
+      <c r="O92">
+        <v>-251.640088792</v>
+      </c>
+      <c r="P92">
+        <v>-1471.922163208</v>
+      </c>
+      <c r="Q92">
+        <v>-1440.222163208</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4353836029666907</v>
+      </c>
+      <c r="T92">
+        <v>8.621382673188929</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01299518527603266</v>
+      </c>
+      <c r="W92">
+        <v>0.2356967497560834</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.08900811832899092</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2576654350771441</v>
+      </c>
+      <c r="C93">
+        <v>-6012.24335102551</v>
+      </c>
+      <c r="D93">
+        <v>1526.17764897449</v>
+      </c>
+      <c r="E93">
+        <v>7783.621000000001</v>
+      </c>
+      <c r="F93">
+        <v>8010.821000000001</v>
+      </c>
+      <c r="G93">
+        <v>472.4</v>
+      </c>
+      <c r="H93">
+        <v>8575.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>200.1</v>
+      </c>
+      <c r="K93">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L93">
+        <v>168.4</v>
+      </c>
+      <c r="M93">
+        <v>1912.9840548</v>
+      </c>
+      <c r="N93">
+        <v>-1744.5840548</v>
+      </c>
+      <c r="O93">
+        <v>-254.7092720008</v>
+      </c>
+      <c r="P93">
+        <v>-1489.8747827992</v>
+      </c>
+      <c r="Q93">
+        <v>-1458.1747827992</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4794484477407676</v>
+      </c>
+      <c r="T93">
+        <v>9.579314081321034</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0128523810422301</v>
+      </c>
+      <c r="W93">
+        <v>0.2357308514071155</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.08803000713856246</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2596654350771441</v>
+      </c>
+      <c r="C94">
+        <v>-6114.094328320206</v>
+      </c>
+      <c r="D94">
+        <v>1512.357671679795</v>
+      </c>
+      <c r="E94">
+        <v>7871.652000000001</v>
+      </c>
+      <c r="F94">
+        <v>8098.852000000001</v>
+      </c>
+      <c r="G94">
+        <v>472.4</v>
+      </c>
+      <c r="H94">
+        <v>8575.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>200.1</v>
+      </c>
+      <c r="K94">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L94">
+        <v>168.4</v>
+      </c>
+      <c r="M94">
+        <v>1934.0058576</v>
+      </c>
+      <c r="N94">
+        <v>-1765.6058576</v>
+      </c>
+      <c r="O94">
+        <v>-257.7784552096</v>
+      </c>
+      <c r="P94">
+        <v>-1507.8274023904</v>
+      </c>
+      <c r="Q94">
+        <v>-1476.1274023904</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.5345295037083636</v>
+      </c>
+      <c r="T94">
+        <v>10.77672834148617</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01271268124829282</v>
+      </c>
+      <c r="W94">
+        <v>0.2357642117179077</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.08707315923488235</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2616654350771441</v>
+      </c>
+      <c r="C95">
+        <v>-6215.697263969682</v>
+      </c>
+      <c r="D95">
+        <v>1498.785736030318</v>
+      </c>
+      <c r="E95">
+        <v>7959.683000000001</v>
+      </c>
+      <c r="F95">
+        <v>8186.883000000001</v>
+      </c>
+      <c r="G95">
+        <v>472.4</v>
+      </c>
+      <c r="H95">
+        <v>8575.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>200.1</v>
+      </c>
+      <c r="K95">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L95">
+        <v>168.4</v>
+      </c>
+      <c r="M95">
+        <v>1955.0276604</v>
+      </c>
+      <c r="N95">
+        <v>-1786.6276604</v>
+      </c>
+      <c r="O95">
+        <v>-260.8476384184</v>
+      </c>
+      <c r="P95">
+        <v>-1525.7800219816</v>
+      </c>
+      <c r="Q95">
+        <v>-1494.0800219816</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6053480042381298</v>
+      </c>
+      <c r="T95">
+        <v>12.31626096169848</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01257598575099935</v>
+      </c>
+      <c r="W95">
+        <v>0.2357968546026614</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.08613688870547509</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2636654350771441</v>
+      </c>
+      <c r="C96">
+        <v>-6317.058776376056</v>
+      </c>
+      <c r="D96">
+        <v>1485.455223623944</v>
+      </c>
+      <c r="E96">
+        <v>8047.714000000001</v>
+      </c>
+      <c r="F96">
+        <v>8274.914000000001</v>
+      </c>
+      <c r="G96">
+        <v>472.4</v>
+      </c>
+      <c r="H96">
+        <v>8575.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>200.1</v>
+      </c>
+      <c r="K96">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L96">
+        <v>168.4</v>
+      </c>
+      <c r="M96">
+        <v>1976.0494632</v>
+      </c>
+      <c r="N96">
+        <v>-1807.6494632</v>
+      </c>
+      <c r="O96">
+        <v>-263.9168216272</v>
+      </c>
+      <c r="P96">
+        <v>-1543.7326415728</v>
+      </c>
+      <c r="Q96">
+        <v>-1512.0326415728</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.6997726716111519</v>
+      </c>
+      <c r="T96">
+        <v>14.36897112198156</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01244219866854191</v>
+      </c>
+      <c r="W96">
+        <v>0.2358288029579522</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.08522053882562952</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2656654350771442</v>
+      </c>
+      <c r="C97">
+        <v>-6418.185250555443</v>
+      </c>
+      <c r="D97">
+        <v>1472.359749444558</v>
+      </c>
+      <c r="E97">
+        <v>8135.745000000002</v>
+      </c>
+      <c r="F97">
+        <v>8362.945000000002</v>
+      </c>
+      <c r="G97">
+        <v>472.4</v>
+      </c>
+      <c r="H97">
+        <v>8575.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>200.1</v>
+      </c>
+      <c r="K97">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L97">
+        <v>168.4</v>
+      </c>
+      <c r="M97">
+        <v>1997.071266</v>
+      </c>
+      <c r="N97">
+        <v>-1828.671266</v>
+      </c>
+      <c r="O97">
+        <v>-266.986004836</v>
+      </c>
+      <c r="P97">
+        <v>-1561.685261164</v>
+      </c>
+      <c r="Q97">
+        <v>-1529.985261164</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.8319672059333825</v>
+      </c>
+      <c r="T97">
+        <v>17.24276534637788</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01231122815624147</v>
+      </c>
+      <c r="W97">
+        <v>0.2358600787162896</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08432348052220184</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2676654350771441</v>
+      </c>
+      <c r="C98">
+        <v>-6519.082848335473</v>
+      </c>
+      <c r="D98">
+        <v>1459.493151664528</v>
+      </c>
+      <c r="E98">
+        <v>8223.776</v>
+      </c>
+      <c r="F98">
+        <v>8450.976000000001</v>
+      </c>
+      <c r="G98">
+        <v>472.4</v>
+      </c>
+      <c r="H98">
+        <v>8575.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>200.1</v>
+      </c>
+      <c r="K98">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L98">
+        <v>168.4</v>
+      </c>
+      <c r="M98">
+        <v>2018.0930688</v>
+      </c>
+      <c r="N98">
+        <v>-1849.6930688</v>
+      </c>
+      <c r="O98">
+        <v>-270.0551880448</v>
+      </c>
+      <c r="P98">
+        <v>-1579.6378807552</v>
+      </c>
+      <c r="Q98">
+        <v>-1547.9378807552</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.030259007416726</v>
+      </c>
+      <c r="T98">
+        <v>21.5534566829723</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01218298619628062</v>
+      </c>
+      <c r="W98">
+        <v>0.2358907028963282</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.08344511093342899</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2696654350771441</v>
+      </c>
+      <c r="C99">
+        <v>-6619.757518022766</v>
+      </c>
+      <c r="D99">
+        <v>1446.849481977234</v>
+      </c>
+      <c r="E99">
+        <v>8311.806999999999</v>
+      </c>
+      <c r="F99">
+        <v>8539.007</v>
+      </c>
+      <c r="G99">
+        <v>472.4</v>
+      </c>
+      <c r="H99">
+        <v>8575.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>200.1</v>
+      </c>
+      <c r="K99">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L99">
+        <v>168.4</v>
+      </c>
+      <c r="M99">
+        <v>2039.1148716</v>
+      </c>
+      <c r="N99">
+        <v>-1870.7148716</v>
+      </c>
+      <c r="O99">
+        <v>-273.1243712536</v>
+      </c>
+      <c r="P99">
+        <v>-1597.5905003464</v>
+      </c>
+      <c r="Q99">
+        <v>-1565.8905003464</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.360745343222301</v>
+      </c>
+      <c r="T99">
+        <v>28.73794224396307</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01205738840044268</v>
+      </c>
+      <c r="W99">
+        <v>0.2359206956499743</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.08258485205782662</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2716654350771441</v>
+      </c>
+      <c r="C100">
+        <v>-6720.215003572224</v>
+      </c>
+      <c r="D100">
+        <v>1434.422996427776</v>
+      </c>
+      <c r="E100">
+        <v>8399.838</v>
+      </c>
+      <c r="F100">
+        <v>8627.038</v>
+      </c>
+      <c r="G100">
+        <v>472.4</v>
+      </c>
+      <c r="H100">
+        <v>8575.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>200.1</v>
+      </c>
+      <c r="K100">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L100">
+        <v>168.4</v>
+      </c>
+      <c r="M100">
+        <v>2060.1366744</v>
+      </c>
+      <c r="N100">
+        <v>-1891.7366744</v>
+      </c>
+      <c r="O100">
+        <v>-276.1935544624</v>
+      </c>
+      <c r="P100">
+        <v>-1615.5431199376</v>
+      </c>
+      <c r="Q100">
+        <v>-1583.8431199376</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.021718014833452</v>
+      </c>
+      <c r="T100">
+        <v>43.1069133659446</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01193435382492796</v>
+      </c>
+      <c r="W100">
+        <v>0.2359500763066072</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08174214948580794</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2736654350771441</v>
+      </c>
+      <c r="C101">
+        <v>-6820.460853287821</v>
+      </c>
+      <c r="D101">
+        <v>1422.208146712179</v>
+      </c>
+      <c r="E101">
+        <v>8487.868999999999</v>
+      </c>
+      <c r="F101">
+        <v>8715.069</v>
+      </c>
+      <c r="G101">
+        <v>472.4</v>
+      </c>
+      <c r="H101">
+        <v>8575.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>200.1</v>
+      </c>
+      <c r="K101">
+        <v>31.69999999999999</v>
+      </c>
+      <c r="L101">
+        <v>168.4</v>
+      </c>
+      <c r="M101">
+        <v>2081.1584772</v>
+      </c>
+      <c r="N101">
+        <v>-1912.7584772</v>
+      </c>
+      <c r="O101">
+        <v>-279.2627376712</v>
+      </c>
+      <c r="P101">
+        <v>-1633.4957395288</v>
+      </c>
+      <c r="Q101">
+        <v>-1601.7957395288</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.004636029666903</v>
+      </c>
+      <c r="T101">
+        <v>86.2138267318892</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01181380479639333</v>
+      </c>
+      <c r="W101">
+        <v>0.2359788634146213</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08091647120817358</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_shoe.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_shoe.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08357235990870196</v>
+        <v>0.08348877426323525</v>
       </c>
       <c r="C2">
-        <v>17850.20267888697</v>
+        <v>17709.15810193691</v>
       </c>
       <c r="D2">
-        <v>16963.50267888697</v>
+        <v>17001.12410193691</v>
       </c>
       <c r="E2">
-        <v>-333.6</v>
+        <v>-154.934</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>178.666</v>
       </c>
       <c r="G2">
         <v>886.7</v>
@@ -1439,28 +1439,28 @@
         <v>235.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>8.9868998</v>
       </c>
       <c r="N2">
-        <v>235.3</v>
+        <v>226.3131002</v>
       </c>
       <c r="O2">
-        <v>34.3538</v>
+        <v>33.0417126292</v>
       </c>
       <c r="P2">
-        <v>200.9462</v>
+        <v>193.2713875708</v>
       </c>
       <c r="Q2">
-        <v>269.5462</v>
+        <v>261.8713875708</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08357235990870196</v>
+        <v>0.08389819420528814</v>
       </c>
       <c r="T2">
-        <v>0.8723408754896529</v>
+        <v>0.8798659169812504</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>26.18255518994437</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08348877426323525</v>
+        <v>0.08340518861776855</v>
       </c>
       <c r="C3">
-        <v>17709.15810193691</v>
+        <v>17568.28076844684</v>
       </c>
       <c r="D3">
-        <v>17001.12410193691</v>
+        <v>17038.91276844684</v>
       </c>
       <c r="E3">
-        <v>-154.934</v>
+        <v>23.73199999999997</v>
       </c>
       <c r="F3">
-        <v>178.666</v>
+        <v>357.332</v>
       </c>
       <c r="G3">
         <v>886.7</v>
@@ -1521,28 +1521,28 @@
         <v>235.3</v>
       </c>
       <c r="M3">
-        <v>8.9868998</v>
+        <v>17.9737996</v>
       </c>
       <c r="N3">
-        <v>226.3131002</v>
+        <v>217.3262004</v>
       </c>
       <c r="O3">
-        <v>33.0417126292</v>
+        <v>31.7296252584</v>
       </c>
       <c r="P3">
-        <v>193.2713875708</v>
+        <v>185.5965751416</v>
       </c>
       <c r="Q3">
-        <v>261.8713875708</v>
+        <v>254.1965751416</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08389819420528814</v>
+        <v>0.08423067818139648</v>
       </c>
       <c r="T3">
-        <v>0.8798659169812504</v>
+        <v>0.8875445307481867</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>26.18255518994437</v>
+        <v>13.09127759497219</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08340518861776855</v>
+        <v>0.08336003297230185</v>
       </c>
       <c r="C4">
-        <v>17568.28076844684</v>
+        <v>17410.09939114879</v>
       </c>
       <c r="D4">
-        <v>17038.91276844684</v>
+        <v>17059.39739114878</v>
       </c>
       <c r="E4">
-        <v>23.73199999999997</v>
+        <v>202.3979999999999</v>
       </c>
       <c r="F4">
-        <v>357.332</v>
+        <v>535.9979999999999</v>
       </c>
       <c r="G4">
         <v>886.7</v>
@@ -1603,45 +1603,45 @@
         <v>235.3</v>
       </c>
       <c r="M4">
-        <v>17.9737996</v>
+        <v>27.76469639999999</v>
       </c>
       <c r="N4">
-        <v>217.3262004</v>
+        <v>207.5353036</v>
       </c>
       <c r="O4">
-        <v>31.7296252584</v>
+        <v>30.3001543256</v>
       </c>
       <c r="P4">
-        <v>185.5965751416</v>
+        <v>177.2351492744</v>
       </c>
       <c r="Q4">
-        <v>254.1965751416</v>
+        <v>245.8351492744</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08423067818139648</v>
+        <v>0.0845700174972184</v>
       </c>
       <c r="T4">
-        <v>0.8875445307481867</v>
+        <v>0.8953814664484619</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.146</v>
       </c>
       <c r="W4">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>13.09127759497219</v>
+        <v>8.47479102994982</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08336003297230185</v>
+        <v>0.08334732932683515</v>
       </c>
       <c r="C5">
-        <v>17410.09939114879</v>
+        <v>17237.20521407781</v>
       </c>
       <c r="D5">
-        <v>17059.39739114878</v>
+        <v>17065.16921407781</v>
       </c>
       <c r="E5">
-        <v>202.3979999999999</v>
+        <v>381.064</v>
       </c>
       <c r="F5">
-        <v>535.9979999999999</v>
+        <v>714.664</v>
       </c>
       <c r="G5">
         <v>886.7</v>
@@ -1685,45 +1685,45 @@
         <v>235.3</v>
       </c>
       <c r="M5">
-        <v>27.76469639999999</v>
+        <v>38.234524</v>
       </c>
       <c r="N5">
-        <v>207.5353036</v>
+        <v>197.065476</v>
       </c>
       <c r="O5">
-        <v>30.3001543256</v>
+        <v>28.771559496</v>
       </c>
       <c r="P5">
-        <v>177.2351492744</v>
+        <v>168.293916504</v>
       </c>
       <c r="Q5">
-        <v>245.8351492744</v>
+        <v>236.893916504</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0845700174972184</v>
+        <v>0.08491642638211995</v>
       </c>
       <c r="T5">
-        <v>0.8953814664484619</v>
+        <v>0.9033816716424931</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.146</v>
       </c>
       <c r="W5">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.47479102994982</v>
+        <v>6.154123953524308</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08334732932683515</v>
+        <v>0.08332523168136843</v>
       </c>
       <c r="C6">
-        <v>17237.20521407781</v>
+        <v>17068.58845407517</v>
       </c>
       <c r="D6">
-        <v>17065.16921407781</v>
+        <v>17075.21845407517</v>
       </c>
       <c r="E6">
-        <v>381.064</v>
+        <v>559.7299999999999</v>
       </c>
       <c r="F6">
-        <v>714.664</v>
+        <v>893.3299999999999</v>
       </c>
       <c r="G6">
         <v>886.7</v>
@@ -1767,45 +1767,45 @@
         <v>235.3</v>
       </c>
       <c r="M6">
-        <v>38.234524</v>
+        <v>48.507819</v>
       </c>
       <c r="N6">
-        <v>197.065476</v>
+        <v>186.792181</v>
       </c>
       <c r="O6">
-        <v>28.771559496</v>
+        <v>27.271658426</v>
       </c>
       <c r="P6">
-        <v>168.293916504</v>
+        <v>159.520522574</v>
       </c>
       <c r="Q6">
-        <v>236.893916504</v>
+        <v>228.120522574</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08491642638211995</v>
+        <v>0.08527012808565099</v>
       </c>
       <c r="T6">
-        <v>0.9033816716424931</v>
+        <v>0.9115503022090299</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.146</v>
       </c>
       <c r="W6">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.154123953524308</v>
+        <v>4.850764368523764</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08332523168136843</v>
+        <v>0.08332704603590176</v>
       </c>
       <c r="C7">
-        <v>17068.58845407517</v>
+        <v>16889.09690281862</v>
       </c>
       <c r="D7">
-        <v>17075.21845407517</v>
+        <v>17074.39290281862</v>
       </c>
       <c r="E7">
-        <v>559.7299999999999</v>
+        <v>738.3960000000001</v>
       </c>
       <c r="F7">
-        <v>893.3299999999999</v>
+        <v>1071.996</v>
       </c>
       <c r="G7">
         <v>886.7</v>
@@ -1849,45 +1849,45 @@
         <v>235.3</v>
       </c>
       <c r="M7">
-        <v>48.507819</v>
+        <v>59.28137880000001</v>
       </c>
       <c r="N7">
-        <v>186.792181</v>
+        <v>176.0186212</v>
       </c>
       <c r="O7">
-        <v>27.271658426</v>
+        <v>25.6987186952</v>
       </c>
       <c r="P7">
-        <v>159.520522574</v>
+        <v>150.3199025048</v>
       </c>
       <c r="Q7">
-        <v>228.120522574</v>
+        <v>218.9199025048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08527012808565099</v>
+        <v>0.08563135535734229</v>
       </c>
       <c r="T7">
-        <v>0.9115503022090299</v>
+        <v>0.9198927334259187</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.146</v>
       </c>
       <c r="W7">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.850764368523764</v>
+        <v>3.969205925419535</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08332704603590176</v>
+        <v>0.08328616039043504</v>
       </c>
       <c r="C8">
-        <v>16889.09690281862</v>
+        <v>16729.05371101004</v>
       </c>
       <c r="D8">
-        <v>17074.39290281862</v>
+        <v>17093.01571101004</v>
       </c>
       <c r="E8">
-        <v>738.3959999999998</v>
+        <v>917.0619999999998</v>
       </c>
       <c r="F8">
-        <v>1071.996</v>
+        <v>1250.662</v>
       </c>
       <c r="G8">
         <v>886.7</v>
@@ -1931,28 +1931,28 @@
         <v>235.3</v>
       </c>
       <c r="M8">
-        <v>59.28137879999999</v>
+        <v>69.16160859999999</v>
       </c>
       <c r="N8">
-        <v>176.0186212</v>
+        <v>166.1383914</v>
       </c>
       <c r="O8">
-        <v>25.6987186952</v>
+        <v>24.2562051444</v>
       </c>
       <c r="P8">
-        <v>150.3199025048</v>
+        <v>141.8821862556</v>
       </c>
       <c r="Q8">
-        <v>218.9199025048</v>
+        <v>210.4821862556</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08563135535734229</v>
+        <v>0.08600035095745703</v>
       </c>
       <c r="T8">
-        <v>0.9198927334259187</v>
+        <v>0.9284145717657513</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>3.969205925419536</v>
+        <v>3.402176507502459</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08328616039043504</v>
+        <v>0.08341607474496834</v>
       </c>
       <c r="C9">
-        <v>16729.05371101004</v>
+        <v>16491.35369116137</v>
       </c>
       <c r="D9">
-        <v>17093.01571101004</v>
+        <v>17033.98169116137</v>
       </c>
       <c r="E9">
-        <v>917.062</v>
+        <v>1095.728</v>
       </c>
       <c r="F9">
-        <v>1250.662</v>
+        <v>1429.328</v>
       </c>
       <c r="G9">
         <v>886.7</v>
@@ -2013,45 +2013,45 @@
         <v>235.3</v>
       </c>
       <c r="M9">
-        <v>69.16160860000001</v>
+        <v>82.6151584</v>
       </c>
       <c r="N9">
-        <v>166.1383914</v>
+        <v>152.6848416</v>
       </c>
       <c r="O9">
-        <v>24.2562051444</v>
+        <v>22.2919868736</v>
       </c>
       <c r="P9">
-        <v>141.8821862556</v>
+        <v>130.3928547264</v>
       </c>
       <c r="Q9">
-        <v>210.4821862556</v>
+        <v>198.9928547264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08600035095745703</v>
+        <v>0.08637736820105253</v>
       </c>
       <c r="T9">
-        <v>0.9284145717657513</v>
+        <v>0.9371216674607975</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V9">
         <v>0.146</v>
       </c>
       <c r="W9">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.402176507502458</v>
+        <v>2.848145601328291</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08341607474496834</v>
+        <v>0.08339653909950162</v>
       </c>
       <c r="C10">
-        <v>16491.35369116137</v>
+        <v>16321.53876722251</v>
       </c>
       <c r="D10">
-        <v>17033.98169116137</v>
+        <v>17042.83276722251</v>
       </c>
       <c r="E10">
-        <v>1095.728</v>
+        <v>1274.394</v>
       </c>
       <c r="F10">
-        <v>1429.328</v>
+        <v>1607.994</v>
       </c>
       <c r="G10">
         <v>886.7</v>
@@ -2095,28 +2095,28 @@
         <v>235.3</v>
       </c>
       <c r="M10">
-        <v>82.6151584</v>
+        <v>92.9420532</v>
       </c>
       <c r="N10">
-        <v>152.6848416</v>
+        <v>142.3579468</v>
       </c>
       <c r="O10">
-        <v>22.2919868736</v>
+        <v>20.7842602328</v>
       </c>
       <c r="P10">
-        <v>130.3928547264</v>
+        <v>121.5736865672</v>
       </c>
       <c r="Q10">
-        <v>198.9928547264</v>
+        <v>190.1736865672</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08637736820105253</v>
+        <v>0.08676267153791387</v>
       </c>
       <c r="T10">
-        <v>0.9371216674607975</v>
+        <v>0.9460201278963942</v>
       </c>
       <c r="U10">
         <v>0.0578</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>2.848145601328291</v>
+        <v>2.531684978958481</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08339653909950162</v>
+        <v>0.08391502345403493</v>
       </c>
       <c r="C11">
-        <v>16321.53876722251</v>
+        <v>15911.03656863303</v>
       </c>
       <c r="D11">
-        <v>17042.83276722251</v>
+        <v>16810.99656863303</v>
       </c>
       <c r="E11">
-        <v>1274.394</v>
+        <v>1453.059999999999</v>
       </c>
       <c r="F11">
-        <v>1607.994</v>
+        <v>1786.66</v>
       </c>
       <c r="G11">
         <v>886.7</v>
@@ -2177,45 +2177,45 @@
         <v>235.3</v>
       </c>
       <c r="M11">
-        <v>92.9420532</v>
+        <v>114.524906</v>
       </c>
       <c r="N11">
-        <v>142.3579468</v>
+        <v>120.775094</v>
       </c>
       <c r="O11">
-        <v>20.7842602328</v>
+        <v>17.633163724</v>
       </c>
       <c r="P11">
-        <v>121.5736865672</v>
+        <v>103.141930276</v>
       </c>
       <c r="Q11">
-        <v>190.1736865672</v>
+        <v>171.741930276</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08676267153791387</v>
+        <v>0.08715653717114991</v>
       </c>
       <c r="T11">
-        <v>0.9460201278963942</v>
+        <v>0.9551163318972266</v>
       </c>
       <c r="U11">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.146</v>
       </c>
       <c r="W11">
-        <v>0.0493612</v>
+        <v>0.0547414</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.531684978958481</v>
+        <v>2.054574923641501</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08391502345403493</v>
+        <v>0.08504838780856822</v>
       </c>
       <c r="C12">
-        <v>15911.03656863303</v>
+        <v>15246.92427799811</v>
       </c>
       <c r="D12">
-        <v>16810.99656863303</v>
+        <v>16325.55027799811</v>
       </c>
       <c r="E12">
-        <v>1453.06</v>
+        <v>1631.726</v>
       </c>
       <c r="F12">
-        <v>1786.66</v>
+        <v>1965.326</v>
       </c>
       <c r="G12">
         <v>886.7</v>
@@ -2259,45 +2259,45 @@
         <v>235.3</v>
       </c>
       <c r="M12">
-        <v>114.524906</v>
+        <v>148.9717108</v>
       </c>
       <c r="N12">
-        <v>120.775094</v>
+        <v>86.32828920000003</v>
       </c>
       <c r="O12">
-        <v>17.633163724</v>
+        <v>12.6039302232</v>
       </c>
       <c r="P12">
-        <v>103.141930276</v>
+        <v>73.72435897680003</v>
       </c>
       <c r="Q12">
-        <v>171.741930276</v>
+        <v>142.3243589768</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08715653717114991</v>
+        <v>0.08755925371749237</v>
       </c>
       <c r="T12">
-        <v>0.9551163318972266</v>
+        <v>0.9644169449767293</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.146</v>
       </c>
       <c r="W12">
-        <v>0.0547414</v>
+        <v>0.0647332</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.0545749236415</v>
+        <v>1.579494514337014</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08504838780856822</v>
+        <v>0.08977318358733499</v>
       </c>
       <c r="C13">
-        <v>15246.92427799811</v>
+        <v>13314.12349068318</v>
       </c>
       <c r="D13">
-        <v>16325.55027799811</v>
+        <v>14571.41549068318</v>
       </c>
       <c r="E13">
-        <v>1631.726</v>
+        <v>1810.392</v>
       </c>
       <c r="F13">
-        <v>1965.326</v>
+        <v>2143.992</v>
       </c>
       <c r="G13">
         <v>886.7</v>
@@ -2341,45 +2341,45 @@
         <v>235.3</v>
       </c>
       <c r="M13">
-        <v>148.9717108</v>
+        <v>254.2774512</v>
       </c>
       <c r="N13">
-        <v>86.32828920000003</v>
+        <v>-18.97745119999999</v>
       </c>
       <c r="O13">
-        <v>12.6039302232</v>
+        <v>-2.770707875199999</v>
       </c>
       <c r="P13">
-        <v>73.72435897680003</v>
+        <v>-16.20674332479999</v>
       </c>
       <c r="Q13">
-        <v>142.3243589768</v>
+        <v>52.39325667519998</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08755925371749237</v>
+        <v>0.08802724781292515</v>
       </c>
       <c r="T13">
-        <v>0.9644169449767293</v>
+        <v>0.9752251227003497</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V13">
-        <v>0.146</v>
+        <v>0.1351036037126992</v>
       </c>
       <c r="W13">
-        <v>0.0647332</v>
+        <v>0.1025767125996739</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y13">
-        <v>1.579494514337014</v>
+        <v>0.9253671487171176</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08977318358733499</v>
+        <v>0.090501183587335</v>
       </c>
       <c r="C14">
-        <v>13314.12349068318</v>
+        <v>12898.14855105539</v>
       </c>
       <c r="D14">
-        <v>14571.41549068318</v>
+        <v>14334.10655105539</v>
       </c>
       <c r="E14">
-        <v>1810.392</v>
+        <v>1989.058</v>
       </c>
       <c r="F14">
-        <v>2143.992</v>
+        <v>2322.658</v>
       </c>
       <c r="G14">
         <v>886.7</v>
@@ -2423,37 +2423,37 @@
         <v>235.3</v>
       </c>
       <c r="M14">
-        <v>254.2774512</v>
+        <v>275.4672388</v>
       </c>
       <c r="N14">
-        <v>-18.97745119999999</v>
+        <v>-40.16723880000001</v>
       </c>
       <c r="O14">
-        <v>-2.770707875199999</v>
+        <v>-5.864416864800001</v>
       </c>
       <c r="P14">
-        <v>-16.20674332479999</v>
+        <v>-34.30282193520001</v>
       </c>
       <c r="Q14">
-        <v>52.39325667519998</v>
+        <v>34.29717806479996</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08802724781292515</v>
+        <v>0.08851261847744152</v>
       </c>
       <c r="T14">
-        <v>0.9752251227003497</v>
+        <v>0.9864346068693192</v>
       </c>
       <c r="U14">
         <v>0.1186</v>
       </c>
       <c r="V14">
-        <v>0.1351036037126992</v>
+        <v>0.1247110188117223</v>
       </c>
       <c r="W14">
-        <v>0.1025767125996739</v>
+        <v>0.1038092731689297</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.9253671487171176</v>
+        <v>0.8541850603542623</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.090501183587335</v>
+        <v>0.1029878697760778</v>
       </c>
       <c r="C15">
-        <v>12898.14855105539</v>
+        <v>9589.701865048761</v>
       </c>
       <c r="D15">
-        <v>14334.10655105539</v>
+        <v>11204.32586504876</v>
       </c>
       <c r="E15">
-        <v>1989.058</v>
+        <v>2167.724</v>
       </c>
       <c r="F15">
-        <v>2322.658</v>
+        <v>2501.324</v>
       </c>
       <c r="G15">
         <v>886.7</v>
@@ -2505,45 +2505,45 @@
         <v>235.3</v>
       </c>
       <c r="M15">
-        <v>275.4672388</v>
+        <v>502.2658592</v>
       </c>
       <c r="N15">
-        <v>-40.16723880000001</v>
+        <v>-266.9658592</v>
       </c>
       <c r="O15">
-        <v>-5.864416864800001</v>
+        <v>-38.9770154432</v>
       </c>
       <c r="P15">
-        <v>-34.30282193520001</v>
+        <v>-227.9888437568</v>
       </c>
       <c r="Q15">
-        <v>34.29717806479996</v>
+        <v>-159.3888437568</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08851261847744152</v>
+        <v>0.08930077240013592</v>
       </c>
       <c r="T15">
-        <v>0.9864346068693192</v>
+        <v>1.004636775984663</v>
       </c>
       <c r="U15">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.1247110188117223</v>
+        <v>0.06839764115107906</v>
       </c>
       <c r="W15">
-        <v>0.1038092731689297</v>
+        <v>0.1870657536568633</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y15">
-        <v>0.8541850603542623</v>
+        <v>0.468476994185473</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1029878697760778</v>
+        <v>0.1045378697760778</v>
       </c>
       <c r="C16">
-        <v>9589.701865048761</v>
+        <v>9115.371327723331</v>
       </c>
       <c r="D16">
-        <v>11204.32586504876</v>
+        <v>10908.66132772333</v>
       </c>
       <c r="E16">
-        <v>2167.724</v>
+        <v>2346.39</v>
       </c>
       <c r="F16">
-        <v>2501.324</v>
+        <v>2679.99</v>
       </c>
       <c r="G16">
         <v>886.7</v>
@@ -2587,37 +2587,37 @@
         <v>235.3</v>
       </c>
       <c r="M16">
-        <v>502.2658592</v>
+        <v>538.1419920000001</v>
       </c>
       <c r="N16">
-        <v>-266.9658592</v>
+        <v>-302.8419920000001</v>
       </c>
       <c r="O16">
-        <v>-38.9770154432</v>
+        <v>-44.21493083200001</v>
       </c>
       <c r="P16">
-        <v>-227.9888437568</v>
+        <v>-258.6270611680001</v>
       </c>
       <c r="Q16">
-        <v>-159.3888437568</v>
+        <v>-190.0270611680001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08930077240013592</v>
+        <v>0.0898125461930787</v>
       </c>
       <c r="T16">
-        <v>1.004636775984663</v>
+        <v>1.016456032172718</v>
       </c>
       <c r="U16">
         <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.06839764115107906</v>
+        <v>0.06383779840767378</v>
       </c>
       <c r="W16">
-        <v>0.1870657536568633</v>
+        <v>0.1879813700797391</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.468476994185473</v>
+        <v>0.4372451945731081</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1045378697760778</v>
+        <v>0.1060878697760778</v>
       </c>
       <c r="C17">
-        <v>9115.371327723331</v>
+        <v>8656.243849804592</v>
       </c>
       <c r="D17">
-        <v>10908.66132772333</v>
+        <v>10628.19984980459</v>
       </c>
       <c r="E17">
-        <v>2346.39</v>
+        <v>2525.056</v>
       </c>
       <c r="F17">
-        <v>2679.99</v>
+        <v>2858.656</v>
       </c>
       <c r="G17">
         <v>886.7</v>
@@ -2669,37 +2669,37 @@
         <v>235.3</v>
       </c>
       <c r="M17">
-        <v>538.141992</v>
+        <v>574.0181248</v>
       </c>
       <c r="N17">
-        <v>-302.8419919999999</v>
+        <v>-338.7181248</v>
       </c>
       <c r="O17">
-        <v>-44.21493083199999</v>
+        <v>-49.4528462208</v>
       </c>
       <c r="P17">
-        <v>-258.627061168</v>
+        <v>-289.2652785792</v>
       </c>
       <c r="Q17">
-        <v>-190.027061168</v>
+        <v>-220.6652785792</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0898125461930787</v>
+        <v>0.09033650507632965</v>
       </c>
       <c r="T17">
-        <v>1.016456032172718</v>
+        <v>1.028556699222394</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.06383779840767378</v>
+        <v>0.05984793600719417</v>
       </c>
       <c r="W17">
-        <v>0.1879813700797391</v>
+        <v>0.1887825344497554</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4372451945731082</v>
+        <v>0.4099173699122889</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1060878697760778</v>
+        <v>0.1076378697760778</v>
       </c>
       <c r="C18">
-        <v>8656.243849804592</v>
+        <v>8211.176212315295</v>
       </c>
       <c r="D18">
-        <v>10628.19984980459</v>
+        <v>10361.79821231529</v>
       </c>
       <c r="E18">
-        <v>2525.056</v>
+        <v>2703.722</v>
       </c>
       <c r="F18">
-        <v>2858.656</v>
+        <v>3037.322</v>
       </c>
       <c r="G18">
         <v>886.7</v>
@@ -2751,37 +2751,37 @@
         <v>235.3</v>
       </c>
       <c r="M18">
-        <v>574.0181248</v>
+        <v>609.8942576000001</v>
       </c>
       <c r="N18">
-        <v>-338.7181248</v>
+        <v>-374.5942576</v>
       </c>
       <c r="O18">
-        <v>-49.4528462208</v>
+        <v>-54.6907616096</v>
       </c>
       <c r="P18">
-        <v>-289.2652785792</v>
+        <v>-319.9034959904001</v>
       </c>
       <c r="Q18">
-        <v>-220.6652785792</v>
+        <v>-251.3034959904001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09033650507632965</v>
+        <v>0.09087308947483963</v>
       </c>
       <c r="T18">
-        <v>1.028556699222394</v>
+        <v>1.040948948610615</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.05984793600719417</v>
+        <v>0.05632746918324157</v>
       </c>
       <c r="W18">
-        <v>0.1887825344497554</v>
+        <v>0.1894894441880051</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.4099173699122889</v>
+        <v>0.3858045834468601</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1076378697760778</v>
+        <v>0.1091878697760778</v>
       </c>
       <c r="C19">
-        <v>8211.176212315295</v>
+        <v>7779.137015111716</v>
       </c>
       <c r="D19">
-        <v>10361.79821231529</v>
+        <v>10108.42501511172</v>
       </c>
       <c r="E19">
-        <v>2703.722</v>
+        <v>2882.388</v>
       </c>
       <c r="F19">
-        <v>3037.322</v>
+        <v>3215.988</v>
       </c>
       <c r="G19">
         <v>886.7</v>
@@ -2833,37 +2833,37 @@
         <v>235.3</v>
       </c>
       <c r="M19">
-        <v>609.8942576000001</v>
+        <v>645.7703904000001</v>
       </c>
       <c r="N19">
-        <v>-374.5942576</v>
+        <v>-410.4703904000001</v>
       </c>
       <c r="O19">
-        <v>-54.6907616096</v>
+        <v>-59.92867699840001</v>
       </c>
       <c r="P19">
-        <v>-319.9034959904001</v>
+        <v>-350.5417134016001</v>
       </c>
       <c r="Q19">
-        <v>-251.3034959904001</v>
+        <v>-281.9417134016001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09087308947483963</v>
+        <v>0.09142276129770353</v>
       </c>
       <c r="T19">
-        <v>1.040948948610615</v>
+        <v>1.053643447983915</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.05632746918324157</v>
+        <v>0.05319816533972815</v>
       </c>
       <c r="W19">
-        <v>0.1894894441880051</v>
+        <v>0.1901178083997826</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3858045834468601</v>
+        <v>0.3643709954775901</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1091878697760778</v>
+        <v>0.1107378697760778</v>
       </c>
       <c r="C20">
-        <v>7779.137015111721</v>
+        <v>7359.193331882337</v>
       </c>
       <c r="D20">
-        <v>10108.42501511172</v>
+        <v>9867.147331882335</v>
       </c>
       <c r="E20">
-        <v>2882.388</v>
+        <v>3061.054</v>
       </c>
       <c r="F20">
-        <v>3215.988</v>
+        <v>3394.654</v>
       </c>
       <c r="G20">
         <v>886.7</v>
@@ -2915,37 +2915,37 @@
         <v>235.3</v>
       </c>
       <c r="M20">
-        <v>645.7703904</v>
+        <v>681.6465231999999</v>
       </c>
       <c r="N20">
-        <v>-410.4703904</v>
+        <v>-446.3465231999999</v>
       </c>
       <c r="O20">
-        <v>-59.92867699839999</v>
+        <v>-65.16659238719998</v>
       </c>
       <c r="P20">
-        <v>-350.5417134016</v>
+        <v>-381.1799308128</v>
       </c>
       <c r="Q20">
-        <v>-281.9417134016</v>
+        <v>-312.5799308128</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09142276129770353</v>
+        <v>0.09198600526434184</v>
       </c>
       <c r="T20">
-        <v>1.053643447983915</v>
+        <v>1.066651391786186</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.05319816533972815</v>
+        <v>0.0503982619007951</v>
       </c>
       <c r="W20">
-        <v>0.1901178083997826</v>
+        <v>0.1906800290103204</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3643709954775901</v>
+        <v>0.3451935746629802</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1107378697760778</v>
+        <v>0.1122878697760777</v>
       </c>
       <c r="C21">
-        <v>7359.193331882337</v>
+        <v>6950.499231780383</v>
       </c>
       <c r="D21">
-        <v>9867.147331882335</v>
+        <v>9637.119231780382</v>
       </c>
       <c r="E21">
-        <v>3061.054</v>
+        <v>3239.72</v>
       </c>
       <c r="F21">
-        <v>3394.654</v>
+        <v>3573.32</v>
       </c>
       <c r="G21">
         <v>886.7</v>
@@ -2997,37 +2997,37 @@
         <v>235.3</v>
       </c>
       <c r="M21">
-        <v>681.6465231999999</v>
+        <v>717.522656</v>
       </c>
       <c r="N21">
-        <v>-446.3465231999999</v>
+        <v>-482.222656</v>
       </c>
       <c r="O21">
-        <v>-65.16659238719998</v>
+        <v>-70.40450777599999</v>
       </c>
       <c r="P21">
-        <v>-381.1799308128</v>
+        <v>-411.818148224</v>
       </c>
       <c r="Q21">
-        <v>-312.5799308128</v>
+        <v>-343.218148224</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09198600526434184</v>
+        <v>0.0925633303301461</v>
       </c>
       <c r="T21">
-        <v>1.066651391786186</v>
+        <v>1.079984534183513</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.0503982619007951</v>
+        <v>0.04787834880575535</v>
       </c>
       <c r="W21">
-        <v>0.1906800290103204</v>
+        <v>0.1911860275598043</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3451935746629802</v>
+        <v>0.3279338959298311</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1122878697760777</v>
+        <v>0.1138378697760778</v>
       </c>
       <c r="C22">
-        <v>6950.499231780383</v>
+        <v>6552.285870018156</v>
       </c>
       <c r="D22">
-        <v>9637.119231780382</v>
+        <v>9417.571870018155</v>
       </c>
       <c r="E22">
-        <v>3239.72</v>
+        <v>3418.386</v>
       </c>
       <c r="F22">
-        <v>3573.32</v>
+        <v>3751.986</v>
       </c>
       <c r="G22">
         <v>886.7</v>
@@ -3079,37 +3079,37 @@
         <v>235.3</v>
       </c>
       <c r="M22">
-        <v>717.522656</v>
+        <v>753.3987888</v>
       </c>
       <c r="N22">
-        <v>-482.222656</v>
+        <v>-518.0987888</v>
       </c>
       <c r="O22">
-        <v>-70.40450777599999</v>
+        <v>-75.64242316479999</v>
       </c>
       <c r="P22">
-        <v>-411.818148224</v>
+        <v>-442.4563656352</v>
       </c>
       <c r="Q22">
-        <v>-343.218148224</v>
+        <v>-373.8563656352</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0925633303301461</v>
+        <v>0.09315527122040113</v>
       </c>
       <c r="T22">
-        <v>1.079984534183513</v>
+        <v>1.093655224489634</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.04787834880575535</v>
+        <v>0.04559842743405271</v>
       </c>
       <c r="W22">
-        <v>0.1911860275598043</v>
+        <v>0.1916438357712422</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3279338959298311</v>
+        <v>0.3123179961236487</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1138378697760778</v>
+        <v>0.1153878697760778</v>
       </c>
       <c r="C23">
-        <v>6552.285870018157</v>
+        <v>6163.852902793844</v>
       </c>
       <c r="D23">
-        <v>9417.571870018155</v>
+        <v>9207.804902793843</v>
       </c>
       <c r="E23">
-        <v>3418.386</v>
+        <v>3597.052</v>
       </c>
       <c r="F23">
-        <v>3751.985999999999</v>
+        <v>3930.652</v>
       </c>
       <c r="G23">
         <v>886.7</v>
@@ -3161,37 +3161,37 @@
         <v>235.3</v>
       </c>
       <c r="M23">
-        <v>753.3987887999999</v>
+        <v>789.2749216</v>
       </c>
       <c r="N23">
-        <v>-518.0987888</v>
+        <v>-553.9749216</v>
       </c>
       <c r="O23">
-        <v>-75.64242316479999</v>
+        <v>-80.8803385536</v>
       </c>
       <c r="P23">
-        <v>-442.4563656352</v>
+        <v>-473.0945830464</v>
       </c>
       <c r="Q23">
-        <v>-373.8563656352</v>
+        <v>-404.4945830464001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09315527122040113</v>
+        <v>0.09376239008220115</v>
       </c>
       <c r="T23">
-        <v>1.093655224489634</v>
+        <v>1.107676445316424</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.04559842743405271</v>
+        <v>0.04352577164159577</v>
       </c>
       <c r="W23">
-        <v>0.1916438357712422</v>
+        <v>0.1920600250543676</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3123179961236486</v>
+        <v>0.2981217235725737</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1153878697760778</v>
+        <v>0.1169378697760778</v>
       </c>
       <c r="C24">
-        <v>6163.852902793844</v>
+        <v>5784.561024562528</v>
       </c>
       <c r="D24">
-        <v>9207.804902793843</v>
+        <v>9007.179024562527</v>
       </c>
       <c r="E24">
-        <v>3597.052</v>
+        <v>3775.718</v>
       </c>
       <c r="F24">
-        <v>3930.652</v>
+        <v>4109.318</v>
       </c>
       <c r="G24">
         <v>886.7</v>
@@ -3243,37 +3243,37 @@
         <v>235.3</v>
       </c>
       <c r="M24">
-        <v>789.2749216</v>
+        <v>825.1510544</v>
       </c>
       <c r="N24">
-        <v>-553.9749216</v>
+        <v>-589.8510544000001</v>
       </c>
       <c r="O24">
-        <v>-80.8803385536</v>
+        <v>-86.1182539424</v>
       </c>
       <c r="P24">
-        <v>-473.0945830464</v>
+        <v>-503.7328004576001</v>
       </c>
       <c r="Q24">
-        <v>-404.4945830464001</v>
+        <v>-435.1328004576001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09376239008220115</v>
+        <v>0.09438527826508689</v>
       </c>
       <c r="T24">
-        <v>1.107676445316424</v>
+        <v>1.122061853697157</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.04352577164159577</v>
+        <v>0.04163334678761334</v>
       </c>
       <c r="W24">
-        <v>0.1920600250543676</v>
+        <v>0.1924400239650473</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2981217235725737</v>
+        <v>0.2851599095042009</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1169378697760778</v>
+        <v>0.1184878697760778</v>
       </c>
       <c r="C25">
-        <v>5784.561024562528</v>
+        <v>5413.825460121026</v>
       </c>
       <c r="D25">
-        <v>9007.179024562527</v>
+        <v>8815.109460121026</v>
       </c>
       <c r="E25">
-        <v>3775.718</v>
+        <v>3954.384</v>
       </c>
       <c r="F25">
-        <v>4109.318</v>
+        <v>4287.984</v>
       </c>
       <c r="G25">
         <v>886.7</v>
@@ -3325,37 +3325,37 @@
         <v>235.3</v>
       </c>
       <c r="M25">
-        <v>825.1510544</v>
+        <v>861.0271872000001</v>
       </c>
       <c r="N25">
-        <v>-589.8510544000001</v>
+        <v>-625.7271872000001</v>
       </c>
       <c r="O25">
-        <v>-86.1182539424</v>
+        <v>-91.35616933120001</v>
       </c>
       <c r="P25">
-        <v>-503.7328004576001</v>
+        <v>-534.3710178688001</v>
       </c>
       <c r="Q25">
-        <v>-435.1328004576001</v>
+        <v>-465.7710178688001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09438527826508689</v>
+        <v>0.09502455824225908</v>
       </c>
       <c r="T25">
-        <v>1.122061853697157</v>
+        <v>1.13682582545633</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.04163334678761334</v>
+        <v>0.03989862400479611</v>
       </c>
       <c r="W25">
-        <v>0.1924400239650473</v>
+        <v>0.1927883562998369</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2851599095042009</v>
+        <v>0.2732782466081926</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1184878697760778</v>
+        <v>0.1200378697760778</v>
       </c>
       <c r="C26">
-        <v>5413.825460121027</v>
+        <v>5051.110271958703</v>
       </c>
       <c r="D26">
-        <v>8815.109460121026</v>
+        <v>8631.060271958702</v>
       </c>
       <c r="E26">
-        <v>3954.384</v>
+        <v>4133.049999999999</v>
       </c>
       <c r="F26">
-        <v>4287.983999999999</v>
+        <v>4466.65</v>
       </c>
       <c r="G26">
         <v>886.7</v>
@@ -3407,37 +3407,37 @@
         <v>235.3</v>
       </c>
       <c r="M26">
-        <v>861.0271872</v>
+        <v>896.90332</v>
       </c>
       <c r="N26">
-        <v>-625.7271871999999</v>
+        <v>-661.6033199999999</v>
       </c>
       <c r="O26">
-        <v>-91.35616933119998</v>
+        <v>-96.59408471999998</v>
       </c>
       <c r="P26">
-        <v>-534.3710178687999</v>
+        <v>-565.00923528</v>
       </c>
       <c r="Q26">
-        <v>-465.7710178687999</v>
+        <v>-496.40923528</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09502455824225908</v>
+        <v>0.0956808856854892</v>
       </c>
       <c r="T26">
-        <v>1.13682582545633</v>
+        <v>1.151983503129081</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.03989862400479612</v>
+        <v>0.03830267904460427</v>
       </c>
       <c r="W26">
-        <v>0.1927883562998369</v>
+        <v>0.1931088220478435</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2732782466081927</v>
+        <v>0.2623471167438649</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1200378697760778</v>
+        <v>0.1215878697760778</v>
       </c>
       <c r="C27">
-        <v>5051.110271958703</v>
+        <v>4695.923366158565</v>
       </c>
       <c r="D27">
-        <v>8631.060271958702</v>
+        <v>8454.539366158564</v>
       </c>
       <c r="E27">
-        <v>4133.049999999999</v>
+        <v>4311.715999999999</v>
       </c>
       <c r="F27">
-        <v>4466.65</v>
+        <v>4645.316</v>
       </c>
       <c r="G27">
         <v>886.7</v>
@@ -3489,37 +3489,37 @@
         <v>235.3</v>
       </c>
       <c r="M27">
-        <v>896.90332</v>
+        <v>932.7794527999999</v>
       </c>
       <c r="N27">
-        <v>-661.6033199999999</v>
+        <v>-697.4794528</v>
       </c>
       <c r="O27">
-        <v>-96.59408471999998</v>
+        <v>-101.8320001088</v>
       </c>
       <c r="P27">
-        <v>-565.00923528</v>
+        <v>-595.6474526912</v>
       </c>
       <c r="Q27">
-        <v>-496.40923528</v>
+        <v>-527.0474526912001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0956808856854892</v>
+        <v>0.09635495170826608</v>
       </c>
       <c r="T27">
-        <v>1.151983503129081</v>
+        <v>1.16755084776596</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.03830267904460427</v>
+        <v>0.03682949908135027</v>
       </c>
       <c r="W27">
-        <v>0.1931088220478435</v>
+        <v>0.1934046365844649</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2623471167438649</v>
+        <v>0.2522568430229469</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1215878697760778</v>
+        <v>0.1231378697760778</v>
       </c>
       <c r="C28">
-        <v>4695.923366158565</v>
+        <v>4347.812098846596</v>
       </c>
       <c r="D28">
-        <v>8454.539366158564</v>
+        <v>8285.094098846595</v>
       </c>
       <c r="E28">
-        <v>4311.715999999999</v>
+        <v>4490.382</v>
       </c>
       <c r="F28">
-        <v>4645.316</v>
+        <v>4823.982</v>
       </c>
       <c r="G28">
         <v>886.7</v>
@@ -3571,37 +3571,37 @@
         <v>235.3</v>
       </c>
       <c r="M28">
-        <v>932.7794527999999</v>
+        <v>968.6555856</v>
       </c>
       <c r="N28">
-        <v>-697.4794528</v>
+        <v>-733.3555856</v>
       </c>
       <c r="O28">
-        <v>-101.8320001088</v>
+        <v>-107.0699154976</v>
       </c>
       <c r="P28">
-        <v>-595.6474526912</v>
+        <v>-626.2856701024</v>
       </c>
       <c r="Q28">
-        <v>-527.0474526912001</v>
+        <v>-557.6856701024001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09635495170826608</v>
+        <v>0.09704748529331082</v>
       </c>
       <c r="T28">
-        <v>1.16755084776596</v>
+        <v>1.183544694995631</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.03682949908135027</v>
+        <v>0.03546544355981877</v>
       </c>
       <c r="W28">
-        <v>0.1934046365844649</v>
+        <v>0.1936785389331884</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2522568430229469</v>
+        <v>0.24291399698506</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1231378697760778</v>
+        <v>0.1246878697760778</v>
       </c>
       <c r="C29">
-        <v>4347.812098846596</v>
+        <v>4006.35940059167</v>
       </c>
       <c r="D29">
-        <v>8285.094098846595</v>
+        <v>8122.30740059167</v>
       </c>
       <c r="E29">
-        <v>4490.382</v>
+        <v>4669.048</v>
       </c>
       <c r="F29">
-        <v>4823.982</v>
+        <v>5002.648</v>
       </c>
       <c r="G29">
         <v>886.7</v>
@@ -3653,37 +3653,37 @@
         <v>235.3</v>
       </c>
       <c r="M29">
-        <v>968.6555856</v>
+        <v>1004.5317184</v>
       </c>
       <c r="N29">
-        <v>-733.3555856</v>
+        <v>-769.2317184000001</v>
       </c>
       <c r="O29">
-        <v>-107.0699154976</v>
+        <v>-112.3078308864</v>
       </c>
       <c r="P29">
-        <v>-626.2856701024</v>
+        <v>-656.9238875136001</v>
       </c>
       <c r="Q29">
-        <v>-557.6856701024001</v>
+        <v>-588.3238875136001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09704748529331082</v>
+        <v>0.09775925592238457</v>
       </c>
       <c r="T29">
-        <v>1.183544694995631</v>
+        <v>1.199982815759459</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.03546544355981877</v>
+        <v>0.03419882057553953</v>
       </c>
       <c r="W29">
-        <v>0.1936785389331884</v>
+        <v>0.1939328768284317</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.24291399698506</v>
+        <v>0.2342384970927365</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1246878697760778</v>
+        <v>0.1262378697760778</v>
       </c>
       <c r="C30">
-        <v>4006.35940059167</v>
+        <v>3671.180348891472</v>
       </c>
       <c r="D30">
-        <v>8122.30740059167</v>
+        <v>7965.794348891472</v>
       </c>
       <c r="E30">
-        <v>4669.048</v>
+        <v>4847.714</v>
       </c>
       <c r="F30">
-        <v>5002.648</v>
+        <v>5181.314</v>
       </c>
       <c r="G30">
         <v>886.7</v>
@@ -3735,37 +3735,37 @@
         <v>235.3</v>
       </c>
       <c r="M30">
-        <v>1004.5317184</v>
+        <v>1040.4078512</v>
       </c>
       <c r="N30">
-        <v>-769.2317184000001</v>
+        <v>-805.1078512000001</v>
       </c>
       <c r="O30">
-        <v>-112.3078308864</v>
+        <v>-117.5457462752</v>
       </c>
       <c r="P30">
-        <v>-656.9238875136001</v>
+        <v>-687.5621049248001</v>
       </c>
       <c r="Q30">
-        <v>-588.3238875136001</v>
+        <v>-618.9621049248001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09775925592238457</v>
+        <v>0.09849107642833366</v>
       </c>
       <c r="T30">
-        <v>1.199982815759459</v>
+        <v>1.216883982178607</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.03419882057553953</v>
+        <v>0.03301955090052092</v>
       </c>
       <c r="W30">
-        <v>0.1939328768284317</v>
+        <v>0.1941696741791754</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2342384970927365</v>
+        <v>0.2261613075378145</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1262378697760778</v>
+        <v>0.1277878697760778</v>
       </c>
       <c r="C31">
-        <v>3671.180348891473</v>
+        <v>3341.919129446165</v>
       </c>
       <c r="D31">
-        <v>7965.794348891472</v>
+        <v>7815.199129446165</v>
       </c>
       <c r="E31">
-        <v>4847.713999999999</v>
+        <v>5026.379999999999</v>
       </c>
       <c r="F31">
-        <v>5181.313999999999</v>
+        <v>5359.98</v>
       </c>
       <c r="G31">
         <v>886.7</v>
@@ -3817,37 +3817,37 @@
         <v>235.3</v>
       </c>
       <c r="M31">
-        <v>1040.4078512</v>
+        <v>1076.283984</v>
       </c>
       <c r="N31">
-        <v>-805.1078511999999</v>
+        <v>-840.983984</v>
       </c>
       <c r="O31">
-        <v>-117.5457462752</v>
+        <v>-122.783661664</v>
       </c>
       <c r="P31">
-        <v>-687.5621049248</v>
+        <v>-718.200322336</v>
       </c>
       <c r="Q31">
-        <v>-618.9621049248001</v>
+        <v>-649.6003223360001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09849107642833366</v>
+        <v>0.09924380609159557</v>
       </c>
       <c r="T31">
-        <v>1.216883982178607</v>
+        <v>1.234268039066872</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.03301955090052093</v>
+        <v>0.03191889920383689</v>
       </c>
       <c r="W31">
-        <v>0.1941696741791754</v>
+        <v>0.1943906850398696</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2261613075378145</v>
+        <v>0.2186225972865541</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1277878697760778</v>
+        <v>0.1293378697760778</v>
       </c>
       <c r="C32">
-        <v>3341.919129446165</v>
+        <v>3018.246335723607</v>
       </c>
       <c r="D32">
-        <v>7815.199129446165</v>
+        <v>7670.192335723607</v>
       </c>
       <c r="E32">
-        <v>5026.379999999999</v>
+        <v>5205.045999999999</v>
       </c>
       <c r="F32">
-        <v>5359.98</v>
+        <v>5538.646</v>
       </c>
       <c r="G32">
         <v>886.7</v>
@@ -3899,37 +3899,37 @@
         <v>235.3</v>
       </c>
       <c r="M32">
-        <v>1076.283984</v>
+        <v>1112.1601168</v>
       </c>
       <c r="N32">
-        <v>-840.983984</v>
+        <v>-876.8601168</v>
       </c>
       <c r="O32">
-        <v>-122.783661664</v>
+        <v>-128.0215770528</v>
       </c>
       <c r="P32">
-        <v>-718.200322336</v>
+        <v>-748.8385397472</v>
       </c>
       <c r="Q32">
-        <v>-649.6003223360001</v>
+        <v>-680.2385397472001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09924380609159557</v>
+        <v>0.1000183540059665</v>
       </c>
       <c r="T32">
-        <v>1.234268039066872</v>
+        <v>1.252155981662044</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.03191889920383689</v>
+        <v>0.03088925729403571</v>
       </c>
       <c r="W32">
-        <v>0.1943906850398696</v>
+        <v>0.1945974371353577</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2186225972865541</v>
+        <v>0.2115702554386006</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1293378697760778</v>
+        <v>0.1308878697760777</v>
       </c>
       <c r="C33">
-        <v>3018.246335723607</v>
+        <v>2699.856563678793</v>
       </c>
       <c r="D33">
-        <v>7670.192335723607</v>
+        <v>7530.468563678793</v>
       </c>
       <c r="E33">
-        <v>5205.045999999999</v>
+        <v>5383.712</v>
       </c>
       <c r="F33">
-        <v>5538.646</v>
+        <v>5717.312</v>
       </c>
       <c r="G33">
         <v>886.7</v>
@@ -3981,37 +3981,37 @@
         <v>235.3</v>
       </c>
       <c r="M33">
-        <v>1112.1601168</v>
+        <v>1148.0362496</v>
       </c>
       <c r="N33">
-        <v>-876.8601168</v>
+        <v>-912.7362496000001</v>
       </c>
       <c r="O33">
-        <v>-128.0215770528</v>
+        <v>-133.2594924416</v>
       </c>
       <c r="P33">
-        <v>-748.8385397472</v>
+        <v>-779.4767571584</v>
       </c>
       <c r="Q33">
-        <v>-680.2385397472001</v>
+        <v>-710.8767571584001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1000183540059665</v>
+        <v>0.1008156827413484</v>
       </c>
       <c r="T33">
-        <v>1.252155981662044</v>
+        <v>1.270570040215898</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.03088925729403571</v>
+        <v>0.02992396800359709</v>
       </c>
       <c r="W33">
-        <v>0.1945974371353577</v>
+        <v>0.1947912672248777</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2115702554386006</v>
+        <v>0.2049586849561444</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1308878697760777</v>
+        <v>0.1440415565765887</v>
       </c>
       <c r="C34">
-        <v>2699.856563678793</v>
+        <v>1512.926562176508</v>
       </c>
       <c r="D34">
-        <v>7530.468563678793</v>
+        <v>6522.204562176508</v>
       </c>
       <c r="E34">
-        <v>5383.712</v>
+        <v>5562.378</v>
       </c>
       <c r="F34">
-        <v>5717.312</v>
+        <v>5895.978</v>
       </c>
       <c r="G34">
         <v>886.7</v>
@@ -4063,45 +4063,45 @@
         <v>235.3</v>
       </c>
       <c r="M34">
-        <v>1148.0362496</v>
+        <v>1390.2716124</v>
       </c>
       <c r="N34">
-        <v>-912.7362496000001</v>
+        <v>-1154.9716124</v>
       </c>
       <c r="O34">
-        <v>-133.2594924416</v>
+        <v>-168.6258554104</v>
       </c>
       <c r="P34">
-        <v>-779.4767571584</v>
+        <v>-986.3457569896001</v>
       </c>
       <c r="Q34">
-        <v>-710.8767571584001</v>
+        <v>-917.7457569896001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1008156827413484</v>
+        <v>0.1017169418875042</v>
       </c>
       <c r="T34">
-        <v>1.270570040215898</v>
+        <v>1.291384339203331</v>
       </c>
       <c r="U34">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.02992396800359709</v>
+        <v>0.02471013555451634</v>
       </c>
       <c r="W34">
-        <v>0.1947912672248777</v>
+        <v>0.2299733500362451</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.2049586849561444</v>
+        <v>0.1692475037980571</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1440415565765887</v>
+        <v>0.1459415565765887</v>
       </c>
       <c r="C35">
-        <v>1512.926562176508</v>
+        <v>1210.513847108645</v>
       </c>
       <c r="D35">
-        <v>6522.204562176508</v>
+        <v>6398.457847108645</v>
       </c>
       <c r="E35">
-        <v>5562.378</v>
+        <v>5741.044</v>
       </c>
       <c r="F35">
-        <v>5895.978</v>
+        <v>6074.644</v>
       </c>
       <c r="G35">
         <v>886.7</v>
@@ -4145,37 +4145,37 @@
         <v>235.3</v>
       </c>
       <c r="M35">
-        <v>1390.2716124</v>
+        <v>1432.4010552</v>
       </c>
       <c r="N35">
-        <v>-1154.9716124</v>
+        <v>-1197.1010552</v>
       </c>
       <c r="O35">
-        <v>-168.6258554104</v>
+        <v>-174.7767540592</v>
       </c>
       <c r="P35">
-        <v>-986.3457569896001</v>
+        <v>-1022.3243011408</v>
       </c>
       <c r="Q35">
-        <v>-917.7457569896001</v>
+        <v>-953.7243011408002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017169418875042</v>
+        <v>0.1025641682797391</v>
       </c>
       <c r="T35">
-        <v>1.291384339203331</v>
+        <v>1.3109507685852</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02471013555451634</v>
+        <v>0.02398336686173645</v>
       </c>
       <c r="W35">
-        <v>0.2299733500362451</v>
+        <v>0.2301447220940026</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1692475037980571</v>
+        <v>0.1642696360392907</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1459415565765887</v>
+        <v>0.1478415565765887</v>
       </c>
       <c r="C36">
-        <v>1210.513847108645</v>
+        <v>912.7094262792662</v>
       </c>
       <c r="D36">
-        <v>6398.457847108645</v>
+        <v>6279.319426279267</v>
       </c>
       <c r="E36">
-        <v>5741.044</v>
+        <v>5919.71</v>
       </c>
       <c r="F36">
-        <v>6074.644</v>
+        <v>6253.31</v>
       </c>
       <c r="G36">
         <v>886.7</v>
@@ -4227,37 +4227,37 @@
         <v>235.3</v>
       </c>
       <c r="M36">
-        <v>1432.4010552</v>
+        <v>1474.530498</v>
       </c>
       <c r="N36">
-        <v>-1197.1010552</v>
+        <v>-1239.230498</v>
       </c>
       <c r="O36">
-        <v>-174.7767540592</v>
+        <v>-180.927652708</v>
       </c>
       <c r="P36">
-        <v>-1022.3243011408</v>
+        <v>-1058.302845292</v>
       </c>
       <c r="Q36">
-        <v>-953.7243011408002</v>
+        <v>-989.7028452920001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1025641682797391</v>
+        <v>0.1034374631763505</v>
       </c>
       <c r="T36">
-        <v>1.3109507685852</v>
+        <v>1.331119241948049</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02398336686173645</v>
+        <v>0.02329812780854397</v>
       </c>
       <c r="W36">
-        <v>0.2301447220940026</v>
+        <v>0.2303063014627453</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1642696360392907</v>
+        <v>0.1595762178667395</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1478415565765887</v>
+        <v>0.1497415565765887</v>
       </c>
       <c r="C37">
-        <v>912.7094262792662</v>
+        <v>619.2605877026699</v>
       </c>
       <c r="D37">
-        <v>6279.319426279267</v>
+        <v>6164.536587702671</v>
       </c>
       <c r="E37">
-        <v>5919.71</v>
+        <v>6098.376</v>
       </c>
       <c r="F37">
-        <v>6253.31</v>
+        <v>6431.976000000001</v>
       </c>
       <c r="G37">
         <v>886.7</v>
@@ -4309,37 +4309,37 @@
         <v>235.3</v>
       </c>
       <c r="M37">
-        <v>1474.530498</v>
+        <v>1516.6599408</v>
       </c>
       <c r="N37">
-        <v>-1239.230498</v>
+        <v>-1281.3599408</v>
       </c>
       <c r="O37">
-        <v>-180.927652708</v>
+        <v>-187.0785513568</v>
       </c>
       <c r="P37">
-        <v>-1058.302845292</v>
+        <v>-1094.2813894432</v>
       </c>
       <c r="Q37">
-        <v>-989.7028452920001</v>
+        <v>-1025.6813894432</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1034374631763505</v>
+        <v>0.104338048538481</v>
       </c>
       <c r="T37">
-        <v>1.331119241948049</v>
+        <v>1.351917980103487</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02329812780854397</v>
+        <v>0.02265095759163998</v>
       </c>
       <c r="W37">
-        <v>0.2303063014627453</v>
+        <v>0.2304589041998913</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1595762178667395</v>
+        <v>0.1551435451482189</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1497415565765887</v>
+        <v>0.1516415565765887</v>
       </c>
       <c r="C38">
-        <v>619.2605877026708</v>
+        <v>329.9327654895851</v>
       </c>
       <c r="D38">
-        <v>6164.536587702671</v>
+        <v>6053.874765489585</v>
       </c>
       <c r="E38">
-        <v>6098.375999999999</v>
+        <v>6277.041999999999</v>
       </c>
       <c r="F38">
-        <v>6431.976</v>
+        <v>6610.642</v>
       </c>
       <c r="G38">
         <v>886.7</v>
@@ -4391,37 +4391,37 @@
         <v>235.3</v>
       </c>
       <c r="M38">
-        <v>1516.6599408</v>
+        <v>1558.7893836</v>
       </c>
       <c r="N38">
-        <v>-1281.3599408</v>
+        <v>-1323.4893836</v>
       </c>
       <c r="O38">
-        <v>-187.0785513568</v>
+        <v>-193.2294500056</v>
       </c>
       <c r="P38">
-        <v>-1094.2813894432</v>
+        <v>-1130.2599335944</v>
       </c>
       <c r="Q38">
-        <v>-1025.6813894432</v>
+        <v>-1061.6599335944</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.104338048538481</v>
+        <v>0.1052672239121077</v>
       </c>
       <c r="T38">
-        <v>1.351917980103487</v>
+        <v>1.373376995660685</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02265095759163998</v>
+        <v>0.02203876954862268</v>
       </c>
       <c r="W38">
-        <v>0.2304589041998913</v>
+        <v>0.2306032581404348</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.155143545148219</v>
+        <v>0.1509504763604292</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1516415565765887</v>
+        <v>0.1535415565765887</v>
       </c>
       <c r="C39">
-        <v>329.9327654895851</v>
+        <v>44.50793983391759</v>
       </c>
       <c r="D39">
-        <v>6053.874765489585</v>
+        <v>5947.115939833917</v>
       </c>
       <c r="E39">
-        <v>6277.041999999999</v>
+        <v>6455.707999999999</v>
       </c>
       <c r="F39">
-        <v>6610.642</v>
+        <v>6789.307999999999</v>
       </c>
       <c r="G39">
         <v>886.7</v>
@@ -4473,37 +4473,37 @@
         <v>235.3</v>
       </c>
       <c r="M39">
-        <v>1558.7893836</v>
+        <v>1600.9188264</v>
       </c>
       <c r="N39">
-        <v>-1323.4893836</v>
+        <v>-1365.6188264</v>
       </c>
       <c r="O39">
-        <v>-193.2294500056</v>
+        <v>-199.3803486544</v>
       </c>
       <c r="P39">
-        <v>-1130.2599335944</v>
+        <v>-1166.2384777456</v>
       </c>
       <c r="Q39">
-        <v>-1061.6599335944</v>
+        <v>-1097.6384777456</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1052672239121077</v>
+        <v>0.1062263726848836</v>
       </c>
       <c r="T39">
-        <v>1.373376995660685</v>
+        <v>1.39552823752618</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02203876954862268</v>
+        <v>0.02145880192892208</v>
       </c>
       <c r="W39">
-        <v>0.2306032581404348</v>
+        <v>0.2307400145051602</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1509504763604292</v>
+        <v>0.1469780954035759</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1535415565765887</v>
+        <v>0.1554415565765887</v>
       </c>
       <c r="C40">
-        <v>44.50793983391759</v>
+        <v>-237.2167966387933</v>
       </c>
       <c r="D40">
-        <v>5947.115939833917</v>
+        <v>5844.057203361206</v>
       </c>
       <c r="E40">
-        <v>6455.707999999999</v>
+        <v>6634.373999999999</v>
       </c>
       <c r="F40">
-        <v>6789.307999999999</v>
+        <v>6967.973999999999</v>
       </c>
       <c r="G40">
         <v>886.7</v>
@@ -4555,37 +4555,37 @@
         <v>235.3</v>
       </c>
       <c r="M40">
-        <v>1600.9188264</v>
+        <v>1643.0482692</v>
       </c>
       <c r="N40">
-        <v>-1365.6188264</v>
+        <v>-1407.7482692</v>
       </c>
       <c r="O40">
-        <v>-199.3803486544</v>
+        <v>-205.5312473032</v>
       </c>
       <c r="P40">
-        <v>-1166.2384777456</v>
+        <v>-1202.2170218968</v>
       </c>
       <c r="Q40">
-        <v>-1097.6384777456</v>
+        <v>-1133.6170218968</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1062263726848836</v>
+        <v>0.1072169689584063</v>
       </c>
       <c r="T40">
-        <v>1.39552823752618</v>
+        <v>1.418405749616773</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02145880192892208</v>
+        <v>0.0209085762384369</v>
       </c>
       <c r="W40">
-        <v>0.2307400145051602</v>
+        <v>0.2308697577229766</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1469780954035759</v>
+        <v>0.1432094262906637</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1554415565765887</v>
+        <v>0.1573415565765887</v>
       </c>
       <c r="C41">
-        <v>-237.2167966387933</v>
+        <v>-515.4305259979601</v>
       </c>
       <c r="D41">
-        <v>5844.057203361206</v>
+        <v>5744.509474002039</v>
       </c>
       <c r="E41">
-        <v>6634.373999999999</v>
+        <v>6813.039999999999</v>
       </c>
       <c r="F41">
-        <v>6967.973999999999</v>
+        <v>7146.639999999999</v>
       </c>
       <c r="G41">
         <v>886.7</v>
@@ -4637,37 +4637,37 @@
         <v>235.3</v>
       </c>
       <c r="M41">
-        <v>1643.0482692</v>
+        <v>1685.177712</v>
       </c>
       <c r="N41">
-        <v>-1407.7482692</v>
+        <v>-1449.877712</v>
       </c>
       <c r="O41">
-        <v>-205.5312473032</v>
+        <v>-211.682145952</v>
       </c>
       <c r="P41">
-        <v>-1202.2170218968</v>
+        <v>-1238.195566048</v>
       </c>
       <c r="Q41">
-        <v>-1133.6170218968</v>
+        <v>-1169.595566048</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1072169689584063</v>
+        <v>0.108240585107713</v>
       </c>
       <c r="T41">
-        <v>1.418405749616773</v>
+        <v>1.442045845443719</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.0209085762384369</v>
+        <v>0.02038586183247598</v>
       </c>
       <c r="W41">
-        <v>0.2308697577229766</v>
+        <v>0.2309930137799022</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1432094262906637</v>
+        <v>0.1396291906333971</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1573415565765887</v>
+        <v>0.1592415565765887</v>
       </c>
       <c r="C42">
-        <v>-515.4305259979601</v>
+        <v>-790.3096627882269</v>
       </c>
       <c r="D42">
-        <v>5744.509474002039</v>
+        <v>5648.296337211773</v>
       </c>
       <c r="E42">
-        <v>6813.039999999999</v>
+        <v>6991.705999999999</v>
       </c>
       <c r="F42">
-        <v>7146.639999999999</v>
+        <v>7325.306</v>
       </c>
       <c r="G42">
         <v>886.7</v>
@@ -4719,37 +4719,37 @@
         <v>235.3</v>
       </c>
       <c r="M42">
-        <v>1685.177712</v>
+        <v>1727.3071548</v>
       </c>
       <c r="N42">
-        <v>-1449.877712</v>
+        <v>-1492.0071548</v>
       </c>
       <c r="O42">
-        <v>-211.682145952</v>
+        <v>-217.8330446008</v>
       </c>
       <c r="P42">
-        <v>-1238.195566048</v>
+        <v>-1274.1741101992</v>
       </c>
       <c r="Q42">
-        <v>-1169.595566048</v>
+        <v>-1205.5741101992</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.108240585107713</v>
+        <v>0.1092989001095387</v>
       </c>
       <c r="T42">
-        <v>1.442045845443719</v>
+        <v>1.46648730045124</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02038586183247598</v>
+        <v>0.01988864569022047</v>
       </c>
       <c r="W42">
-        <v>0.2309930137799022</v>
+        <v>0.231110257346246</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1396291906333971</v>
+        <v>0.1362236006179484</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1592415565765887</v>
+        <v>0.1611415565765887</v>
       </c>
       <c r="C43">
-        <v>-790.3096627882269</v>
+        <v>-1062.018997378357</v>
       </c>
       <c r="D43">
-        <v>5648.296337211773</v>
+        <v>5555.253002621643</v>
       </c>
       <c r="E43">
-        <v>6991.705999999999</v>
+        <v>7170.371999999999</v>
       </c>
       <c r="F43">
-        <v>7325.306</v>
+        <v>7503.972</v>
       </c>
       <c r="G43">
         <v>886.7</v>
@@ -4801,37 +4801,37 @@
         <v>235.3</v>
       </c>
       <c r="M43">
-        <v>1727.3071548</v>
+        <v>1769.4365976</v>
       </c>
       <c r="N43">
-        <v>-1492.0071548</v>
+        <v>-1534.1365976</v>
       </c>
       <c r="O43">
-        <v>-217.8330446008</v>
+        <v>-223.9839432496</v>
       </c>
       <c r="P43">
-        <v>-1274.1741101992</v>
+        <v>-1310.1526543504</v>
       </c>
       <c r="Q43">
-        <v>-1205.5741101992</v>
+        <v>-1241.5526543504</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1092989001095387</v>
+        <v>0.1103937087321169</v>
       </c>
       <c r="T43">
-        <v>1.46648730045124</v>
+        <v>1.491771564252123</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.01988864569022047</v>
+        <v>0.01941510650711998</v>
       </c>
       <c r="W43">
-        <v>0.231110257346246</v>
+        <v>0.2312219178856211</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1362236006179484</v>
+        <v>0.1329801815556163</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1611415565765887</v>
+        <v>0.1630415565765887</v>
       </c>
       <c r="C44">
-        <v>-1062.018997378356</v>
+        <v>-1330.712637859963</v>
       </c>
       <c r="D44">
-        <v>5555.253002621643</v>
+        <v>5465.225362140036</v>
       </c>
       <c r="E44">
-        <v>7170.371999999998</v>
+        <v>7349.037999999999</v>
       </c>
       <c r="F44">
-        <v>7503.971999999999</v>
+        <v>7682.637999999999</v>
       </c>
       <c r="G44">
         <v>886.7</v>
@@ -4883,37 +4883,37 @@
         <v>235.3</v>
       </c>
       <c r="M44">
-        <v>1769.4365976</v>
+        <v>1811.5660404</v>
       </c>
       <c r="N44">
-        <v>-1534.1365976</v>
+        <v>-1576.2660404</v>
       </c>
       <c r="O44">
-        <v>-223.9839432495999</v>
+        <v>-230.1348418984</v>
       </c>
       <c r="P44">
-        <v>-1310.1526543504</v>
+        <v>-1346.1311985016</v>
       </c>
       <c r="Q44">
-        <v>-1241.5526543504</v>
+        <v>-1277.5311985016</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1103937087321169</v>
+        <v>0.1115269316923295</v>
       </c>
       <c r="T44">
-        <v>1.491771564252123</v>
+        <v>1.517942995203915</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.01941510650711998</v>
+        <v>0.01896359240230324</v>
       </c>
       <c r="W44">
-        <v>0.2312219178856211</v>
+        <v>0.2313283849115369</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1329801815556163</v>
+        <v>0.1298876191938578</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1630415565765887</v>
+        <v>0.1649415565765887</v>
       </c>
       <c r="C45">
-        <v>-1330.712637859963</v>
+        <v>-1596.534861821089</v>
       </c>
       <c r="D45">
-        <v>5465.225362140036</v>
+        <v>5378.06913817891</v>
       </c>
       <c r="E45">
-        <v>7349.037999999999</v>
+        <v>7527.703999999999</v>
       </c>
       <c r="F45">
-        <v>7682.637999999999</v>
+        <v>7861.303999999999</v>
       </c>
       <c r="G45">
         <v>886.7</v>
@@ -4965,37 +4965,37 @@
         <v>235.3</v>
       </c>
       <c r="M45">
-        <v>1811.5660404</v>
+        <v>1853.6954832</v>
       </c>
       <c r="N45">
-        <v>-1576.2660404</v>
+        <v>-1618.3954832</v>
       </c>
       <c r="O45">
-        <v>-230.1348418984</v>
+        <v>-236.2857405472</v>
       </c>
       <c r="P45">
-        <v>-1346.1311985016</v>
+        <v>-1382.1097426528</v>
       </c>
       <c r="Q45">
-        <v>-1277.5311985016</v>
+        <v>-1313.5097426528</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1115269316923295</v>
+        <v>0.1127006269011211</v>
       </c>
       <c r="T45">
-        <v>1.517942995203915</v>
+        <v>1.545049120118271</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.01896359240230324</v>
+        <v>0.01853260166588725</v>
       </c>
       <c r="W45">
-        <v>0.2313283849115369</v>
+        <v>0.2314300125271838</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1298876191938578</v>
+        <v>0.1269356278485428</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1649415565765887</v>
+        <v>0.1668415565765887</v>
       </c>
       <c r="C46">
-        <v>-1596.534861821089</v>
+        <v>-1859.620887897623</v>
       </c>
       <c r="D46">
-        <v>5378.06913817891</v>
+        <v>5293.649112102376</v>
       </c>
       <c r="E46">
-        <v>7527.703999999999</v>
+        <v>7706.369999999999</v>
       </c>
       <c r="F46">
-        <v>7861.303999999999</v>
+        <v>8039.969999999999</v>
       </c>
       <c r="G46">
         <v>886.7</v>
@@ -5047,37 +5047,37 @@
         <v>235.3</v>
       </c>
       <c r="M46">
-        <v>1853.6954832</v>
+        <v>1895.824926</v>
       </c>
       <c r="N46">
-        <v>-1618.3954832</v>
+        <v>-1660.524926</v>
       </c>
       <c r="O46">
-        <v>-236.2857405472</v>
+        <v>-242.436639196</v>
       </c>
       <c r="P46">
-        <v>-1382.1097426528</v>
+        <v>-1418.088286804</v>
       </c>
       <c r="Q46">
-        <v>-1313.5097426528</v>
+        <v>-1349.488286804</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1127006269011211</v>
+        <v>0.113917001935687</v>
       </c>
       <c r="T46">
-        <v>1.545049120118271</v>
+        <v>1.573140922302239</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.01853260166588725</v>
+        <v>0.01812076607331198</v>
       </c>
       <c r="W46">
-        <v>0.2314300125271838</v>
+        <v>0.231527123359913</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1269356278485428</v>
+        <v>0.1241148361185752</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1668415565765887</v>
+        <v>0.1687415565765887</v>
       </c>
       <c r="C47">
-        <v>-1859.620887897623</v>
+        <v>-2120.097575781088</v>
       </c>
       <c r="D47">
-        <v>5293.649112102376</v>
+        <v>5211.838424218912</v>
       </c>
       <c r="E47">
-        <v>7706.369999999999</v>
+        <v>7885.036</v>
       </c>
       <c r="F47">
-        <v>8039.969999999999</v>
+        <v>8218.636</v>
       </c>
       <c r="G47">
         <v>886.7</v>
@@ -5129,37 +5129,37 @@
         <v>235.3</v>
       </c>
       <c r="M47">
-        <v>1895.824926</v>
+        <v>1937.9543688</v>
       </c>
       <c r="N47">
-        <v>-1660.524926</v>
+        <v>-1702.6543688</v>
       </c>
       <c r="O47">
-        <v>-242.436639196</v>
+        <v>-248.5875378448</v>
       </c>
       <c r="P47">
-        <v>-1418.088286804</v>
+        <v>-1454.0668309552</v>
       </c>
       <c r="Q47">
-        <v>-1349.488286804</v>
+        <v>-1385.4668309552</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.113917001935687</v>
+        <v>0.1151784278974589</v>
       </c>
       <c r="T47">
-        <v>1.573140922302239</v>
+        <v>1.602273161604133</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.01812076607331198</v>
+        <v>0.01772683637606607</v>
       </c>
       <c r="W47">
-        <v>0.231527123359913</v>
+        <v>0.2316200119825236</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1241148361185752</v>
+        <v>0.1214166875073018</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1687415565765887</v>
+        <v>0.1706415565765887</v>
       </c>
       <c r="C48">
-        <v>-2120.097575781088</v>
+        <v>-2378.084062304667</v>
       </c>
       <c r="D48">
-        <v>5211.838424218912</v>
+        <v>5132.517937695333</v>
       </c>
       <c r="E48">
-        <v>7885.036</v>
+        <v>8063.701999999999</v>
       </c>
       <c r="F48">
-        <v>8218.636</v>
+        <v>8397.302</v>
       </c>
       <c r="G48">
         <v>886.7</v>
@@ -5211,37 +5211,37 @@
         <v>235.3</v>
       </c>
       <c r="M48">
-        <v>1937.9543688</v>
+        <v>1980.0838116</v>
       </c>
       <c r="N48">
-        <v>-1702.6543688</v>
+        <v>-1744.7838116</v>
       </c>
       <c r="O48">
-        <v>-248.5875378448</v>
+        <v>-254.7384364936</v>
       </c>
       <c r="P48">
-        <v>-1454.0668309552</v>
+        <v>-1490.0453751064</v>
       </c>
       <c r="Q48">
-        <v>-1385.4668309552</v>
+        <v>-1421.4453751064</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1151784278974589</v>
+        <v>0.1164874548389204</v>
       </c>
       <c r="T48">
-        <v>1.602273161604133</v>
+        <v>1.632504730691003</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.01772683637606607</v>
+        <v>0.01734966964466041</v>
       </c>
       <c r="W48">
-        <v>0.2316200119825236</v>
+        <v>0.2317089478977891</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1214166875073018</v>
+        <v>0.1188333537305507</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1706415565765887</v>
+        <v>0.1725415565765887</v>
       </c>
       <c r="C49">
-        <v>-2378.084062304667</v>
+        <v>-2633.692340315339</v>
       </c>
       <c r="D49">
-        <v>5132.517937695333</v>
+        <v>5055.575659684662</v>
       </c>
       <c r="E49">
-        <v>8063.701999999999</v>
+        <v>8242.368</v>
       </c>
       <c r="F49">
-        <v>8397.302</v>
+        <v>8575.968000000001</v>
       </c>
       <c r="G49">
         <v>886.7</v>
@@ -5293,37 +5293,37 @@
         <v>235.3</v>
       </c>
       <c r="M49">
-        <v>1980.0838116</v>
+        <v>2022.2132544</v>
       </c>
       <c r="N49">
-        <v>-1744.7838116</v>
+        <v>-1786.9132544</v>
       </c>
       <c r="O49">
-        <v>-254.7384364936</v>
+        <v>-260.8893351424001</v>
       </c>
       <c r="P49">
-        <v>-1490.0453751064</v>
+        <v>-1526.0239192576</v>
       </c>
       <c r="Q49">
-        <v>-1421.4453751064</v>
+        <v>-1457.4239192576</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1164874548389204</v>
+        <v>0.1178468289704381</v>
       </c>
       <c r="T49">
-        <v>1.632504730691003</v>
+        <v>1.663899052435061</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.01734966964466041</v>
+        <v>0.01698821819372998</v>
       </c>
       <c r="W49">
-        <v>0.2317089478977891</v>
+        <v>0.2317941781499185</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1188333537305507</v>
+        <v>0.1163576588611642</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1725415565765887</v>
+        <v>0.1744415565765887</v>
       </c>
       <c r="C50">
-        <v>-2633.692340315337</v>
+        <v>-2887.027786247314</v>
       </c>
       <c r="D50">
-        <v>5055.575659684662</v>
+        <v>4980.906213752686</v>
       </c>
       <c r="E50">
-        <v>8242.367999999999</v>
+        <v>8421.034</v>
       </c>
       <c r="F50">
-        <v>8575.967999999999</v>
+        <v>8754.634</v>
       </c>
       <c r="G50">
         <v>886.7</v>
@@ -5375,37 +5375,37 @@
         <v>235.3</v>
       </c>
       <c r="M50">
-        <v>2022.2132544</v>
+        <v>2064.3426972</v>
       </c>
       <c r="N50">
-        <v>-1786.9132544</v>
+        <v>-1829.0426972</v>
       </c>
       <c r="O50">
-        <v>-260.8893351423999</v>
+        <v>-267.0402337912</v>
       </c>
       <c r="P50">
-        <v>-1526.0239192576</v>
+        <v>-1562.0024634088</v>
       </c>
       <c r="Q50">
-        <v>-1457.4239192576</v>
+        <v>-1493.4024634088</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1178468289704381</v>
+        <v>0.1192595118914271</v>
       </c>
       <c r="T50">
-        <v>1.663899052435061</v>
+        <v>1.696524524051435</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.01698821819372998</v>
+        <v>0.01664151986324569</v>
       </c>
       <c r="W50">
-        <v>0.2317941781499185</v>
+        <v>0.2318759296162467</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1163576588611642</v>
+        <v>0.1139830127619568</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1744415565765887</v>
+        <v>0.1763415565765887</v>
       </c>
       <c r="C51">
-        <v>-2887.027786247314</v>
+        <v>-3138.189641623282</v>
       </c>
       <c r="D51">
-        <v>4980.906213752686</v>
+        <v>4908.410358376717</v>
       </c>
       <c r="E51">
-        <v>8421.034</v>
+        <v>8599.699999999999</v>
       </c>
       <c r="F51">
-        <v>8754.634</v>
+        <v>8933.299999999999</v>
       </c>
       <c r="G51">
         <v>886.7</v>
@@ -5457,37 +5457,37 @@
         <v>235.3</v>
       </c>
       <c r="M51">
-        <v>2064.3426972</v>
+        <v>2106.47214</v>
       </c>
       <c r="N51">
-        <v>-1829.0426972</v>
+        <v>-1871.17214</v>
       </c>
       <c r="O51">
-        <v>-267.0402337912</v>
+        <v>-273.19113244</v>
       </c>
       <c r="P51">
-        <v>-1562.0024634088</v>
+        <v>-1597.98100756</v>
       </c>
       <c r="Q51">
-        <v>-1493.4024634088</v>
+        <v>-1529.38100756</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1192595118914271</v>
+        <v>0.1207287021292557</v>
       </c>
       <c r="T51">
-        <v>1.696524524051435</v>
+        <v>1.730455014532463</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.01664151986324569</v>
+        <v>0.01630868946598079</v>
       </c>
       <c r="W51">
-        <v>0.2318759296162467</v>
+        <v>0.2319544110239218</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1139830127619568</v>
+        <v>0.1117033525067177</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1763415565765887</v>
+        <v>0.1782415565765887</v>
       </c>
       <c r="C52">
-        <v>-3138.189641623282</v>
+        <v>-3387.271453110083</v>
       </c>
       <c r="D52">
-        <v>4908.410358376717</v>
+        <v>4837.994546889916</v>
       </c>
       <c r="E52">
-        <v>8599.699999999999</v>
+        <v>8778.365999999998</v>
       </c>
       <c r="F52">
-        <v>8933.299999999999</v>
+        <v>9111.965999999999</v>
       </c>
       <c r="G52">
         <v>886.7</v>
@@ -5539,37 +5539,37 @@
         <v>235.3</v>
       </c>
       <c r="M52">
-        <v>2106.47214</v>
+        <v>2148.6015828</v>
       </c>
       <c r="N52">
-        <v>-1871.17214</v>
+        <v>-1913.3015828</v>
       </c>
       <c r="O52">
-        <v>-273.19113244</v>
+        <v>-279.3420310888</v>
       </c>
       <c r="P52">
-        <v>-1597.98100756</v>
+        <v>-1633.9595517112</v>
       </c>
       <c r="Q52">
-        <v>-1529.38100756</v>
+        <v>-1565.3595517112</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1207287021292557</v>
+        <v>0.122257859315567</v>
       </c>
       <c r="T52">
-        <v>1.730455014532463</v>
+        <v>1.765770422992309</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01630868946598079</v>
+        <v>0.01598891124115763</v>
       </c>
       <c r="W52">
-        <v>0.2319544110239218</v>
+        <v>0.232029814729335</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1117033525067177</v>
+        <v>0.1095130906928605</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1782415565765887</v>
+        <v>0.1801415565765887</v>
       </c>
       <c r="C53">
-        <v>-3387.271453110083</v>
+        <v>-3634.361475232012</v>
       </c>
       <c r="D53">
-        <v>4837.994546889916</v>
+        <v>4769.570524767988</v>
       </c>
       <c r="E53">
-        <v>8778.365999999998</v>
+        <v>8957.031999999999</v>
       </c>
       <c r="F53">
-        <v>9111.965999999999</v>
+        <v>9290.632</v>
       </c>
       <c r="G53">
         <v>886.7</v>
@@ -5621,37 +5621,37 @@
         <v>235.3</v>
       </c>
       <c r="M53">
-        <v>2148.6015828</v>
+        <v>2190.7310256</v>
       </c>
       <c r="N53">
-        <v>-1913.3015828</v>
+        <v>-1955.4310256</v>
       </c>
       <c r="O53">
-        <v>-279.3420310888</v>
+        <v>-285.4929297376</v>
       </c>
       <c r="P53">
-        <v>-1633.9595517112</v>
+        <v>-1669.9380958624</v>
       </c>
       <c r="Q53">
-        <v>-1565.3595517112</v>
+        <v>-1601.3380958624</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.122257859315567</v>
+        <v>0.1238507313846413</v>
       </c>
       <c r="T53">
-        <v>1.765770422992309</v>
+        <v>1.802557306804649</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01598891124115763</v>
+        <v>0.01568143217882768</v>
       </c>
       <c r="W53">
-        <v>0.232029814729335</v>
+        <v>0.2321023182922324</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1095130906928605</v>
+        <v>0.1074070697179977</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1801415565765887</v>
+        <v>0.1820415565765887</v>
       </c>
       <c r="C54">
-        <v>-3634.361475232012</v>
+        <v>-3879.543039387101</v>
       </c>
       <c r="D54">
-        <v>4769.570524767988</v>
+        <v>4703.054960612898</v>
       </c>
       <c r="E54">
-        <v>8957.031999999999</v>
+        <v>9135.697999999999</v>
       </c>
       <c r="F54">
-        <v>9290.632</v>
+        <v>9469.297999999999</v>
       </c>
       <c r="G54">
         <v>886.7</v>
@@ -5703,37 +5703,37 @@
         <v>235.3</v>
       </c>
       <c r="M54">
-        <v>2190.7310256</v>
+        <v>2232.8604684</v>
       </c>
       <c r="N54">
-        <v>-1955.4310256</v>
+        <v>-1997.5604684</v>
       </c>
       <c r="O54">
-        <v>-285.4929297376</v>
+        <v>-291.6438283863999</v>
       </c>
       <c r="P54">
-        <v>-1669.9380958624</v>
+        <v>-1705.9166400136</v>
       </c>
       <c r="Q54">
-        <v>-1601.3380958624</v>
+        <v>-1637.3166400136</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1238507313846413</v>
+        <v>0.125511385243889</v>
       </c>
       <c r="T54">
-        <v>1.802557306804649</v>
+        <v>1.840909589928153</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01568143217882768</v>
+        <v>0.01538555609998188</v>
       </c>
       <c r="W54">
-        <v>0.2321023182922324</v>
+        <v>0.2321720858716243</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1074070697179977</v>
+        <v>0.1053805212327525</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1820415565765887</v>
+        <v>0.1839415565765887</v>
       </c>
       <c r="C55">
-        <v>-3879.543039387101</v>
+        <v>-4122.894892410703</v>
       </c>
       <c r="D55">
-        <v>4703.054960612898</v>
+        <v>4638.369107589298</v>
       </c>
       <c r="E55">
-        <v>9135.697999999999</v>
+        <v>9314.364</v>
       </c>
       <c r="F55">
-        <v>9469.297999999999</v>
+        <v>9647.964</v>
       </c>
       <c r="G55">
         <v>886.7</v>
@@ -5785,37 +5785,37 @@
         <v>235.3</v>
       </c>
       <c r="M55">
-        <v>2232.8604684</v>
+        <v>2274.9899112</v>
       </c>
       <c r="N55">
-        <v>-1997.5604684</v>
+        <v>-2039.6899112</v>
       </c>
       <c r="O55">
-        <v>-291.6438283863999</v>
+        <v>-297.7947270352</v>
       </c>
       <c r="P55">
-        <v>-1705.9166400136</v>
+        <v>-1741.8951841648</v>
       </c>
       <c r="Q55">
-        <v>-1637.3166400136</v>
+        <v>-1673.295184164801</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.125511385243889</v>
+        <v>0.1272442414448431</v>
       </c>
       <c r="T55">
-        <v>1.840909589928153</v>
+        <v>1.880929363622243</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01538555609998188</v>
+        <v>0.01510063839442665</v>
       </c>
       <c r="W55">
-        <v>0.2321720858716243</v>
+        <v>0.2322392694665942</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1053805212327525</v>
+        <v>0.1034290300988127</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1839415565765887</v>
+        <v>0.1858415565765887</v>
       </c>
       <c r="C56">
-        <v>-4122.894892410703</v>
+        <v>-4364.491507578492</v>
       </c>
       <c r="D56">
-        <v>4638.369107589298</v>
+        <v>4575.438492421507</v>
       </c>
       <c r="E56">
-        <v>9314.364</v>
+        <v>9493.029999999999</v>
       </c>
       <c r="F56">
-        <v>9647.964</v>
+        <v>9826.629999999999</v>
       </c>
       <c r="G56">
         <v>886.7</v>
@@ -5867,37 +5867,37 @@
         <v>235.3</v>
       </c>
       <c r="M56">
-        <v>2274.9899112</v>
+        <v>2317.119354</v>
       </c>
       <c r="N56">
-        <v>-2039.6899112</v>
+        <v>-2081.819354</v>
       </c>
       <c r="O56">
-        <v>-297.7947270352</v>
+        <v>-303.9456256839999</v>
       </c>
       <c r="P56">
-        <v>-1741.8951841648</v>
+        <v>-1777.873728316</v>
       </c>
       <c r="Q56">
-        <v>-1673.295184164801</v>
+        <v>-1709.273728316</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1272442414448431</v>
+        <v>0.1290541134769507</v>
       </c>
       <c r="T56">
-        <v>1.880929363622243</v>
+        <v>1.922727793924959</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01510063839442665</v>
+        <v>0.01482608133270981</v>
       </c>
       <c r="W56">
-        <v>0.2322392694665942</v>
+        <v>0.232304010021747</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1034290300988127</v>
+        <v>0.1015485022788344</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1858415565765887</v>
+        <v>0.1877415565765887</v>
       </c>
       <c r="C57">
-        <v>-4364.491507578492</v>
+        <v>-4604.403370631361</v>
       </c>
       <c r="D57">
-        <v>4575.438492421507</v>
+        <v>4514.192629368639</v>
       </c>
       <c r="E57">
-        <v>9493.029999999999</v>
+        <v>9671.696</v>
       </c>
       <c r="F57">
-        <v>9826.629999999999</v>
+        <v>10005.296</v>
       </c>
       <c r="G57">
         <v>886.7</v>
@@ -5949,37 +5949,37 @@
         <v>235.3</v>
       </c>
       <c r="M57">
-        <v>2317.119354</v>
+        <v>2359.2487968</v>
       </c>
       <c r="N57">
-        <v>-2081.819354</v>
+        <v>-2123.9487968</v>
       </c>
       <c r="O57">
-        <v>-303.9456256839999</v>
+        <v>-310.0965243328</v>
       </c>
       <c r="P57">
-        <v>-1777.873728316</v>
+        <v>-1813.8522724672</v>
       </c>
       <c r="Q57">
-        <v>-1709.273728316</v>
+        <v>-1745.2522724672</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1290541134769507</v>
+        <v>0.1309462524196087</v>
       </c>
       <c r="T57">
-        <v>1.922727793924959</v>
+        <v>1.966426152877799</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01482608133270981</v>
+        <v>0.01456132988033999</v>
       </c>
       <c r="W57">
-        <v>0.232304010021747</v>
+        <v>0.2323664384142158</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1015485022788344</v>
+        <v>0.09973513616671226</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1877415565765887</v>
+        <v>0.1896415565765887</v>
       </c>
       <c r="C58">
-        <v>-4604.403370631361</v>
+        <v>-4842.697243131709</v>
       </c>
       <c r="D58">
-        <v>4514.192629368639</v>
+        <v>4454.564756868291</v>
       </c>
       <c r="E58">
-        <v>9671.696</v>
+        <v>9850.361999999999</v>
       </c>
       <c r="F58">
-        <v>10005.296</v>
+        <v>10183.962</v>
       </c>
       <c r="G58">
         <v>886.7</v>
@@ -6031,37 +6031,37 @@
         <v>235.3</v>
       </c>
       <c r="M58">
-        <v>2359.2487968</v>
+        <v>2401.3782396</v>
       </c>
       <c r="N58">
-        <v>-2123.9487968</v>
+        <v>-2166.0782396</v>
       </c>
       <c r="O58">
-        <v>-310.0965243328</v>
+        <v>-316.2474229816</v>
       </c>
       <c r="P58">
-        <v>-1813.8522724672</v>
+        <v>-1849.8308166184</v>
       </c>
       <c r="Q58">
-        <v>-1745.2522724672</v>
+        <v>-1781.2308166184</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1309462524196087</v>
+        <v>0.1329263978247159</v>
       </c>
       <c r="T58">
-        <v>1.966426152877799</v>
+        <v>2.0121569936424</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01456132988033999</v>
+        <v>0.01430586795261472</v>
       </c>
       <c r="W58">
-        <v>0.2323664384142158</v>
+        <v>0.2324266763367735</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.09973513616671226</v>
+        <v>0.09798539693571739</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1896415565765887</v>
+        <v>0.1915415565765887</v>
       </c>
       <c r="C59">
-        <v>-4842.697243131709</v>
+        <v>-5079.436405219848</v>
       </c>
       <c r="D59">
-        <v>4454.564756868291</v>
+        <v>4396.491594780153</v>
       </c>
       <c r="E59">
-        <v>9850.361999999999</v>
+        <v>10029.028</v>
       </c>
       <c r="F59">
-        <v>10183.962</v>
+        <v>10362.628</v>
       </c>
       <c r="G59">
         <v>886.7</v>
@@ -6113,37 +6113,37 @@
         <v>235.3</v>
       </c>
       <c r="M59">
-        <v>2401.3782396</v>
+        <v>2443.5076824</v>
       </c>
       <c r="N59">
-        <v>-2166.0782396</v>
+        <v>-2208.2076824</v>
       </c>
       <c r="O59">
-        <v>-316.2474229816</v>
+        <v>-322.3983216304</v>
       </c>
       <c r="P59">
-        <v>-1849.8308166184</v>
+        <v>-1885.8093607696</v>
       </c>
       <c r="Q59">
-        <v>-1781.2308166184</v>
+        <v>-1817.2093607696</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1329263978247159</v>
+        <v>0.1350008358681615</v>
       </c>
       <c r="T59">
-        <v>2.0121569936424</v>
+        <v>2.060065493491028</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01430586795261472</v>
+        <v>0.01405921505687999</v>
       </c>
       <c r="W59">
-        <v>0.2324266763367735</v>
+        <v>0.2324848370895877</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09798539693571739</v>
+        <v>0.09629599354027396</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1915415565765887</v>
+        <v>0.1934415565765887</v>
       </c>
       <c r="C60">
-        <v>-5079.436405219844</v>
+        <v>-5314.680879626195</v>
       </c>
       <c r="D60">
-        <v>4396.491594780155</v>
+        <v>4339.913120373803</v>
       </c>
       <c r="E60">
-        <v>10029.028</v>
+        <v>10207.694</v>
       </c>
       <c r="F60">
-        <v>10362.628</v>
+        <v>10541.294</v>
       </c>
       <c r="G60">
         <v>886.7</v>
@@ -6195,37 +6195,37 @@
         <v>235.3</v>
       </c>
       <c r="M60">
-        <v>2443.5076824</v>
+        <v>2485.637125199999</v>
       </c>
       <c r="N60">
-        <v>-2208.2076824</v>
+        <v>-2250.337125199999</v>
       </c>
       <c r="O60">
-        <v>-322.3983216303999</v>
+        <v>-328.5492202791999</v>
       </c>
       <c r="P60">
-        <v>-1885.8093607696</v>
+        <v>-1921.7879049208</v>
       </c>
       <c r="Q60">
-        <v>-1817.2093607696</v>
+        <v>-1853.1879049208</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1350008358681615</v>
+        <v>0.1371764660112874</v>
       </c>
       <c r="T60">
-        <v>2.060065493491027</v>
+        <v>2.110310993332272</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01405921505687999</v>
+        <v>0.0138209232762549</v>
       </c>
       <c r="W60">
-        <v>0.2324848370895877</v>
+        <v>0.2325410262914591</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09629599354027396</v>
+        <v>0.09466385805654054</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1934415565765887</v>
+        <v>0.1953415565765887</v>
       </c>
       <c r="C61">
-        <v>-5314.680879626195</v>
+        <v>-5548.487638606374</v>
       </c>
       <c r="D61">
-        <v>4339.913120373803</v>
+        <v>4284.772361393625</v>
       </c>
       <c r="E61">
-        <v>10207.694</v>
+        <v>10386.36</v>
       </c>
       <c r="F61">
-        <v>10541.294</v>
+        <v>10719.96</v>
       </c>
       <c r="G61">
         <v>886.7</v>
@@ -6277,37 +6277,37 @@
         <v>235.3</v>
       </c>
       <c r="M61">
-        <v>2485.637125199999</v>
+        <v>2527.766568</v>
       </c>
       <c r="N61">
-        <v>-2250.337125199999</v>
+        <v>-2292.466568</v>
       </c>
       <c r="O61">
-        <v>-328.5492202791999</v>
+        <v>-334.7001189279999</v>
       </c>
       <c r="P61">
-        <v>-1921.7879049208</v>
+        <v>-1957.766449072</v>
       </c>
       <c r="Q61">
-        <v>-1853.1879049208</v>
+        <v>-1889.166449072</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1371764660112874</v>
+        <v>0.1394608776615696</v>
       </c>
       <c r="T61">
-        <v>2.110310993332272</v>
+        <v>2.163068768165579</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0138209232762549</v>
+        <v>0.01359057455498399</v>
       </c>
       <c r="W61">
-        <v>0.2325410262914591</v>
+        <v>0.2325953425199348</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09466385805654054</v>
+        <v>0.09308612708893149</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1953415565765887</v>
+        <v>0.1972415565765887</v>
       </c>
       <c r="C62">
-        <v>-5548.487638606374</v>
+        <v>-5780.910795298902</v>
       </c>
       <c r="D62">
-        <v>4284.772361393625</v>
+        <v>4231.015204701097</v>
       </c>
       <c r="E62">
-        <v>10386.36</v>
+        <v>10565.026</v>
       </c>
       <c r="F62">
-        <v>10719.96</v>
+        <v>10898.626</v>
       </c>
       <c r="G62">
         <v>886.7</v>
@@ -6359,37 +6359,37 @@
         <v>235.3</v>
       </c>
       <c r="M62">
-        <v>2527.766568</v>
+        <v>2569.8960108</v>
       </c>
       <c r="N62">
-        <v>-2292.466568</v>
+        <v>-2334.596010799999</v>
       </c>
       <c r="O62">
-        <v>-334.7001189279999</v>
+        <v>-340.8510175767999</v>
       </c>
       <c r="P62">
-        <v>-1957.766449072</v>
+        <v>-1993.7449932232</v>
       </c>
       <c r="Q62">
-        <v>-1889.166449072</v>
+        <v>-1925.1449932232</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1394608776615696</v>
+        <v>0.1418624386272508</v>
       </c>
       <c r="T62">
-        <v>2.163068768165579</v>
+        <v>2.218532069913414</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01359057455498399</v>
+        <v>0.01336777825080392</v>
       </c>
       <c r="W62">
-        <v>0.2325953425199348</v>
+        <v>0.2326478778884604</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09308612708893149</v>
+        <v>0.09156012500550637</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1972415565765887</v>
+        <v>0.1991415565765887</v>
       </c>
       <c r="C63">
-        <v>-5780.910795298902</v>
+        <v>-6012.001780856662</v>
       </c>
       <c r="D63">
-        <v>4231.015204701097</v>
+        <v>4178.590219143338</v>
       </c>
       <c r="E63">
-        <v>10565.026</v>
+        <v>10743.692</v>
       </c>
       <c r="F63">
-        <v>10898.626</v>
+        <v>11077.292</v>
       </c>
       <c r="G63">
         <v>886.7</v>
@@ -6441,37 +6441,37 @@
         <v>235.3</v>
       </c>
       <c r="M63">
-        <v>2569.8960108</v>
+        <v>2612.0254536</v>
       </c>
       <c r="N63">
-        <v>-2334.596010799999</v>
+        <v>-2376.7254536</v>
       </c>
       <c r="O63">
-        <v>-340.8510175767999</v>
+        <v>-347.0019162255999</v>
       </c>
       <c r="P63">
-        <v>-1993.7449932232</v>
+        <v>-2029.7235373744</v>
       </c>
       <c r="Q63">
-        <v>-1925.1449932232</v>
+        <v>-1961.1235373744</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1418624386272508</v>
+        <v>0.1443903975384943</v>
       </c>
       <c r="T63">
-        <v>2.218532069913414</v>
+        <v>2.276914492805873</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01336777825080392</v>
+        <v>0.01315216892417805</v>
       </c>
       <c r="W63">
-        <v>0.2326478778884604</v>
+        <v>0.2326987185676788</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09156012500550637</v>
+        <v>0.0900833487957402</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1991415565765887</v>
+        <v>0.2010415565765887</v>
       </c>
       <c r="C64">
-        <v>-6012.001780856662</v>
+        <v>-6241.809508570886</v>
       </c>
       <c r="D64">
-        <v>4178.590219143338</v>
+        <v>4127.448491429112</v>
       </c>
       <c r="E64">
-        <v>10743.692</v>
+        <v>10922.358</v>
       </c>
       <c r="F64">
-        <v>11077.292</v>
+        <v>11255.958</v>
       </c>
       <c r="G64">
         <v>886.7</v>
@@ -6523,37 +6523,37 @@
         <v>235.3</v>
       </c>
       <c r="M64">
-        <v>2612.0254536</v>
+        <v>2654.1548964</v>
       </c>
       <c r="N64">
-        <v>-2376.7254536</v>
+        <v>-2418.8548964</v>
       </c>
       <c r="O64">
-        <v>-347.0019162255999</v>
+        <v>-353.1528148744</v>
       </c>
       <c r="P64">
-        <v>-2029.7235373744</v>
+        <v>-2065.7020815256</v>
       </c>
       <c r="Q64">
-        <v>-1961.1235373744</v>
+        <v>-1997.1020815256</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1443903975384943</v>
+        <v>0.1470550028773725</v>
       </c>
       <c r="T64">
-        <v>2.276914492805873</v>
+        <v>2.338452722341167</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01315216892417805</v>
+        <v>0.01294340433807999</v>
       </c>
       <c r="W64">
-        <v>0.2326987185676788</v>
+        <v>0.2327479452570808</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0900833487957402</v>
+        <v>0.08865345437041094</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2010415565765887</v>
+        <v>0.2029415565765887</v>
       </c>
       <c r="C65">
-        <v>-6241.809508570886</v>
+        <v>-6470.380526088599</v>
       </c>
       <c r="D65">
-        <v>4127.448491429112</v>
+        <v>4077.5434739114</v>
       </c>
       <c r="E65">
-        <v>10922.358</v>
+        <v>11101.024</v>
       </c>
       <c r="F65">
-        <v>11255.958</v>
+        <v>11434.624</v>
       </c>
       <c r="G65">
         <v>886.7</v>
@@ -6605,37 +6605,37 @@
         <v>235.3</v>
       </c>
       <c r="M65">
-        <v>2654.1548964</v>
+        <v>2696.2843392</v>
       </c>
       <c r="N65">
-        <v>-2418.8548964</v>
+        <v>-2460.9843392</v>
       </c>
       <c r="O65">
-        <v>-353.1528148744</v>
+        <v>-359.3037135232</v>
       </c>
       <c r="P65">
-        <v>-2065.7020815256</v>
+        <v>-2101.6806256768</v>
       </c>
       <c r="Q65">
-        <v>-1997.1020815256</v>
+        <v>-2033.0806256768</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1470550028773725</v>
+        <v>0.1498676418461884</v>
       </c>
       <c r="T65">
-        <v>2.338452722341167</v>
+        <v>2.403409742406199</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01294340433807999</v>
+        <v>0.01274116364529749</v>
       </c>
       <c r="W65">
-        <v>0.2327479452570808</v>
+        <v>0.2327956336124389</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.08865345437041094</v>
+        <v>0.08726824414587331</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2029415565765887</v>
+        <v>0.2048415565765887</v>
       </c>
       <c r="C66">
-        <v>-6470.380526088599</v>
+        <v>-6697.759156719203</v>
       </c>
       <c r="D66">
-        <v>4077.5434739114</v>
+        <v>4028.830843280796</v>
       </c>
       <c r="E66">
-        <v>11101.024</v>
+        <v>11279.69</v>
       </c>
       <c r="F66">
-        <v>11434.624</v>
+        <v>11613.29</v>
       </c>
       <c r="G66">
         <v>886.7</v>
@@ -6687,37 +6687,37 @@
         <v>235.3</v>
       </c>
       <c r="M66">
-        <v>2696.2843392</v>
+        <v>2738.413782</v>
       </c>
       <c r="N66">
-        <v>-2460.9843392</v>
+        <v>-2503.113782</v>
       </c>
       <c r="O66">
-        <v>-359.3037135232</v>
+        <v>-365.4546121719999</v>
       </c>
       <c r="P66">
-        <v>-2101.6806256768</v>
+        <v>-2137.659169828</v>
       </c>
       <c r="Q66">
-        <v>-2033.0806256768</v>
+        <v>-2069.059169828</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1498676418461884</v>
+        <v>0.1528410030417938</v>
       </c>
       <c r="T66">
-        <v>2.403409742406199</v>
+        <v>2.472078592189234</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01274116364529749</v>
+        <v>0.01254514574306214</v>
       </c>
       <c r="W66">
-        <v>0.2327956336124389</v>
+        <v>0.232841854633786</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08726824414587331</v>
+        <v>0.08592565577439826</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2048415565765887</v>
+        <v>0.2067415565765887</v>
       </c>
       <c r="C67">
-        <v>-6697.759156719203</v>
+        <v>-6923.987630731878</v>
       </c>
       <c r="D67">
-        <v>4028.830843280796</v>
+        <v>3981.268369268122</v>
       </c>
       <c r="E67">
-        <v>11279.69</v>
+        <v>11458.356</v>
       </c>
       <c r="F67">
-        <v>11613.29</v>
+        <v>11791.956</v>
       </c>
       <c r="G67">
         <v>886.7</v>
@@ -6769,37 +6769,37 @@
         <v>235.3</v>
       </c>
       <c r="M67">
-        <v>2738.413782</v>
+        <v>2780.5432248</v>
       </c>
       <c r="N67">
-        <v>-2503.113782</v>
+        <v>-2545.2432248</v>
       </c>
       <c r="O67">
-        <v>-365.4546121719999</v>
+        <v>-371.6055108208</v>
       </c>
       <c r="P67">
-        <v>-2137.659169828</v>
+        <v>-2173.6377139792</v>
       </c>
       <c r="Q67">
-        <v>-2069.059169828</v>
+        <v>-2105.0377139792</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1528410030417938</v>
+        <v>0.1559892678371407</v>
       </c>
       <c r="T67">
-        <v>2.472078592189234</v>
+        <v>2.544786786077152</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01254514574306214</v>
+        <v>0.01235506777725817</v>
       </c>
       <c r="W67">
-        <v>0.232841854633786</v>
+        <v>0.2328866750181225</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08592565577439826</v>
+        <v>0.0846237518990286</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2067415565765887</v>
+        <v>0.2086415565765887</v>
       </c>
       <c r="C68">
-        <v>-6923.987630731878</v>
+        <v>-7149.106207461283</v>
       </c>
       <c r="D68">
-        <v>3981.268369268122</v>
+        <v>3934.815792538716</v>
       </c>
       <c r="E68">
-        <v>11458.356</v>
+        <v>11637.022</v>
       </c>
       <c r="F68">
-        <v>11791.956</v>
+        <v>11970.622</v>
       </c>
       <c r="G68">
         <v>886.7</v>
@@ -6851,37 +6851,37 @@
         <v>235.3</v>
       </c>
       <c r="M68">
-        <v>2780.5432248</v>
+        <v>2822.6726676</v>
       </c>
       <c r="N68">
-        <v>-2545.2432248</v>
+        <v>-2587.3726676</v>
       </c>
       <c r="O68">
-        <v>-371.6055108208</v>
+        <v>-377.7564094695999</v>
       </c>
       <c r="P68">
-        <v>-2173.6377139792</v>
+        <v>-2209.6162581304</v>
       </c>
       <c r="Q68">
-        <v>-2105.0377139792</v>
+        <v>-2141.0162581304</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1559892678371407</v>
+        <v>0.1593283365594783</v>
       </c>
       <c r="T68">
-        <v>2.544786786077152</v>
+        <v>2.621901537170399</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01235506777725817</v>
+        <v>0.01217066378058267</v>
       </c>
       <c r="W68">
-        <v>0.2328866750181225</v>
+        <v>0.2329301574805386</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.0846237518990286</v>
+        <v>0.08336071082590879</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2086415565765887</v>
+        <v>0.2105415565765887</v>
       </c>
       <c r="C69">
-        <v>-7149.106207461283</v>
+        <v>-7373.153288963618</v>
       </c>
       <c r="D69">
-        <v>3934.815792538716</v>
+        <v>3889.434711036382</v>
       </c>
       <c r="E69">
-        <v>11637.022</v>
+        <v>11815.688</v>
       </c>
       <c r="F69">
-        <v>11970.622</v>
+        <v>12149.288</v>
       </c>
       <c r="G69">
         <v>886.7</v>
@@ -6933,37 +6933,37 @@
         <v>235.3</v>
       </c>
       <c r="M69">
-        <v>2822.6726676</v>
+        <v>2864.8021104</v>
       </c>
       <c r="N69">
-        <v>-2587.3726676</v>
+        <v>-2629.5021104</v>
       </c>
       <c r="O69">
-        <v>-377.7564094695999</v>
+        <v>-383.9073081184</v>
       </c>
       <c r="P69">
-        <v>-2209.6162581304</v>
+        <v>-2245.5948022816</v>
       </c>
       <c r="Q69">
-        <v>-2141.0162581304</v>
+        <v>-2176.9948022816</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1593283365594783</v>
+        <v>0.162876097076962</v>
       </c>
       <c r="T69">
-        <v>2.621901537170399</v>
+        <v>2.703835960206974</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01217066378058267</v>
+        <v>0.01199168343086822</v>
       </c>
       <c r="W69">
-        <v>0.2329301574805386</v>
+        <v>0.2329723610470013</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08336071082590879</v>
+        <v>0.08213481801964539</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2105415565765887</v>
+        <v>0.2124415565765887</v>
       </c>
       <c r="C70">
-        <v>-7373.153288963618</v>
+        <v>-7596.165525897456</v>
       </c>
       <c r="D70">
-        <v>3889.434711036382</v>
+        <v>3845.088474102543</v>
       </c>
       <c r="E70">
-        <v>11815.688</v>
+        <v>11994.354</v>
       </c>
       <c r="F70">
-        <v>12149.288</v>
+        <v>12327.954</v>
       </c>
       <c r="G70">
         <v>886.7</v>
@@ -7015,37 +7015,37 @@
         <v>235.3</v>
       </c>
       <c r="M70">
-        <v>2864.8021104</v>
+        <v>2906.9315532</v>
       </c>
       <c r="N70">
-        <v>-2629.5021104</v>
+        <v>-2671.6315532</v>
       </c>
       <c r="O70">
-        <v>-383.9073081184</v>
+        <v>-390.0582067672</v>
       </c>
       <c r="P70">
-        <v>-2245.5948022816</v>
+        <v>-2281.5733464328</v>
       </c>
       <c r="Q70">
-        <v>-2176.9948022816</v>
+        <v>-2212.9733464328</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.162876097076962</v>
+        <v>0.1666527453697672</v>
       </c>
       <c r="T70">
-        <v>2.703835960206974</v>
+        <v>2.791056475052361</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01199168343086822</v>
+        <v>0.01181789091737738</v>
       </c>
       <c r="W70">
-        <v>0.2329723610470013</v>
+        <v>0.2330133413216824</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08213481801964539</v>
+        <v>0.0809444583382013</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2124415565765887</v>
+        <v>0.2143415565765887</v>
       </c>
       <c r="C71">
-        <v>-7596.165525897456</v>
+        <v>-7818.177916242886</v>
       </c>
       <c r="D71">
-        <v>3845.088474102543</v>
+        <v>3801.742083757115</v>
       </c>
       <c r="E71">
-        <v>11994.354</v>
+        <v>12173.02</v>
       </c>
       <c r="F71">
-        <v>12327.954</v>
+        <v>12506.62</v>
       </c>
       <c r="G71">
         <v>886.7</v>
@@ -7097,37 +7097,37 @@
         <v>235.3</v>
       </c>
       <c r="M71">
-        <v>2906.9315532</v>
+        <v>2949.060996</v>
       </c>
       <c r="N71">
-        <v>-2671.6315532</v>
+        <v>-2713.760996</v>
       </c>
       <c r="O71">
-        <v>-390.0582067672</v>
+        <v>-396.209105416</v>
       </c>
       <c r="P71">
-        <v>-2281.5733464328</v>
+        <v>-2317.551890584</v>
       </c>
       <c r="Q71">
-        <v>-2212.9733464328</v>
+        <v>-2248.951890584</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1666527453697672</v>
+        <v>0.1706811702154261</v>
       </c>
       <c r="T71">
-        <v>2.791056475052361</v>
+        <v>2.884091690887439</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01181789091737738</v>
+        <v>0.01164906390427199</v>
       </c>
       <c r="W71">
-        <v>0.2330133413216824</v>
+        <v>0.2330531507313727</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0809444583382013</v>
+        <v>0.07978810893336985</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2143415565765887</v>
+        <v>0.2162415565765887</v>
       </c>
       <c r="C72">
-        <v>-7818.177916242886</v>
+        <v>-8039.223897417796</v>
       </c>
       <c r="D72">
-        <v>3801.742083757115</v>
+        <v>3759.362102582204</v>
       </c>
       <c r="E72">
-        <v>12173.02</v>
+        <v>12351.686</v>
       </c>
       <c r="F72">
-        <v>12506.62</v>
+        <v>12685.286</v>
       </c>
       <c r="G72">
         <v>886.7</v>
@@ -7179,37 +7179,37 @@
         <v>235.3</v>
       </c>
       <c r="M72">
-        <v>2949.060996</v>
+        <v>2991.1904388</v>
       </c>
       <c r="N72">
-        <v>-2713.760996</v>
+        <v>-2755.8904388</v>
       </c>
       <c r="O72">
-        <v>-396.209105416</v>
+        <v>-402.3600040648</v>
       </c>
       <c r="P72">
-        <v>-2317.551890584</v>
+        <v>-2353.5304347352</v>
       </c>
       <c r="Q72">
-        <v>-2248.951890584</v>
+        <v>-2284.9304347352</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1706811702154261</v>
+        <v>0.1749874174642339</v>
       </c>
       <c r="T72">
-        <v>2.884091690887439</v>
+        <v>2.983543128504248</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01164906390427199</v>
+        <v>0.01148499258167661</v>
       </c>
       <c r="W72">
-        <v>0.2330531507313727</v>
+        <v>0.2330918387492407</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.07978810893336985</v>
+        <v>0.07866433275120965</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2162415565765887</v>
+        <v>0.2181415565765887</v>
       </c>
       <c r="C73">
-        <v>-8039.223897417793</v>
+        <v>-8259.335432300912</v>
       </c>
       <c r="D73">
-        <v>3759.362102582206</v>
+        <v>3717.916567699086</v>
       </c>
       <c r="E73">
-        <v>12351.686</v>
+        <v>12530.352</v>
       </c>
       <c r="F73">
-        <v>12685.286</v>
+        <v>12863.952</v>
       </c>
       <c r="G73">
         <v>886.7</v>
@@ -7261,37 +7261,37 @@
         <v>235.3</v>
       </c>
       <c r="M73">
-        <v>2991.1904388</v>
+        <v>3033.3198816</v>
       </c>
       <c r="N73">
-        <v>-2755.8904388</v>
+        <v>-2798.0198816</v>
       </c>
       <c r="O73">
-        <v>-402.3600040647999</v>
+        <v>-408.5109027135999</v>
       </c>
       <c r="P73">
-        <v>-2353.5304347352</v>
+        <v>-2389.5089788864</v>
       </c>
       <c r="Q73">
-        <v>-2284.9304347352</v>
+        <v>-2320.9089788864</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1749874174642339</v>
+        <v>0.1796012538022422</v>
       </c>
       <c r="T73">
-        <v>2.983543128504247</v>
+        <v>3.090098240236541</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01148499258167661</v>
+        <v>0.01132547879581999</v>
       </c>
       <c r="W73">
-        <v>0.2330918387492407</v>
+        <v>0.2331294520999456</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07866433275120976</v>
+        <v>0.07757177257410963</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2181415565765887</v>
+        <v>0.2200415565765887</v>
       </c>
       <c r="C74">
-        <v>-8259.335432300912</v>
+        <v>-8478.543089626637</v>
       </c>
       <c r="D74">
-        <v>3717.916567699086</v>
+        <v>3677.374910373362</v>
       </c>
       <c r="E74">
-        <v>12530.352</v>
+        <v>12709.018</v>
       </c>
       <c r="F74">
-        <v>12863.952</v>
+        <v>13042.618</v>
       </c>
       <c r="G74">
         <v>886.7</v>
@@ -7343,37 +7343,37 @@
         <v>235.3</v>
       </c>
       <c r="M74">
-        <v>3033.3198816</v>
+        <v>3075.4493244</v>
       </c>
       <c r="N74">
-        <v>-2798.0198816</v>
+        <v>-2840.149324399999</v>
       </c>
       <c r="O74">
-        <v>-408.5109027135999</v>
+        <v>-414.6618013623999</v>
       </c>
       <c r="P74">
-        <v>-2389.5089788864</v>
+        <v>-2425.4875230376</v>
       </c>
       <c r="Q74">
-        <v>-2320.9089788864</v>
+        <v>-2356.8875230376</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1796012538022422</v>
+        <v>0.1845568557949179</v>
       </c>
       <c r="T74">
-        <v>3.090098240236541</v>
+        <v>3.204546323208265</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01132547879581999</v>
+        <v>0.01117033525067177</v>
       </c>
       <c r="W74">
-        <v>0.2331294520999456</v>
+        <v>0.2331660349478916</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07757177257410963</v>
+        <v>0.0765091455525464</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2200415565765887</v>
+        <v>0.2219415565765887</v>
       </c>
       <c r="C75">
-        <v>-8478.543089626637</v>
+        <v>-8696.876119176653</v>
       </c>
       <c r="D75">
-        <v>3677.374910373362</v>
+        <v>3637.707880823347</v>
       </c>
       <c r="E75">
-        <v>12709.018</v>
+        <v>12887.684</v>
       </c>
       <c r="F75">
-        <v>13042.618</v>
+        <v>13221.284</v>
       </c>
       <c r="G75">
         <v>886.7</v>
@@ -7425,37 +7425,37 @@
         <v>235.3</v>
       </c>
       <c r="M75">
-        <v>3075.4493244</v>
+        <v>3117.5787672</v>
       </c>
       <c r="N75">
-        <v>-2840.149324399999</v>
+        <v>-2882.2787672</v>
       </c>
       <c r="O75">
-        <v>-414.6618013623999</v>
+        <v>-420.8127000112</v>
       </c>
       <c r="P75">
-        <v>-2425.4875230376</v>
+        <v>-2461.4660671888</v>
       </c>
       <c r="Q75">
-        <v>-2356.8875230376</v>
+        <v>-2392.8660671888</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1845568557949179</v>
+        <v>0.1898936579408763</v>
       </c>
       <c r="T75">
-        <v>3.204546323208265</v>
+        <v>3.327798104870122</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01117033525067177</v>
+        <v>0.01101938477431134</v>
       </c>
       <c r="W75">
-        <v>0.2331660349478916</v>
+        <v>0.2332016290702174</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.0765091455525464</v>
+        <v>0.07547523818021473</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2219415565765887</v>
+        <v>0.2238415565765887</v>
       </c>
       <c r="C76">
-        <v>-8696.876119176653</v>
+        <v>-8914.362522157069</v>
       </c>
       <c r="D76">
-        <v>3637.707880823347</v>
+        <v>3598.887477842929</v>
       </c>
       <c r="E76">
-        <v>12887.684</v>
+        <v>13066.35</v>
       </c>
       <c r="F76">
-        <v>13221.284</v>
+        <v>13399.95</v>
       </c>
       <c r="G76">
         <v>886.7</v>
@@ -7507,37 +7507,37 @@
         <v>235.3</v>
       </c>
       <c r="M76">
-        <v>3117.5787672</v>
+        <v>3159.70821</v>
       </c>
       <c r="N76">
-        <v>-2882.2787672</v>
+        <v>-2924.40821</v>
       </c>
       <c r="O76">
-        <v>-420.8127000112</v>
+        <v>-426.9635986599999</v>
       </c>
       <c r="P76">
-        <v>-2461.4660671888</v>
+        <v>-2497.44461134</v>
       </c>
       <c r="Q76">
-        <v>-2392.8660671888</v>
+        <v>-2428.84461134</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1898936579408763</v>
+        <v>0.1956574042585113</v>
       </c>
       <c r="T76">
-        <v>3.327798104870122</v>
+        <v>3.460910029064927</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01101938477431134</v>
+        <v>0.01087245964398719</v>
       </c>
       <c r="W76">
-        <v>0.2332016290702174</v>
+        <v>0.2332362740159478</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07547523818021473</v>
+        <v>0.07446890167114517</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2238415565765887</v>
+        <v>0.2257415565765887</v>
       </c>
       <c r="C77">
-        <v>-8914.362522157069</v>
+        <v>-9131.029117116861</v>
       </c>
       <c r="D77">
-        <v>3598.887477842929</v>
+        <v>3560.886882883137</v>
       </c>
       <c r="E77">
-        <v>13066.35</v>
+        <v>13245.016</v>
       </c>
       <c r="F77">
-        <v>13399.95</v>
+        <v>13578.616</v>
       </c>
       <c r="G77">
         <v>886.7</v>
@@ -7589,37 +7589,37 @@
         <v>235.3</v>
       </c>
       <c r="M77">
-        <v>3159.70821</v>
+        <v>3201.8376528</v>
       </c>
       <c r="N77">
-        <v>-2924.40821</v>
+        <v>-2966.5376528</v>
       </c>
       <c r="O77">
-        <v>-426.9635986599999</v>
+        <v>-433.1144973087999</v>
       </c>
       <c r="P77">
-        <v>-2497.44461134</v>
+        <v>-2533.4231554912</v>
       </c>
       <c r="Q77">
-        <v>-2428.84461134</v>
+        <v>-2464.8231554912</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1956574042585113</v>
+        <v>0.2019014627692826</v>
       </c>
       <c r="T77">
-        <v>3.460910029064927</v>
+        <v>3.605114613609299</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01087245964398719</v>
+        <v>0.01072940096446104</v>
       </c>
       <c r="W77">
-        <v>0.2332362740159478</v>
+        <v>0.2332700072525801</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07446890167114517</v>
+        <v>0.07348904770178799</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2257415565765887</v>
+        <v>0.2276415565765887</v>
       </c>
       <c r="C78">
-        <v>-9131.029117116861</v>
+        <v>-9346.901601733753</v>
       </c>
       <c r="D78">
-        <v>3560.886882883137</v>
+        <v>3523.680398266246</v>
       </c>
       <c r="E78">
-        <v>13245.016</v>
+        <v>13423.682</v>
       </c>
       <c r="F78">
-        <v>13578.616</v>
+        <v>13757.282</v>
       </c>
       <c r="G78">
         <v>886.7</v>
@@ -7671,37 +7671,37 @@
         <v>235.3</v>
       </c>
       <c r="M78">
-        <v>3201.8376528</v>
+        <v>3243.9670956</v>
       </c>
       <c r="N78">
-        <v>-2966.5376528</v>
+        <v>-3008.6670956</v>
       </c>
       <c r="O78">
-        <v>-433.1144973087999</v>
+        <v>-439.2653959575999</v>
       </c>
       <c r="P78">
-        <v>-2533.4231554912</v>
+        <v>-2569.4016996424</v>
       </c>
       <c r="Q78">
-        <v>-2464.8231554912</v>
+        <v>-2500.8016996424</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2019014627692826</v>
+        <v>0.2086884828896862</v>
       </c>
       <c r="T78">
-        <v>3.605114613609299</v>
+        <v>3.761858727244485</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01072940096446104</v>
+        <v>0.01059005809479272</v>
       </c>
       <c r="W78">
-        <v>0.2332700072525801</v>
+        <v>0.2333028643012479</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07348904770178799</v>
+        <v>0.07253464448488167</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2276415565765887</v>
+        <v>0.2295415565765887</v>
       </c>
       <c r="C79">
-        <v>-9346.901601733753</v>
+        <v>-9562.004610766684</v>
       </c>
       <c r="D79">
-        <v>3523.680398266246</v>
+        <v>3487.243389233314</v>
       </c>
       <c r="E79">
-        <v>13423.682</v>
+        <v>13602.348</v>
       </c>
       <c r="F79">
-        <v>13757.282</v>
+        <v>13935.948</v>
       </c>
       <c r="G79">
         <v>886.7</v>
@@ -7753,37 +7753,37 @@
         <v>235.3</v>
       </c>
       <c r="M79">
-        <v>3243.9670956</v>
+        <v>3286.0965384</v>
       </c>
       <c r="N79">
-        <v>-3008.6670956</v>
+        <v>-3050.796538399999</v>
       </c>
       <c r="O79">
-        <v>-439.2653959575999</v>
+        <v>-445.4162946063999</v>
       </c>
       <c r="P79">
-        <v>-2569.4016996424</v>
+        <v>-2605.3802437936</v>
       </c>
       <c r="Q79">
-        <v>-2500.8016996424</v>
+        <v>-2536.7802437936</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2086884828896862</v>
+        <v>0.2160925048392174</v>
       </c>
       <c r="T79">
-        <v>3.761858727244485</v>
+        <v>3.932852305755599</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01059005809479272</v>
+        <v>0.01045428811921845</v>
       </c>
       <c r="W79">
-        <v>0.2333028643012479</v>
+        <v>0.2333348788614883</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07253464448488167</v>
+        <v>0.0716047131453319</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2295415565765887</v>
+        <v>0.2314415565765887</v>
       </c>
       <c r="C80">
-        <v>-9562.004610766684</v>
+        <v>-9776.361770449508</v>
       </c>
       <c r="D80">
-        <v>3487.243389233314</v>
+        <v>3451.552229550492</v>
       </c>
       <c r="E80">
-        <v>13602.348</v>
+        <v>13781.014</v>
       </c>
       <c r="F80">
-        <v>13935.948</v>
+        <v>14114.614</v>
       </c>
       <c r="G80">
         <v>886.7</v>
@@ -7835,37 +7835,37 @@
         <v>235.3</v>
       </c>
       <c r="M80">
-        <v>3286.0965384</v>
+        <v>3328.2259812</v>
       </c>
       <c r="N80">
-        <v>-3050.796538399999</v>
+        <v>-3092.9259812</v>
       </c>
       <c r="O80">
-        <v>-445.4162946063999</v>
+        <v>-451.5671932552</v>
       </c>
       <c r="P80">
-        <v>-2605.3802437936</v>
+        <v>-2641.3587879448</v>
       </c>
       <c r="Q80">
-        <v>-2536.7802437936</v>
+        <v>-2572.7587879448</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2160925048392174</v>
+        <v>0.224201671736323</v>
       </c>
       <c r="T80">
-        <v>3.932852305755599</v>
+        <v>4.120130986982056</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01045428811921845</v>
+        <v>0.01032195535821569</v>
       </c>
       <c r="W80">
-        <v>0.2333348788614883</v>
+        <v>0.2333660829265327</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.0716047131453319</v>
+        <v>0.07069832437134038</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2314415565765887</v>
+        <v>0.2333415565765887</v>
       </c>
       <c r="C81">
-        <v>-9776.361770449508</v>
+        <v>-9989.995749578269</v>
       </c>
       <c r="D81">
-        <v>3451.552229550492</v>
+        <v>3416.58425042173</v>
       </c>
       <c r="E81">
-        <v>13781.014</v>
+        <v>13959.68</v>
       </c>
       <c r="F81">
-        <v>14114.614</v>
+        <v>14293.28</v>
       </c>
       <c r="G81">
         <v>886.7</v>
@@ -7917,37 +7917,37 @@
         <v>235.3</v>
       </c>
       <c r="M81">
-        <v>3328.2259812</v>
+        <v>3370.355424</v>
       </c>
       <c r="N81">
-        <v>-3092.9259812</v>
+        <v>-3135.055424</v>
       </c>
       <c r="O81">
-        <v>-451.5671932552</v>
+        <v>-457.7180919039999</v>
       </c>
       <c r="P81">
-        <v>-2641.3587879448</v>
+        <v>-2677.337332096</v>
       </c>
       <c r="Q81">
-        <v>-2572.7587879448</v>
+        <v>-2608.737332096</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.224201671736323</v>
+        <v>0.2331217553231391</v>
       </c>
       <c r="T81">
-        <v>4.120130986982056</v>
+        <v>4.326137536331158</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01032195535821569</v>
+        <v>0.01019293091623799</v>
       </c>
       <c r="W81">
-        <v>0.2333660829265327</v>
+        <v>0.2333965068899511</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07069832437134038</v>
+        <v>0.06981459531669865</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2333415565765887</v>
+        <v>0.2352415565765887</v>
       </c>
       <c r="C82">
-        <v>-9989.995749578269</v>
+        <v>-10202.92830752421</v>
       </c>
       <c r="D82">
-        <v>3416.58425042173</v>
+        <v>3382.317692475787</v>
       </c>
       <c r="E82">
-        <v>13959.68</v>
+        <v>14138.346</v>
       </c>
       <c r="F82">
-        <v>14293.28</v>
+        <v>14471.946</v>
       </c>
       <c r="G82">
         <v>886.7</v>
@@ -7999,37 +7999,37 @@
         <v>235.3</v>
       </c>
       <c r="M82">
-        <v>3370.355424</v>
+        <v>3412.4848668</v>
       </c>
       <c r="N82">
-        <v>-3135.055424</v>
+        <v>-3177.1848668</v>
       </c>
       <c r="O82">
-        <v>-457.7180919039999</v>
+        <v>-463.8689905527999</v>
       </c>
       <c r="P82">
-        <v>-2677.337332096</v>
+        <v>-2713.3158762472</v>
       </c>
       <c r="Q82">
-        <v>-2608.737332096</v>
+        <v>-2644.7158762472</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2331217553231391</v>
+        <v>0.2429807950769886</v>
       </c>
       <c r="T82">
-        <v>4.326137536331158</v>
+        <v>4.553828985611747</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01019293091623799</v>
+        <v>0.0100670922629511</v>
       </c>
       <c r="W82">
-        <v>0.2333965068899511</v>
+        <v>0.2334261796443961</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.06981459531669865</v>
+        <v>0.06895268673254185</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2352415565765887</v>
+        <v>0.2371415565765887</v>
       </c>
       <c r="C83">
-        <v>-10202.92830752421</v>
+        <v>-10415.1803393862</v>
       </c>
       <c r="D83">
-        <v>3382.317692475787</v>
+        <v>3348.731660613795</v>
       </c>
       <c r="E83">
-        <v>14138.346</v>
+        <v>14317.012</v>
       </c>
       <c r="F83">
-        <v>14471.946</v>
+        <v>14650.612</v>
       </c>
       <c r="G83">
         <v>886.7</v>
@@ -8081,37 +8081,37 @@
         <v>235.3</v>
       </c>
       <c r="M83">
-        <v>3412.4848668</v>
+        <v>3454.6143096</v>
       </c>
       <c r="N83">
-        <v>-3177.1848668</v>
+        <v>-3219.3143096</v>
       </c>
       <c r="O83">
-        <v>-463.8689905527999</v>
+        <v>-470.0198892015999</v>
       </c>
       <c r="P83">
-        <v>-2713.3158762472</v>
+        <v>-2749.2944203984</v>
       </c>
       <c r="Q83">
-        <v>-2644.7158762472</v>
+        <v>-2680.6944203984</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2429807950769886</v>
+        <v>0.2539352836923769</v>
       </c>
       <c r="T83">
-        <v>4.553828985611747</v>
+        <v>4.806819484812399</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.0100670922629511</v>
+        <v>0.009944322845110234</v>
       </c>
       <c r="W83">
-        <v>0.2334261796443961</v>
+        <v>0.233455128673123</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06895268673254185</v>
+        <v>0.06811180030897424</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2371415565765887</v>
+        <v>0.2390415565765887</v>
       </c>
       <c r="C84">
-        <v>-10415.1803393862</v>
+        <v>-10626.77191847946</v>
       </c>
       <c r="D84">
-        <v>3348.731660613795</v>
+        <v>3315.806081520539</v>
       </c>
       <c r="E84">
-        <v>14317.012</v>
+        <v>14495.678</v>
       </c>
       <c r="F84">
-        <v>14650.612</v>
+        <v>14829.278</v>
       </c>
       <c r="G84">
         <v>886.7</v>
@@ -8163,37 +8163,37 @@
         <v>235.3</v>
       </c>
       <c r="M84">
-        <v>3454.6143096</v>
+        <v>3496.7437524</v>
       </c>
       <c r="N84">
-        <v>-3219.3143096</v>
+        <v>-3261.4437524</v>
       </c>
       <c r="O84">
-        <v>-470.0198892015999</v>
+        <v>-476.1707878504</v>
       </c>
       <c r="P84">
-        <v>-2749.2944203984</v>
+        <v>-2785.2729645496</v>
       </c>
       <c r="Q84">
-        <v>-2680.6944203984</v>
+        <v>-2716.6729645496</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2539352836923769</v>
+        <v>0.2661785356742814</v>
       </c>
       <c r="T84">
-        <v>4.806819484812399</v>
+        <v>5.089573572154306</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.009944322845110234</v>
+        <v>0.009824511726494447</v>
       </c>
       <c r="W84">
-        <v>0.233455128673123</v>
+        <v>0.2334833801348926</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06811180030897424</v>
+        <v>0.06729117620886615</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2390415565765887</v>
+        <v>0.2409415565765888</v>
       </c>
       <c r="C85">
-        <v>-10626.77191847946</v>
+        <v>-10837.72233634212</v>
       </c>
       <c r="D85">
-        <v>3315.806081520539</v>
+        <v>3283.521663657878</v>
       </c>
       <c r="E85">
-        <v>14495.678</v>
+        <v>14674.344</v>
       </c>
       <c r="F85">
-        <v>14829.278</v>
+        <v>15007.944</v>
       </c>
       <c r="G85">
         <v>886.7</v>
@@ -8245,37 +8245,37 @@
         <v>235.3</v>
       </c>
       <c r="M85">
-        <v>3496.7437524</v>
+        <v>3538.8731952</v>
       </c>
       <c r="N85">
-        <v>-3261.4437524</v>
+        <v>-3303.5731952</v>
       </c>
       <c r="O85">
-        <v>-476.1707878504</v>
+        <v>-482.3216864991999</v>
       </c>
       <c r="P85">
-        <v>-2785.2729645496</v>
+        <v>-2821.2515087008</v>
       </c>
       <c r="Q85">
-        <v>-2716.6729645496</v>
+        <v>-2752.6515087008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2661785356742814</v>
+        <v>0.2799521941539241</v>
       </c>
       <c r="T85">
-        <v>5.089573572154306</v>
+        <v>5.407671920413951</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.009824511726494447</v>
+        <v>0.009707553253559991</v>
       </c>
       <c r="W85">
-        <v>0.2334833801348926</v>
+        <v>0.2335109589428106</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06729117620886615</v>
+        <v>0.06649009077780821</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2409415565765887</v>
+        <v>0.2428415565765887</v>
       </c>
       <c r="C86">
-        <v>-10837.72233634212</v>
+        <v>-11048.05014042721</v>
       </c>
       <c r="D86">
-        <v>3283.521663657876</v>
+        <v>3251.859859572783</v>
       </c>
       <c r="E86">
-        <v>14674.344</v>
+        <v>14853.01</v>
       </c>
       <c r="F86">
-        <v>15007.944</v>
+        <v>15186.61</v>
       </c>
       <c r="G86">
         <v>886.7</v>
@@ -8327,37 +8327,37 @@
         <v>235.3</v>
       </c>
       <c r="M86">
-        <v>3538.873195199999</v>
+        <v>3581.002638</v>
       </c>
       <c r="N86">
-        <v>-3303.573195199999</v>
+        <v>-3345.702638</v>
       </c>
       <c r="O86">
-        <v>-482.3216864991999</v>
+        <v>-488.472585148</v>
       </c>
       <c r="P86">
-        <v>-2821.251508700799</v>
+        <v>-2857.230052852</v>
       </c>
       <c r="Q86">
-        <v>-2752.651508700799</v>
+        <v>-2788.630052852</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2799521941539239</v>
+        <v>0.2955623404308522</v>
       </c>
       <c r="T86">
-        <v>5.407671920413947</v>
+        <v>5.768183381774877</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.009707553253559991</v>
+        <v>0.009593346744694579</v>
       </c>
       <c r="W86">
-        <v>0.2335109589428106</v>
+        <v>0.233537888837601</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06649009077780821</v>
+        <v>0.06570785441571636</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2428415565765887</v>
+        <v>0.2447415565765887</v>
       </c>
       <c r="C87">
-        <v>-11048.05014042721</v>
+        <v>-11257.77316963473</v>
       </c>
       <c r="D87">
-        <v>3251.859859572783</v>
+        <v>3220.802830365265</v>
       </c>
       <c r="E87">
-        <v>14853.01</v>
+        <v>15031.676</v>
       </c>
       <c r="F87">
-        <v>15186.61</v>
+        <v>15365.276</v>
       </c>
       <c r="G87">
         <v>886.7</v>
@@ -8409,37 +8409,37 @@
         <v>235.3</v>
       </c>
       <c r="M87">
-        <v>3581.002638</v>
+        <v>3623.1320808</v>
       </c>
       <c r="N87">
-        <v>-3345.702638</v>
+        <v>-3387.832080799999</v>
       </c>
       <c r="O87">
-        <v>-488.472585148</v>
+        <v>-494.6234837967999</v>
       </c>
       <c r="P87">
-        <v>-2857.230052852</v>
+        <v>-2893.208597003199</v>
       </c>
       <c r="Q87">
-        <v>-2788.630052852</v>
+        <v>-2824.6085970032</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2955623404308522</v>
+        <v>0.3134025076044845</v>
       </c>
       <c r="T87">
-        <v>5.768183381774877</v>
+        <v>6.180196480473082</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.009593346744694579</v>
+        <v>0.009481796201151619</v>
       </c>
       <c r="W87">
-        <v>0.233537888837601</v>
+        <v>0.2335641924557685</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06570785441571636</v>
+        <v>0.06494380959692891</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2447415565765887</v>
+        <v>0.2466415565765887</v>
       </c>
       <c r="C88">
-        <v>-11257.77316963473</v>
+        <v>-11466.90858782688</v>
       </c>
       <c r="D88">
-        <v>3220.802830365265</v>
+        <v>3190.333412173116</v>
       </c>
       <c r="E88">
-        <v>15031.676</v>
+        <v>15210.342</v>
       </c>
       <c r="F88">
-        <v>15365.276</v>
+        <v>15543.942</v>
       </c>
       <c r="G88">
         <v>886.7</v>
@@ -8491,37 +8491,37 @@
         <v>235.3</v>
       </c>
       <c r="M88">
-        <v>3623.1320808</v>
+        <v>3665.2615236</v>
       </c>
       <c r="N88">
-        <v>-3387.832080799999</v>
+        <v>-3429.9615236</v>
       </c>
       <c r="O88">
-        <v>-494.6234837967999</v>
+        <v>-500.7743824455999</v>
       </c>
       <c r="P88">
-        <v>-2893.208597003199</v>
+        <v>-2929.1871411544</v>
       </c>
       <c r="Q88">
-        <v>-2824.6085970032</v>
+        <v>-2860.5871411544</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3134025076044845</v>
+        <v>0.3339873158817525</v>
       </c>
       <c r="T88">
-        <v>6.180196480473082</v>
+        <v>6.655596209740243</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.009481796201151619</v>
+        <v>0.009372810037919991</v>
       </c>
       <c r="W88">
-        <v>0.2335641924557685</v>
+        <v>0.2335898913930585</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06494380959692891</v>
+        <v>0.06419732902684927</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2466415565765887</v>
+        <v>0.2485415565765887</v>
       </c>
       <c r="C89">
-        <v>-11466.90858782688</v>
+        <v>-11675.47291545878</v>
       </c>
       <c r="D89">
-        <v>3190.333412173116</v>
+        <v>3160.435084541214</v>
       </c>
       <c r="E89">
-        <v>15210.342</v>
+        <v>15389.008</v>
       </c>
       <c r="F89">
-        <v>15543.942</v>
+        <v>15722.608</v>
       </c>
       <c r="G89">
         <v>886.7</v>
@@ -8573,37 +8573,37 @@
         <v>235.3</v>
       </c>
       <c r="M89">
-        <v>3665.2615236</v>
+        <v>3707.3909664</v>
       </c>
       <c r="N89">
-        <v>-3429.9615236</v>
+        <v>-3472.0909664</v>
       </c>
       <c r="O89">
-        <v>-500.7743824455999</v>
+        <v>-506.9252810943999</v>
       </c>
       <c r="P89">
-        <v>-2929.1871411544</v>
+        <v>-2965.1656853056</v>
       </c>
       <c r="Q89">
-        <v>-2860.5871411544</v>
+        <v>-2896.5656853056</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3339873158817525</v>
+        <v>0.3580029255385653</v>
       </c>
       <c r="T89">
-        <v>6.655596209740243</v>
+        <v>7.210229227218598</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.009372810037919991</v>
+        <v>0.009266300832943627</v>
       </c>
       <c r="W89">
-        <v>0.2335898913930585</v>
+        <v>0.2336150062635919</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06419732902684927</v>
+        <v>0.06346781392427148</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2485415565765887</v>
+        <v>0.2504415565765887</v>
       </c>
       <c r="C90">
-        <v>-11675.47291545878</v>
+        <v>-11883.48205944714</v>
       </c>
       <c r="D90">
-        <v>3160.435084541214</v>
+        <v>3131.091940552856</v>
       </c>
       <c r="E90">
-        <v>15389.008</v>
+        <v>15567.674</v>
       </c>
       <c r="F90">
-        <v>15722.608</v>
+        <v>15901.274</v>
       </c>
       <c r="G90">
         <v>886.7</v>
@@ -8655,37 +8655,37 @@
         <v>235.3</v>
       </c>
       <c r="M90">
-        <v>3707.3909664</v>
+        <v>3749.5204092</v>
       </c>
       <c r="N90">
-        <v>-3472.0909664</v>
+        <v>-3514.2204092</v>
       </c>
       <c r="O90">
-        <v>-506.9252810943999</v>
+        <v>-513.0761797431999</v>
       </c>
       <c r="P90">
-        <v>-2965.1656853056</v>
+        <v>-3001.1442294568</v>
       </c>
       <c r="Q90">
-        <v>-2896.5656853056</v>
+        <v>-2932.5442294568</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3580029255385653</v>
+        <v>0.3863850096784348</v>
       </c>
       <c r="T90">
-        <v>7.210229227218598</v>
+        <v>7.865704611511197</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.009266300832943627</v>
+        <v>0.009162185093247632</v>
       </c>
       <c r="W90">
-        <v>0.2336150062635919</v>
+        <v>0.2336395567550122</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06346781392427148</v>
+        <v>0.06275469241950438</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2504415565765887</v>
+        <v>0.2523415565765887</v>
       </c>
       <c r="C91">
-        <v>-11883.48205944714</v>
+        <v>-12090.95134139028</v>
       </c>
       <c r="D91">
-        <v>3131.091940552856</v>
+        <v>3102.288658609717</v>
       </c>
       <c r="E91">
-        <v>15567.674</v>
+        <v>15746.34</v>
       </c>
       <c r="F91">
-        <v>15901.274</v>
+        <v>16079.94</v>
       </c>
       <c r="G91">
         <v>886.7</v>
@@ -8737,37 +8737,37 @@
         <v>235.3</v>
       </c>
       <c r="M91">
-        <v>3749.5204092</v>
+        <v>3791.649852</v>
       </c>
       <c r="N91">
-        <v>-3514.2204092</v>
+        <v>-3556.349852</v>
       </c>
       <c r="O91">
-        <v>-513.0761797431999</v>
+        <v>-519.227078392</v>
       </c>
       <c r="P91">
-        <v>-3001.1442294568</v>
+        <v>-3037.122773608</v>
       </c>
       <c r="Q91">
-        <v>-2932.5442294568</v>
+        <v>-2968.522773608</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3863850096784348</v>
+        <v>0.4204435106462783</v>
       </c>
       <c r="T91">
-        <v>7.865704611511197</v>
+        <v>8.652275072662317</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.009162185093247632</v>
+        <v>0.009060383036655991</v>
       </c>
       <c r="W91">
-        <v>0.2336395567550122</v>
+        <v>0.2336635616799565</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06275469241950438</v>
+        <v>0.06205741805928766</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2523415565765887</v>
+        <v>0.2542415565765887</v>
       </c>
       <c r="C92">
-        <v>-12090.95134139028</v>
+        <v>-12297.89552424483</v>
       </c>
       <c r="D92">
-        <v>3102.288658609717</v>
+        <v>3074.010475755173</v>
       </c>
       <c r="E92">
-        <v>15746.34</v>
+        <v>15925.006</v>
       </c>
       <c r="F92">
-        <v>16079.94</v>
+        <v>16258.606</v>
       </c>
       <c r="G92">
         <v>886.7</v>
@@ -8819,37 +8819,37 @@
         <v>235.3</v>
       </c>
       <c r="M92">
-        <v>3791.649852</v>
+        <v>3833.7792948</v>
       </c>
       <c r="N92">
-        <v>-3556.349852</v>
+        <v>-3598.4792948</v>
       </c>
       <c r="O92">
-        <v>-519.227078392</v>
+        <v>-525.3779770407999</v>
       </c>
       <c r="P92">
-        <v>-3037.122773608</v>
+        <v>-3073.1013177592</v>
       </c>
       <c r="Q92">
-        <v>-2968.522773608</v>
+        <v>-3004.5013177592</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4204435106462783</v>
+        <v>0.4620705673847538</v>
       </c>
       <c r="T92">
-        <v>8.652275072662317</v>
+        <v>9.613638969624798</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.009060383036655991</v>
+        <v>0.008960818387901529</v>
       </c>
       <c r="W92">
-        <v>0.2336635616799565</v>
+        <v>0.2336870390241328</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06205741805928766</v>
+        <v>0.06137546841028452</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2542415565765887</v>
+        <v>0.2561415565765887</v>
       </c>
       <c r="C93">
-        <v>-12297.89552424483</v>
+        <v>-12504.32883755654</v>
       </c>
       <c r="D93">
-        <v>3074.010475755173</v>
+        <v>3046.243162443463</v>
       </c>
       <c r="E93">
-        <v>15925.006</v>
+        <v>16103.672</v>
       </c>
       <c r="F93">
-        <v>16258.606</v>
+        <v>16437.272</v>
       </c>
       <c r="G93">
         <v>886.7</v>
@@ -8901,37 +8901,37 @@
         <v>235.3</v>
       </c>
       <c r="M93">
-        <v>3833.7792948</v>
+        <v>3875.9087376</v>
       </c>
       <c r="N93">
-        <v>-3598.4792948</v>
+        <v>-3640.6087376</v>
       </c>
       <c r="O93">
-        <v>-525.3779770407999</v>
+        <v>-531.5288756896</v>
       </c>
       <c r="P93">
-        <v>-3073.1013177592</v>
+        <v>-3109.0798619104</v>
       </c>
       <c r="Q93">
-        <v>-3004.5013177592</v>
+        <v>-3040.4798619104</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4620705673847538</v>
+        <v>0.5141043883078481</v>
       </c>
       <c r="T93">
-        <v>9.613638969624798</v>
+        <v>10.8153438408279</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.008960818387901529</v>
+        <v>0.008863418188033035</v>
       </c>
       <c r="W93">
-        <v>0.2336870390241328</v>
+        <v>0.2337100059912618</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06137546841028452</v>
+        <v>0.06070834375365097</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2561415565765887</v>
+        <v>0.2580415565765887</v>
       </c>
       <c r="C94">
-        <v>-12504.32883755654</v>
+        <v>-12710.26500133596</v>
       </c>
       <c r="D94">
-        <v>3046.243162443463</v>
+        <v>3018.972998664043</v>
       </c>
       <c r="E94">
-        <v>16103.672</v>
+        <v>16282.338</v>
       </c>
       <c r="F94">
-        <v>16437.272</v>
+        <v>16615.938</v>
       </c>
       <c r="G94">
         <v>886.7</v>
@@ -8983,37 +8983,37 @@
         <v>235.3</v>
       </c>
       <c r="M94">
-        <v>3875.9087376</v>
+        <v>3918.0381804</v>
       </c>
       <c r="N94">
-        <v>-3640.6087376</v>
+        <v>-3682.7381804</v>
       </c>
       <c r="O94">
-        <v>-531.5288756896</v>
+        <v>-537.6797743384</v>
       </c>
       <c r="P94">
-        <v>-3109.0798619104</v>
+        <v>-3145.0584060616</v>
       </c>
       <c r="Q94">
-        <v>-3040.4798619104</v>
+        <v>-3076.4584060616</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5141043883078481</v>
+        <v>0.5810050152089693</v>
       </c>
       <c r="T94">
-        <v>10.8153438408279</v>
+        <v>12.36039296094618</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.008863418188033035</v>
+        <v>0.008768112616118701</v>
       </c>
       <c r="W94">
-        <v>0.2337100059912618</v>
+        <v>0.2337324790451192</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06070834375365097</v>
+        <v>0.06005556586382677</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2580415565765887</v>
+        <v>0.2599415565765887</v>
       </c>
       <c r="C95">
-        <v>-12710.26500133596</v>
+        <v>-12915.71724866301</v>
       </c>
       <c r="D95">
-        <v>3018.972998664043</v>
+        <v>2992.186751336986</v>
       </c>
       <c r="E95">
-        <v>16282.338</v>
+        <v>16461.004</v>
       </c>
       <c r="F95">
-        <v>16615.938</v>
+        <v>16794.604</v>
       </c>
       <c r="G95">
         <v>886.7</v>
@@ -9065,37 +9065,37 @@
         <v>235.3</v>
       </c>
       <c r="M95">
-        <v>3918.0381804</v>
+        <v>3960.1676232</v>
       </c>
       <c r="N95">
-        <v>-3682.7381804</v>
+        <v>-3724.8676232</v>
       </c>
       <c r="O95">
-        <v>-537.6797743384</v>
+        <v>-543.8306729871999</v>
       </c>
       <c r="P95">
-        <v>-3145.0584060616</v>
+        <v>-3181.0369502128</v>
       </c>
       <c r="Q95">
-        <v>-3076.4584060616</v>
+        <v>-3112.4369502128</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5810050152089693</v>
+        <v>0.670205851077131</v>
       </c>
       <c r="T95">
-        <v>12.36039296094618</v>
+        <v>14.42045845443721</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.008768112616118701</v>
+        <v>0.008674834822330203</v>
       </c>
       <c r="W95">
-        <v>0.2337324790451192</v>
+        <v>0.2337544739488945</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06005556586382677</v>
+        <v>0.05941667686527541</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2599415565765887</v>
+        <v>0.2618415565765887</v>
       </c>
       <c r="C96">
-        <v>-12915.71724866301</v>
+        <v>-13120.69834709883</v>
       </c>
       <c r="D96">
-        <v>2992.186751336986</v>
+        <v>2965.871652901167</v>
       </c>
       <c r="E96">
-        <v>16461.004</v>
+        <v>16639.67</v>
       </c>
       <c r="F96">
-        <v>16794.604</v>
+        <v>16973.27</v>
       </c>
       <c r="G96">
         <v>886.7</v>
@@ -9147,37 +9147,37 @@
         <v>235.3</v>
       </c>
       <c r="M96">
-        <v>3960.1676232</v>
+        <v>4002.297066</v>
       </c>
       <c r="N96">
-        <v>-3724.8676232</v>
+        <v>-3766.997066</v>
       </c>
       <c r="O96">
-        <v>-543.8306729871999</v>
+        <v>-549.9815716359999</v>
       </c>
       <c r="P96">
-        <v>-3181.0369502128</v>
+        <v>-3217.015494364</v>
       </c>
       <c r="Q96">
-        <v>-3112.4369502128</v>
+        <v>-3148.415494364</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.670205851077131</v>
+        <v>0.7950870212925575</v>
       </c>
       <c r="T96">
-        <v>14.42045845443721</v>
+        <v>17.30455014532465</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.008674834822330203</v>
+        <v>0.008583520771568834</v>
       </c>
       <c r="W96">
-        <v>0.2337544739488945</v>
+        <v>0.2337760058020641</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.05941667686527541</v>
+        <v>0.05879123816143039</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2618415565765887</v>
+        <v>0.2637415565765887</v>
       </c>
       <c r="C97">
-        <v>-13120.69834709883</v>
+        <v>-13325.22061897754</v>
       </c>
       <c r="D97">
-        <v>2965.871652901167</v>
+        <v>2940.015381022463</v>
       </c>
       <c r="E97">
-        <v>16639.67</v>
+        <v>16818.336</v>
       </c>
       <c r="F97">
-        <v>16973.27</v>
+        <v>17151.936</v>
       </c>
       <c r="G97">
         <v>886.7</v>
@@ -9229,37 +9229,37 @@
         <v>235.3</v>
       </c>
       <c r="M97">
-        <v>4002.297066</v>
+        <v>4044.426508800001</v>
       </c>
       <c r="N97">
-        <v>-3766.997066</v>
+        <v>-3809.1265088</v>
       </c>
       <c r="O97">
-        <v>-549.9815716359999</v>
+        <v>-556.1324702848</v>
       </c>
       <c r="P97">
-        <v>-3217.015494364</v>
+        <v>-3252.9940385152</v>
       </c>
       <c r="Q97">
-        <v>-3148.415494364</v>
+        <v>-3184.3940385152</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7950870212925575</v>
+        <v>0.9824087766156975</v>
       </c>
       <c r="T97">
-        <v>17.30455014532465</v>
+        <v>21.63068768165583</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.008583520771568834</v>
+        <v>0.00849410909686499</v>
       </c>
       <c r="W97">
-        <v>0.2337760058020641</v>
+        <v>0.2337970890749592</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05879123816143039</v>
+        <v>0.05817882943058217</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2637415565765887</v>
+        <v>0.2656415565765887</v>
       </c>
       <c r="C98">
-        <v>-13325.22061897754</v>
+        <v>-13529.29596064582</v>
       </c>
       <c r="D98">
-        <v>2940.015381022463</v>
+        <v>2914.606039354177</v>
       </c>
       <c r="E98">
-        <v>16818.336</v>
+        <v>16997.002</v>
       </c>
       <c r="F98">
-        <v>17151.936</v>
+        <v>17330.602</v>
       </c>
       <c r="G98">
         <v>886.7</v>
@@ -9311,37 +9311,37 @@
         <v>235.3</v>
       </c>
       <c r="M98">
-        <v>4044.4265088</v>
+        <v>4086.5559516</v>
       </c>
       <c r="N98">
-        <v>-3809.1265088</v>
+        <v>-3851.2559516</v>
       </c>
       <c r="O98">
-        <v>-556.1324702847999</v>
+        <v>-562.2833689335999</v>
       </c>
       <c r="P98">
-        <v>-3252.994038515199</v>
+        <v>-3288.9725826664</v>
       </c>
       <c r="Q98">
-        <v>-3184.3940385152</v>
+        <v>-3220.3725826664</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9824087766156948</v>
+        <v>1.29461170215426</v>
       </c>
       <c r="T98">
-        <v>21.63068768165577</v>
+        <v>28.84091690887436</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.008494109096864991</v>
+        <v>0.008406540961845765</v>
       </c>
       <c r="W98">
-        <v>0.2337970890749592</v>
+        <v>0.2338177376411968</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05817882943058217</v>
+        <v>0.05757904768387512</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2656415565765887</v>
+        <v>0.2675415565765887</v>
       </c>
       <c r="C99">
-        <v>-13529.29596064582</v>
+        <v>-13732.9358607134</v>
       </c>
       <c r="D99">
-        <v>2914.606039354177</v>
+        <v>2889.632139286596</v>
       </c>
       <c r="E99">
-        <v>16997.002</v>
+        <v>17175.668</v>
       </c>
       <c r="F99">
-        <v>17330.602</v>
+        <v>17509.268</v>
       </c>
       <c r="G99">
         <v>886.7</v>
@@ -9393,37 +9393,37 @@
         <v>235.3</v>
       </c>
       <c r="M99">
-        <v>4086.5559516</v>
+        <v>4128.6853944</v>
       </c>
       <c r="N99">
-        <v>-3851.2559516</v>
+        <v>-3893.3853944</v>
       </c>
       <c r="O99">
-        <v>-562.2833689335999</v>
+        <v>-568.4342675824</v>
       </c>
       <c r="P99">
-        <v>-3288.9725826664</v>
+        <v>-3324.9511268176</v>
       </c>
       <c r="Q99">
-        <v>-3220.3725826664</v>
+        <v>-3256.3511268176</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.29461170215426</v>
+        <v>1.91901755323139</v>
       </c>
       <c r="T99">
-        <v>28.84091690887436</v>
+        <v>43.26137536331154</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.008406540961845765</v>
+        <v>0.008320759931622847</v>
       </c>
       <c r="W99">
-        <v>0.2338177376411968</v>
+        <v>0.2338379648081234</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05757904768387512</v>
+        <v>0.0569915063809785</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2675415565765887</v>
+        <v>0.2694415565765887</v>
       </c>
       <c r="C100">
-        <v>-13732.9358607134</v>
+        <v>-13936.15141737312</v>
       </c>
       <c r="D100">
-        <v>2889.632139286596</v>
+        <v>2865.082582626879</v>
       </c>
       <c r="E100">
-        <v>17175.668</v>
+        <v>17354.334</v>
       </c>
       <c r="F100">
-        <v>17509.268</v>
+        <v>17687.934</v>
       </c>
       <c r="G100">
         <v>886.7</v>
@@ -9475,37 +9475,37 @@
         <v>235.3</v>
       </c>
       <c r="M100">
-        <v>4128.6853944</v>
+        <v>4170.8148372</v>
       </c>
       <c r="N100">
-        <v>-3893.3853944</v>
+        <v>-3935.514837199999</v>
       </c>
       <c r="O100">
-        <v>-568.4342675824</v>
+        <v>-574.5851662311999</v>
       </c>
       <c r="P100">
-        <v>-3324.9511268176</v>
+        <v>-3360.9296709688</v>
       </c>
       <c r="Q100">
-        <v>-3256.3511268176</v>
+        <v>-3292.3296709688</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.91901755323139</v>
+        <v>3.792235106462779</v>
       </c>
       <c r="T100">
-        <v>43.26137536331154</v>
+        <v>86.52275072662309</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.008320759931622847</v>
+        <v>0.008236711851505448</v>
       </c>
       <c r="W100">
-        <v>0.2338379648081234</v>
+        <v>0.233857783345415</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0569915063809785</v>
+        <v>0.0564158345993524</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2694415565765887</v>
-      </c>
-      <c r="C101">
-        <v>-13936.15141737312</v>
-      </c>
-      <c r="D101">
-        <v>2865.082582626879</v>
-      </c>
-      <c r="E101">
-        <v>17354.334</v>
-      </c>
-      <c r="F101">
-        <v>17687.934</v>
-      </c>
-      <c r="G101">
-        <v>886.7</v>
-      </c>
-      <c r="H101">
-        <v>17533</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>303.9</v>
-      </c>
-      <c r="K101">
-        <v>68.59999999999997</v>
-      </c>
-      <c r="L101">
-        <v>235.3</v>
-      </c>
-      <c r="M101">
-        <v>4170.8148372</v>
-      </c>
-      <c r="N101">
-        <v>-3935.514837199999</v>
-      </c>
-      <c r="O101">
-        <v>-574.5851662311999</v>
-      </c>
-      <c r="P101">
-        <v>-3360.9296709688</v>
-      </c>
-      <c r="Q101">
-        <v>-3292.3296709688</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.792235106462779</v>
-      </c>
-      <c r="T101">
-        <v>86.52275072662309</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.008236711851505448</v>
-      </c>
-      <c r="W101">
-        <v>0.233857783345415</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0564158345993524</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
